--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="991">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="1032">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -2998,6 +2998,129 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">The Ligor Epithon</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Irakli Tsikhelashvili</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">irakli.tsikhelashvili@nfa.gov.ge</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">National Food Agency of Georgia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nini&amp;Irakli</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">State Veterinarian;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tanupong Don Phinichka</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tanupongdph@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kanthanet Tharot</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tharotk.job@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr. Modu Bole Yusuf </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Federal College of Veterinary and Medical Laboratory Technology Vom </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Georgia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nini Tsertsvadze</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ninitsertsvadzee@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tbilisi, Georgia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Seleshe Nigatu Woldegebreal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">seleshe2@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">UoG_VEPH</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Akpem Terese Shadrach</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">terese990@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vet Konect Sentinels</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Scientist;Researcher;Professional;Animal Health Scientist;Undergraduate Student;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Marie Florrie Raphaël</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mariegaspard78@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mauritius</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Team Rod</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Agricultural Laboratory Technician;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nurul Putri Fajriani </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">nurulnpf11@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vetanalyst</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Krishna Adhikari</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vet.krishna22@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nepal (Asia-Pacific)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pierre Kenley MERVIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mervilpierrekenley07@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Haiti</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Todier Lab</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Undergraduate Student;Professional;Data Scientist;Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ASFA SAKHAWAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">asfa.sakhawat.041@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ASFA GOAT </x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3094,8 +3217,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M290" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M290"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M304" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M304"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -14160,11 +14283,527 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="291" hidden="0">
+      <x:c r="A291">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B291" s="2">
+        <x:v>46135.3891319444</x:v>
+      </x:c>
+      <x:c r="C291" s="2">
+        <x:v>46135.3895949074</x:v>
+      </x:c>
+      <x:c r="D291" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E291" s="10" t="s"/>
+      <x:c r="F291" s="2"/>
+      <x:c r="G291" s="10" t="s">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="H291" s="10" t="s">
+        <x:v>889</x:v>
+      </x:c>
+      <x:c r="I291" s="10" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J291" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K291" s="10" t="s">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c r="L291" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M291" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" hidden="0">
+      <x:c r="A292">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B292" s="2">
+        <x:v>46135.4186458333</x:v>
+      </x:c>
+      <x:c r="C292" s="2">
+        <x:v>46135.4202430556</x:v>
+      </x:c>
+      <x:c r="D292" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E292" s="10" t="s"/>
+      <x:c r="F292" s="2"/>
+      <x:c r="G292" s="10" t="s">
+        <x:v>991</x:v>
+      </x:c>
+      <x:c r="H292" s="10" t="s">
+        <x:v>992</x:v>
+      </x:c>
+      <x:c r="I292" s="10" t="s">
+        <x:v>993</x:v>
+      </x:c>
+      <x:c r="J292" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K292" s="10" t="s">
+        <x:v>994</x:v>
+      </x:c>
+      <x:c r="L292" s="10" t="s">
+        <x:v>995</x:v>
+      </x:c>
+      <x:c r="M292" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" hidden="0">
+      <x:c r="A293">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B293" s="2">
+        <x:v>46135.4205555556</x:v>
+      </x:c>
+      <x:c r="C293" s="2">
+        <x:v>46135.4211689815</x:v>
+      </x:c>
+      <x:c r="D293" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E293" s="10" t="s"/>
+      <x:c r="F293" s="2"/>
+      <x:c r="G293" s="10" t="s">
+        <x:v>996</x:v>
+      </x:c>
+      <x:c r="H293" s="10" t="s">
+        <x:v>997</x:v>
+      </x:c>
+      <x:c r="I293" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J293" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K293" s="10" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="L293" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M293" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" hidden="0">
+      <x:c r="A294">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B294" s="2">
+        <x:v>46135.420625</x:v>
+      </x:c>
+      <x:c r="C294" s="2">
+        <x:v>46135.4214467593</x:v>
+      </x:c>
+      <x:c r="D294" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E294" s="10" t="s"/>
+      <x:c r="F294" s="2"/>
+      <x:c r="G294" s="10" t="s">
+        <x:v>998</x:v>
+      </x:c>
+      <x:c r="H294" s="10" t="s">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="I294" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J294" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K294" s="10" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="L294" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M294" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" hidden="0">
+      <x:c r="A295">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B295" s="2">
+        <x:v>46135.4313310185</x:v>
+      </x:c>
+      <x:c r="C295" s="2">
+        <x:v>46135.4319328704</x:v>
+      </x:c>
+      <x:c r="D295" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E295" s="10" t="s"/>
+      <x:c r="F295" s="2"/>
+      <x:c r="G295" s="10" t="s">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="H295" s="10" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I295" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J295" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K295" s="10" t="s">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="L295" s="10" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="M295" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" hidden="0">
+      <x:c r="A296">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B296" s="2">
+        <x:v>46135.4343171296</x:v>
+      </x:c>
+      <x:c r="C296" s="2">
+        <x:v>46135.4372569444</x:v>
+      </x:c>
+      <x:c r="D296" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E296" s="10" t="s"/>
+      <x:c r="F296" s="2"/>
+      <x:c r="G296" s="10" t="s">
+        <x:v>991</x:v>
+      </x:c>
+      <x:c r="H296" s="10" t="s">
+        <x:v>992</x:v>
+      </x:c>
+      <x:c r="I296" s="10" t="s">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="J296" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K296" s="10" t="s">
+        <x:v>994</x:v>
+      </x:c>
+      <x:c r="L296" s="10" t="s">
+        <x:v>995</x:v>
+      </x:c>
+      <x:c r="M296" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" hidden="0">
+      <x:c r="A297">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B297" s="2">
+        <x:v>46135.4283449074</x:v>
+      </x:c>
+      <x:c r="C297" s="2">
+        <x:v>46135.4467824074</x:v>
+      </x:c>
+      <x:c r="D297" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E297" s="10" t="s"/>
+      <x:c r="F297" s="2"/>
+      <x:c r="G297" s="10" t="s">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="H297" s="10" t="s">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="I297" s="10" t="s">
+        <x:v>1005</x:v>
+      </x:c>
+      <x:c r="J297" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K297" s="10" t="s">
+        <x:v>994</x:v>
+      </x:c>
+      <x:c r="L297" s="10" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M297" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" hidden="0">
+      <x:c r="A298">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B298" s="2">
+        <x:v>46135.6037847222</x:v>
+      </x:c>
+      <x:c r="C298" s="2">
+        <x:v>46135.6062731481</x:v>
+      </x:c>
+      <x:c r="D298" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E298" s="10" t="s"/>
+      <x:c r="F298" s="2"/>
+      <x:c r="G298" s="10" t="s">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="H298" s="10" t="s">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="I298" s="10" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="J298" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K298" s="10" t="s">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="L298" s="10" t="s">
+        <x:v>742</x:v>
+      </x:c>
+      <x:c r="M298" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" hidden="0">
+      <x:c r="A299">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B299" s="2">
+        <x:v>46135.6748611111</x:v>
+      </x:c>
+      <x:c r="C299" s="2">
+        <x:v>46135.6793171296</x:v>
+      </x:c>
+      <x:c r="D299" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E299" s="10" t="s"/>
+      <x:c r="F299" s="2"/>
+      <x:c r="G299" s="10" t="s">
+        <x:v>1009</x:v>
+      </x:c>
+      <x:c r="H299" s="10" t="s">
+        <x:v>1010</x:v>
+      </x:c>
+      <x:c r="I299" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J299" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K299" s="10" t="s">
+        <x:v>1011</x:v>
+      </x:c>
+      <x:c r="L299" s="10" t="s">
+        <x:v>1012</x:v>
+      </x:c>
+      <x:c r="M299" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" hidden="0">
+      <x:c r="A300">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B300" s="2">
+        <x:v>46135.7480787037</x:v>
+      </x:c>
+      <x:c r="C300" s="2">
+        <x:v>46135.750150463</x:v>
+      </x:c>
+      <x:c r="D300" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E300" s="10" t="s"/>
+      <x:c r="F300" s="2"/>
+      <x:c r="G300" s="10" t="s">
+        <x:v>1013</x:v>
+      </x:c>
+      <x:c r="H300" s="10" t="s">
+        <x:v>1014</x:v>
+      </x:c>
+      <x:c r="I300" s="10" t="s">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="J300" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K300" s="10" t="s">
+        <x:v>1016</x:v>
+      </x:c>
+      <x:c r="L300" s="10" t="s">
+        <x:v>1017</x:v>
+      </x:c>
+      <x:c r="M300" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" hidden="0">
+      <x:c r="A301">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B301" s="2">
+        <x:v>46135.7911574074</x:v>
+      </x:c>
+      <x:c r="C301" s="2">
+        <x:v>46135.791875</x:v>
+      </x:c>
+      <x:c r="D301" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E301" s="10" t="s"/>
+      <x:c r="F301" s="2"/>
+      <x:c r="G301" s="10" t="s">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="H301" s="10" t="s">
+        <x:v>1019</x:v>
+      </x:c>
+      <x:c r="I301" s="10" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J301" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K301" s="10" t="s">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="L301" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M301" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" hidden="0">
+      <x:c r="A302">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B302" s="2">
+        <x:v>46136.1751041667</x:v>
+      </x:c>
+      <x:c r="C302" s="2">
+        <x:v>46136.1758217593</x:v>
+      </x:c>
+      <x:c r="D302" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E302" s="10" t="s"/>
+      <x:c r="F302" s="2"/>
+      <x:c r="G302" s="10" t="s">
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="H302" s="10" t="s">
+        <x:v>1022</x:v>
+      </x:c>
+      <x:c r="I302" s="10" t="s">
+        <x:v>1023</x:v>
+      </x:c>
+      <x:c r="J302" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K302" s="10" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L302" s="10" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="M302" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" hidden="0">
+      <x:c r="A303">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B303" s="2">
+        <x:v>46136.2869328704</x:v>
+      </x:c>
+      <x:c r="C303" s="2">
+        <x:v>46136.2912615741</x:v>
+      </x:c>
+      <x:c r="D303" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E303" s="10" t="s"/>
+      <x:c r="F303" s="2"/>
+      <x:c r="G303" s="10" t="s">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="H303" s="10" t="s">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="I303" s="10" t="s">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="J303" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K303" s="10" t="s">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="L303" s="10" t="s">
+        <x:v>1028</x:v>
+      </x:c>
+      <x:c r="M303" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" hidden="0">
+      <x:c r="A304">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B304" s="2">
+        <x:v>46136.3350347222</x:v>
+      </x:c>
+      <x:c r="C304" s="2">
+        <x:v>46136.3438194444</x:v>
+      </x:c>
+      <x:c r="D304" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E304" s="10" t="s"/>
+      <x:c r="F304" s="2"/>
+      <x:c r="G304" s="10" t="s">
+        <x:v>1029</x:v>
+      </x:c>
+      <x:c r="H304" s="10" t="s">
+        <x:v>1030</x:v>
+      </x:c>
+      <x:c r="I304" s="10" t="s"/>
+      <x:c r="J304" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K304" s="10" t="s">
+        <x:v>1031</x:v>
+      </x:c>
+      <x:c r="L304" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M304" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R300fca0ba5734c2f"/>
+    <x:tablePart r:id="R8cd4db46a5fd4748"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14451,13 +15090,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48B8CAB-BD5E-4A93-9EB6-2726A7E290D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EA68085-0A79-4B98-91B6-13161AC92B17}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59FEB566-B446-4128-94C6-03ABDB01F2F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{665DE5A3-1586-4FFB-82C7-23397BA248CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13576F2F-84F8-4B5C-823F-A4DBDCBAAC86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAEF3961-FE3C-4C33-8B5A-DE03FD2B2700}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="1032">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="1065">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -3121,6 +3121,105 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">ASFA GOAT </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vitor Salvador Picao Goncalves</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vitorspg@unb.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">OUEDRAOGO Daouda</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Burkina Faso</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Young Vet Power</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ibrahim Ishaq Ogido </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ibrahimogido@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nigerian </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Alpha</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Habyb Palyoga</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hbb.plyg@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brunei Darussalam</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cremaster</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Wafula Noel Auma </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">wafulanoel5@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Public Health </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Jabir Isaak Hassan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jabirhassan670@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AMUlytics</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Scientist;Animal Health Scientist;Undergraduate Student;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tomojit Ukil</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tomojit@onehealthtrust.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Adem Filali </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">adem.filali.20000@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tunisia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Filali Tech</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Data Scientist;Animal Health Scientist;Graduate Student;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Samson Mpinda </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">samsonmpinda952@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">IVSA MALAWI </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Chimwemwe Chita</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vetdocchita@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zambia</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3217,8 +3316,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M304" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M304"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M314" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M314"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -14799,304 +14898,381 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="305" hidden="0">
+      <x:c r="A305">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B305" s="2">
+        <x:v>46136.8523148148</x:v>
+      </x:c>
+      <x:c r="C305" s="2">
+        <x:v>46136.8530439815</x:v>
+      </x:c>
+      <x:c r="D305" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E305" s="10" t="s"/>
+      <x:c r="F305" s="2"/>
+      <x:c r="G305" s="10" t="s">
+        <x:v>1032</x:v>
+      </x:c>
+      <x:c r="H305" s="10" t="s">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="I305" s="10" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J305" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K305" s="10" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="L305" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M305" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" hidden="0">
+      <x:c r="A306">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B306" s="2">
+        <x:v>46137.8445601852</x:v>
+      </x:c>
+      <x:c r="C306" s="2">
+        <x:v>46137.8461111111</x:v>
+      </x:c>
+      <x:c r="D306" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E306" s="10" t="s"/>
+      <x:c r="F306" s="2"/>
+      <x:c r="G306" s="10" t="s">
+        <x:v>1034</x:v>
+      </x:c>
+      <x:c r="H306" s="10" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="I306" s="10" t="s">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c r="J306" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K306" s="10" t="s">
+        <x:v>1036</x:v>
+      </x:c>
+      <x:c r="L306" s="10" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="M306" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" hidden="0">
+      <x:c r="A307">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B307" s="2">
+        <x:v>46137.9427546296</x:v>
+      </x:c>
+      <x:c r="C307" s="2">
+        <x:v>46137.9440625</x:v>
+      </x:c>
+      <x:c r="D307" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E307" s="10" t="s"/>
+      <x:c r="F307" s="2"/>
+      <x:c r="G307" s="10" t="s">
+        <x:v>1037</x:v>
+      </x:c>
+      <x:c r="H307" s="10" t="s">
+        <x:v>1038</x:v>
+      </x:c>
+      <x:c r="I307" s="10" t="s">
+        <x:v>1039</x:v>
+      </x:c>
+      <x:c r="J307" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K307" s="10" t="s">
+        <x:v>1040</x:v>
+      </x:c>
+      <x:c r="L307" s="10" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="M307" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" hidden="0">
+      <x:c r="A308">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B308" s="2">
+        <x:v>46138.2328125</x:v>
+      </x:c>
+      <x:c r="C308" s="2">
+        <x:v>46138.2340509259</x:v>
+      </x:c>
+      <x:c r="D308" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E308" s="10" t="s"/>
+      <x:c r="F308" s="2"/>
+      <x:c r="G308" s="10" t="s">
+        <x:v>1041</x:v>
+      </x:c>
+      <x:c r="H308" s="10" t="s">
+        <x:v>1042</x:v>
+      </x:c>
+      <x:c r="I308" s="10" t="s">
+        <x:v>1043</x:v>
+      </x:c>
+      <x:c r="J308" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K308" s="10" t="s">
+        <x:v>1044</x:v>
+      </x:c>
+      <x:c r="L308" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M308" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" hidden="0">
+      <x:c r="A309">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B309" s="2">
+        <x:v>46139.3216203704</x:v>
+      </x:c>
+      <x:c r="C309" s="2">
+        <x:v>46139.3227893518</x:v>
+      </x:c>
+      <x:c r="D309" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E309" s="10" t="s"/>
+      <x:c r="F309" s="2"/>
+      <x:c r="G309" s="10" t="s">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="H309" s="10" t="s">
+        <x:v>1046</x:v>
+      </x:c>
+      <x:c r="I309" s="10" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J309" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K309" s="10" t="s">
+        <x:v>1047</x:v>
+      </x:c>
+      <x:c r="L309" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M309" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" hidden="0">
+      <x:c r="A310">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B310" s="2">
+        <x:v>46139.9275</x:v>
+      </x:c>
+      <x:c r="C310" s="2">
+        <x:v>46139.928900463</x:v>
+      </x:c>
+      <x:c r="D310" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E310" s="10" t="s"/>
+      <x:c r="F310" s="2"/>
+      <x:c r="G310" s="10" t="s">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="H310" s="10" t="s">
+        <x:v>1049</x:v>
+      </x:c>
+      <x:c r="I310" s="10" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J310" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K310" s="10" t="s">
+        <x:v>1050</x:v>
+      </x:c>
+      <x:c r="L310" s="10" t="s">
+        <x:v>1051</x:v>
+      </x:c>
+      <x:c r="M310" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" hidden="0">
+      <x:c r="A311">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B311" s="2">
+        <x:v>46140.9000115741</x:v>
+      </x:c>
+      <x:c r="C311" s="2">
+        <x:v>46140.9015972222</x:v>
+      </x:c>
+      <x:c r="D311" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E311" s="10" t="s"/>
+      <x:c r="F311" s="2"/>
+      <x:c r="G311" s="10" t="s">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="H311" s="10" t="s">
+        <x:v>1053</x:v>
+      </x:c>
+      <x:c r="I311" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J311" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K311" s="10" t="s">
+        <x:v>846</x:v>
+      </x:c>
+      <x:c r="L311" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M311" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" hidden="0">
+      <x:c r="A312">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B312" s="2">
+        <x:v>46141.9572106481</x:v>
+      </x:c>
+      <x:c r="C312" s="2">
+        <x:v>46141.9591550926</x:v>
+      </x:c>
+      <x:c r="D312" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E312" s="10" t="s"/>
+      <x:c r="F312" s="2"/>
+      <x:c r="G312" s="10" t="s">
+        <x:v>1054</x:v>
+      </x:c>
+      <x:c r="H312" s="10" t="s">
+        <x:v>1055</x:v>
+      </x:c>
+      <x:c r="I312" s="10" t="s">
+        <x:v>1056</x:v>
+      </x:c>
+      <x:c r="J312" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K312" s="10" t="s">
+        <x:v>1057</x:v>
+      </x:c>
+      <x:c r="L312" s="10" t="s">
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c r="M312" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" hidden="0">
+      <x:c r="A313">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B313" s="2">
+        <x:v>46141.9697685185</x:v>
+      </x:c>
+      <x:c r="C313" s="2">
+        <x:v>46141.9706134259</x:v>
+      </x:c>
+      <x:c r="D313" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E313" s="10" t="s"/>
+      <x:c r="F313" s="2"/>
+      <x:c r="G313" s="10" t="s">
+        <x:v>1059</x:v>
+      </x:c>
+      <x:c r="H313" s="10" t="s">
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c r="I313" s="10" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="J313" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K313" s="10" t="s">
+        <x:v>1061</x:v>
+      </x:c>
+      <x:c r="L313" s="10" t="s">
+        <x:v>915</x:v>
+      </x:c>
+      <x:c r="M313" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" hidden="0">
+      <x:c r="A314">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B314" s="2">
+        <x:v>46142.4372685185</x:v>
+      </x:c>
+      <x:c r="C314" s="2">
+        <x:v>46142.4388773148</x:v>
+      </x:c>
+      <x:c r="D314" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E314" s="10" t="s"/>
+      <x:c r="F314" s="2"/>
+      <x:c r="G314" s="10" t="s">
+        <x:v>1062</x:v>
+      </x:c>
+      <x:c r="H314" s="10" t="s">
+        <x:v>1063</x:v>
+      </x:c>
+      <x:c r="I314" s="10" t="s">
+        <x:v>1064</x:v>
+      </x:c>
+      <x:c r="J314" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K314" s="10" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="L314" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M314" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R8cd4db46a5fd4748"/>
+    <x:tablePart r:id="R61545cdcb6a54e11"/>
   </x:tableParts>
 </x:worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096F5A18ADBDD9E4D8F394AC4B3466405" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e59e3e6d23932d1d7525b22f7d7f3a7d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" xmlns:ns3="76b4ec34-0f89-435f-928a-b7c414764614" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d88756df8cabe05f154bf6d416a348" ns2:_="" ns3:_="">
-    <xsd:import namespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb"/>
-    <xsd:import namespace="76b4ec34-0f89-435f-928a-b7c414764614"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ad0b2da7-f7f1-4ade-bc4d-78491eef27d0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="76b4ec34-0f89-435f-928a-b7c414764614" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c696ee1e-5302-4bbd-96b7-dbc90bffde0f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="76b4ec34-0f89-435f-928a-b7c414764614">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="76b4ec34-0f89-435f-928a-b7c414764614" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EA68085-0A79-4B98-91B6-13161AC92B17}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{665DE5A3-1586-4FFB-82C7-23397BA248CF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAEF3961-FE3C-4C33-8B5A-DE03FD2B2700}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="1065">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="1109">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -3220,6 +3220,138 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Zambia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aditto Ahosan Kabbo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">aditahosankabbo@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PUSTStat</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ai-Ping Hsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">aphsu@mail.ncyu.edu.tw</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Chinese Taipei</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">VVL-NCYU</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vanessa Alejandra Valencia Palacios</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vanessavalencia2124@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">... </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Thierry Eynem</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Eynemthierry@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ChadAxis</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tawfik Esmat Abdel Hafeez Tawfik</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sohag Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pratikkiju2@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Disease_Intel</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Varangkana Thaotumpitak</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">varangkana.tha@mahidol.ac.th</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kapom</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kan Kledmanee   </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">kan.kle@mahidol.ac.th</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Methinee Pipatthana    </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">methinee.pip@mahidol.ac.th</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Thanayod Sasivimolrattana </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">thanayod.sas@mahidol.ac.th</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bopit Puyati  	</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bpuyati@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mustapha el otmani </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mustapha_elotmani@um5.ac.ma</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">I don't have a team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Emmanuel Opoku Darko </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">edopoku.svm@knust.edu.gh </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ghana </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KVTH</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Professional;Veterinary Medical Officer;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr. Srikanth S.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dr.srikanthsrirama@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">POH (PuduOneHealth)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Daniela Pacheco de Lacerda</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">daniela.lac@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Emily Javan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">emjavan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WOAH That's What I Call Data</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3316,8 +3448,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M314" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M314"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M330" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M330"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -15268,11 +15400,896 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="315" hidden="0">
+      <x:c r="A315">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B315" s="2">
+        <x:v>46142.9306018518</x:v>
+      </x:c>
+      <x:c r="C315" s="2">
+        <x:v>46142.9316435185</x:v>
+      </x:c>
+      <x:c r="D315" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E315" s="10" t="s"/>
+      <x:c r="F315" s="2"/>
+      <x:c r="G315" s="10" t="s">
+        <x:v>1065</x:v>
+      </x:c>
+      <x:c r="H315" s="10" t="s">
+        <x:v>1066</x:v>
+      </x:c>
+      <x:c r="I315" s="10" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="J315" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K315" s="10" t="s">
+        <x:v>1067</x:v>
+      </x:c>
+      <x:c r="L315" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M315" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" hidden="0">
+      <x:c r="A316">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B316" s="2">
+        <x:v>46143.1733449074</x:v>
+      </x:c>
+      <x:c r="C316" s="2">
+        <x:v>46143.185150463</x:v>
+      </x:c>
+      <x:c r="D316" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E316" s="10" t="s"/>
+      <x:c r="F316" s="2"/>
+      <x:c r="G316" s="10" t="s">
+        <x:v>1068</x:v>
+      </x:c>
+      <x:c r="H316" s="10" t="s">
+        <x:v>1069</x:v>
+      </x:c>
+      <x:c r="I316" s="10" t="s">
+        <x:v>1070</x:v>
+      </x:c>
+      <x:c r="J316" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K316" s="10" t="s">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c r="L316" s="10" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="M316" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" hidden="0">
+      <x:c r="A317">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B317" s="2">
+        <x:v>46143.6325347222</x:v>
+      </x:c>
+      <x:c r="C317" s="2">
+        <x:v>46143.63375</x:v>
+      </x:c>
+      <x:c r="D317" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E317" s="10" t="s"/>
+      <x:c r="F317" s="2"/>
+      <x:c r="G317" s="10" t="s">
+        <x:v>1072</x:v>
+      </x:c>
+      <x:c r="H317" s="10" t="s">
+        <x:v>1073</x:v>
+      </x:c>
+      <x:c r="I317" s="10" t="s">
+        <x:v>881</x:v>
+      </x:c>
+      <x:c r="J317" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K317" s="10" t="s">
+        <x:v>1074</x:v>
+      </x:c>
+      <x:c r="L317" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M317" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" hidden="0">
+      <x:c r="A318">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B318" s="2">
+        <x:v>46143.7225347222</x:v>
+      </x:c>
+      <x:c r="C318" s="2">
+        <x:v>46143.726412037</x:v>
+      </x:c>
+      <x:c r="D318" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E318" s="10" t="s"/>
+      <x:c r="F318" s="2"/>
+      <x:c r="G318" s="10" t="s">
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="H318" s="10" t="s">
+        <x:v>1076</x:v>
+      </x:c>
+      <x:c r="I318" s="10" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J318" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K318" s="10" t="s">
+        <x:v>1077</x:v>
+      </x:c>
+      <x:c r="L318" s="10" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="M318" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" hidden="0">
+      <x:c r="A319">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B319" s="2">
+        <x:v>46143.7933912037</x:v>
+      </x:c>
+      <x:c r="C319" s="2">
+        <x:v>46143.7958333333</x:v>
+      </x:c>
+      <x:c r="D319" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E319" s="10" t="s"/>
+      <x:c r="F319" s="2"/>
+      <x:c r="G319" s="10" t="s">
+        <x:v>1078</x:v>
+      </x:c>
+      <x:c r="H319" s="10" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="I319" s="10" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="J319" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K319" s="10" t="s">
+        <x:v>1079</x:v>
+      </x:c>
+      <x:c r="L319" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M319" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" hidden="0">
+      <x:c r="A320">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B320" s="2">
+        <x:v>46144.3020023148</x:v>
+      </x:c>
+      <x:c r="C320" s="2">
+        <x:v>46144.3027546296</x:v>
+      </x:c>
+      <x:c r="D320" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E320" s="10" t="s"/>
+      <x:c r="F320" s="2"/>
+      <x:c r="G320" s="10" t="s">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c r="H320" s="10" t="s">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="I320" s="10" t="s">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="J320" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K320" s="10" t="s">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="L320" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M320" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" hidden="0">
+      <x:c r="A321">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B321" s="2">
+        <x:v>46145.5023263889</x:v>
+      </x:c>
+      <x:c r="C321" s="2">
+        <x:v>46145.5064814815</x:v>
+      </x:c>
+      <x:c r="D321" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E321" s="10" t="s"/>
+      <x:c r="F321" s="2"/>
+      <x:c r="G321" s="10" t="s">
+        <x:v>1082</x:v>
+      </x:c>
+      <x:c r="H321" s="10" t="s">
+        <x:v>1083</x:v>
+      </x:c>
+      <x:c r="I321" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J321" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K321" s="10" t="s">
+        <x:v>1084</x:v>
+      </x:c>
+      <x:c r="L321" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M321" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" hidden="0">
+      <x:c r="A322">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B322" s="2">
+        <x:v>46145.5065162037</x:v>
+      </x:c>
+      <x:c r="C322" s="2">
+        <x:v>46145.507025463</x:v>
+      </x:c>
+      <x:c r="D322" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E322" s="10" t="s"/>
+      <x:c r="F322" s="2"/>
+      <x:c r="G322" s="10" t="s">
+        <x:v>1085</x:v>
+      </x:c>
+      <x:c r="H322" s="10" t="s">
+        <x:v>1086</x:v>
+      </x:c>
+      <x:c r="I322" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J322" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K322" s="10" t="s">
+        <x:v>1084</x:v>
+      </x:c>
+      <x:c r="L322" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M322" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" hidden="0">
+      <x:c r="A323">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B323" s="2">
+        <x:v>46145.5070601852</x:v>
+      </x:c>
+      <x:c r="C323" s="2">
+        <x:v>46145.5077546296</x:v>
+      </x:c>
+      <x:c r="D323" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E323" s="10" t="s"/>
+      <x:c r="F323" s="2"/>
+      <x:c r="G323" s="10" t="s">
+        <x:v>1087</x:v>
+      </x:c>
+      <x:c r="H323" s="10" t="s">
+        <x:v>1088</x:v>
+      </x:c>
+      <x:c r="I323" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J323" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K323" s="10" t="s">
+        <x:v>1084</x:v>
+      </x:c>
+      <x:c r="L323" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M323" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" hidden="0">
+      <x:c r="A324">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B324" s="2">
+        <x:v>46145.5077893518</x:v>
+      </x:c>
+      <x:c r="C324" s="2">
+        <x:v>46145.508125</x:v>
+      </x:c>
+      <x:c r="D324" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E324" s="10" t="s"/>
+      <x:c r="F324" s="2"/>
+      <x:c r="G324" s="10" t="s">
+        <x:v>1089</x:v>
+      </x:c>
+      <x:c r="H324" s="10" t="s">
+        <x:v>1090</x:v>
+      </x:c>
+      <x:c r="I324" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J324" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K324" s="10" t="s">
+        <x:v>1084</x:v>
+      </x:c>
+      <x:c r="L324" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M324" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" hidden="0">
+      <x:c r="A325">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B325" s="2">
+        <x:v>46145.5081481481</x:v>
+      </x:c>
+      <x:c r="C325" s="2">
+        <x:v>46145.5084143518</x:v>
+      </x:c>
+      <x:c r="D325" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E325" s="10" t="s"/>
+      <x:c r="F325" s="2"/>
+      <x:c r="G325" s="10" t="s">
+        <x:v>1091</x:v>
+      </x:c>
+      <x:c r="H325" s="10" t="s">
+        <x:v>1092</x:v>
+      </x:c>
+      <x:c r="I325" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J325" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K325" s="10" t="s">
+        <x:v>1084</x:v>
+      </x:c>
+      <x:c r="L325" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M325" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" hidden="0">
+      <x:c r="A326">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B326" s="2">
+        <x:v>46145.6104050926</x:v>
+      </x:c>
+      <x:c r="C326" s="2">
+        <x:v>46145.6134259259</x:v>
+      </x:c>
+      <x:c r="D326" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E326" s="10" t="s"/>
+      <x:c r="F326" s="2"/>
+      <x:c r="G326" s="10" t="s">
+        <x:v>1093</x:v>
+      </x:c>
+      <x:c r="H326" s="10" t="s">
+        <x:v>1094</x:v>
+      </x:c>
+      <x:c r="I326" s="10" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J326" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K326" s="10" t="s">
+        <x:v>1095</x:v>
+      </x:c>
+      <x:c r="L326" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M326" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" hidden="0">
+      <x:c r="A327">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="B327" s="2">
+        <x:v>46145.7722569444</x:v>
+      </x:c>
+      <x:c r="C327" s="2">
+        <x:v>46145.7794791667</x:v>
+      </x:c>
+      <x:c r="D327" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E327" s="10" t="s"/>
+      <x:c r="F327" s="2"/>
+      <x:c r="G327" s="10" t="s">
+        <x:v>1096</x:v>
+      </x:c>
+      <x:c r="H327" s="10" t="s">
+        <x:v>1097</x:v>
+      </x:c>
+      <x:c r="I327" s="10" t="s">
+        <x:v>1098</x:v>
+      </x:c>
+      <x:c r="J327" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K327" s="10" t="s">
+        <x:v>1099</x:v>
+      </x:c>
+      <x:c r="L327" s="10" t="s">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="M327" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" hidden="0">
+      <x:c r="A328">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B328" s="2">
+        <x:v>46146.5204166667</x:v>
+      </x:c>
+      <x:c r="C328" s="2">
+        <x:v>46146.5229976852</x:v>
+      </x:c>
+      <x:c r="D328" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E328" s="10" t="s"/>
+      <x:c r="F328" s="2"/>
+      <x:c r="G328" s="10" t="s">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H328" s="10" t="s">
+        <x:v>1102</x:v>
+      </x:c>
+      <x:c r="I328" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J328" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K328" s="10" t="s">
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="L328" s="10" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="M328" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" hidden="0">
+      <x:c r="A329">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B329" s="2">
+        <x:v>46146.7839351852</x:v>
+      </x:c>
+      <x:c r="C329" s="2">
+        <x:v>46146.7845138889</x:v>
+      </x:c>
+      <x:c r="D329" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E329" s="10" t="s"/>
+      <x:c r="F329" s="2"/>
+      <x:c r="G329" s="10" t="s">
+        <x:v>1104</x:v>
+      </x:c>
+      <x:c r="H329" s="10" t="s">
+        <x:v>1105</x:v>
+      </x:c>
+      <x:c r="I329" s="10" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J329" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K329" s="10" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="L329" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M329" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" hidden="0">
+      <x:c r="A330">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B330" s="2">
+        <x:v>46146.8863541667</x:v>
+      </x:c>
+      <x:c r="C330" s="2">
+        <x:v>46146.8886342593</x:v>
+      </x:c>
+      <x:c r="D330" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E330" s="10" t="s"/>
+      <x:c r="F330" s="2"/>
+      <x:c r="G330" s="10" t="s">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="H330" s="10" t="s">
+        <x:v>1107</x:v>
+      </x:c>
+      <x:c r="I330" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J330" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K330" s="10" t="s">
+        <x:v>1108</x:v>
+      </x:c>
+      <x:c r="L330" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="M330" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R61545cdcb6a54e11"/>
+    <x:tablePart r:id="R05c4cad12a2f41d1"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096F5A18ADBDD9E4D8F394AC4B3466405" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e59e3e6d23932d1d7525b22f7d7f3a7d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" xmlns:ns3="76b4ec34-0f89-435f-928a-b7c414764614" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d88756df8cabe05f154bf6d416a348" ns2:_="" ns3:_="">
+    <xsd:import namespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb"/>
+    <xsd:import namespace="76b4ec34-0f89-435f-928a-b7c414764614"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ad0b2da7-f7f1-4ade-bc4d-78491eef27d0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="76b4ec34-0f89-435f-928a-b7c414764614" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c696ee1e-5302-4bbd-96b7-dbc90bffde0f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="76b4ec34-0f89-435f-928a-b7c414764614">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="76b4ec34-0f89-435f-928a-b7c414764614" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{350E80FE-03B0-45E2-9D0F-3A4576F6DF14}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7151A021-81F8-46F0-86D3-710E3C9E3B60}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE20E32-D5E4-4701-98EB-ACBAE19094D1}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="1109">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="1123">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -3352,6 +3352,48 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">WOAH That's What I Call Data</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Valquiria Agnes Cardoso Côrtes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">valquiria.cortes@alumni.usp.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brasil</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">kurabachew gebrehiwot</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">gebrehiwotkurabachew@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CHEN，TING-JUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">s1114738@mail.ncyu.edu.tw</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Santatra Randrianarisoa</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">santatrarandria6@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Santatra Randrianarisoa </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nishitha Aysha Ashraf</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">nishitha.aysha@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Swochhal Prakash Shrestha </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">swochhal@gmail.com </x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3448,8 +3490,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M330" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M330"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M337" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M337"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -15992,11 +16034,270 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="331" hidden="0">
+      <x:c r="A331">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B331" s="2">
+        <x:v>46147.575150463</x:v>
+      </x:c>
+      <x:c r="C331" s="2">
+        <x:v>46147.5782291667</x:v>
+      </x:c>
+      <x:c r="D331" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E331" s="10" t="s"/>
+      <x:c r="F331" s="2"/>
+      <x:c r="G331" s="10" t="s">
+        <x:v>1109</x:v>
+      </x:c>
+      <x:c r="H331" s="10" t="s">
+        <x:v>1110</x:v>
+      </x:c>
+      <x:c r="I331" s="10" t="s">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="J331" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K331" s="10" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="L331" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M331" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" hidden="0">
+      <x:c r="A332">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B332" s="2">
+        <x:v>46147.6183680556</x:v>
+      </x:c>
+      <x:c r="C332" s="2">
+        <x:v>46147.6205208333</x:v>
+      </x:c>
+      <x:c r="D332" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E332" s="10" t="s"/>
+      <x:c r="F332" s="2"/>
+      <x:c r="G332" s="10" t="s">
+        <x:v>1112</x:v>
+      </x:c>
+      <x:c r="H332" s="10" t="s">
+        <x:v>1113</x:v>
+      </x:c>
+      <x:c r="I332" s="10" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="J332" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K332" s="10" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="L332" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M332" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" hidden="0">
+      <x:c r="A333">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B333" s="2">
+        <x:v>46148.2278587963</x:v>
+      </x:c>
+      <x:c r="C333" s="2">
+        <x:v>46148.2469675926</x:v>
+      </x:c>
+      <x:c r="D333" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E333" s="10" t="s"/>
+      <x:c r="F333" s="2"/>
+      <x:c r="G333" s="10" t="s">
+        <x:v>1114</x:v>
+      </x:c>
+      <x:c r="H333" s="10" t="s">
+        <x:v>1115</x:v>
+      </x:c>
+      <x:c r="I333" s="10" t="s">
+        <x:v>1070</x:v>
+      </x:c>
+      <x:c r="J333" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K333" s="10" t="s">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c r="L333" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M333" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" hidden="0">
+      <x:c r="A334">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B334" s="2">
+        <x:v>46148.2647685185</x:v>
+      </x:c>
+      <x:c r="C334" s="2">
+        <x:v>46148.2657638889</x:v>
+      </x:c>
+      <x:c r="D334" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E334" s="10" t="s"/>
+      <x:c r="F334" s="2"/>
+      <x:c r="G334" s="10" t="s">
+        <x:v>1116</x:v>
+      </x:c>
+      <x:c r="H334" s="10" t="s">
+        <x:v>1117</x:v>
+      </x:c>
+      <x:c r="I334" s="10" t="s">
+        <x:v>871</x:v>
+      </x:c>
+      <x:c r="J334" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K334" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L334" s="10" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="M334" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" hidden="0">
+      <x:c r="A335">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B335" s="2">
+        <x:v>46148.2684375</x:v>
+      </x:c>
+      <x:c r="C335" s="2">
+        <x:v>46148.268912037</x:v>
+      </x:c>
+      <x:c r="D335" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E335" s="10" t="s"/>
+      <x:c r="F335" s="2"/>
+      <x:c r="G335" s="10" t="s">
+        <x:v>1118</x:v>
+      </x:c>
+      <x:c r="H335" s="10" t="s">
+        <x:v>1117</x:v>
+      </x:c>
+      <x:c r="I335" s="10" t="s">
+        <x:v>871</x:v>
+      </x:c>
+      <x:c r="J335" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K335" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L335" s="10" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M335" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" hidden="0">
+      <x:c r="A336">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B336" s="2">
+        <x:v>46148.3338657407</x:v>
+      </x:c>
+      <x:c r="C336" s="2">
+        <x:v>46148.3346296296</x:v>
+      </x:c>
+      <x:c r="D336" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E336" s="10" t="s"/>
+      <x:c r="F336" s="2"/>
+      <x:c r="G336" s="10" t="s">
+        <x:v>1119</x:v>
+      </x:c>
+      <x:c r="H336" s="10" t="s">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="I336" s="10" t="s">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="J336" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K336" s="10" t="s">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="L336" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M336" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" hidden="0">
+      <x:c r="A337">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B337" s="2">
+        <x:v>46148.3446527778</x:v>
+      </x:c>
+      <x:c r="C337" s="2">
+        <x:v>46148.3452430556</x:v>
+      </x:c>
+      <x:c r="D337" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E337" s="10" t="s"/>
+      <x:c r="F337" s="2"/>
+      <x:c r="G337" s="10" t="s">
+        <x:v>1121</x:v>
+      </x:c>
+      <x:c r="H337" s="10" t="s">
+        <x:v>1122</x:v>
+      </x:c>
+      <x:c r="I337" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="J337" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K337" s="10" t="s">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="L337" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M337" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R05c4cad12a2f41d1"/>
+    <x:tablePart r:id="Rb2438a8849d14d33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16283,13 +16584,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{350E80FE-03B0-45E2-9D0F-3A4576F6DF14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E27EF0C2-196B-4C71-ADA6-CAFA6316F259}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7151A021-81F8-46F0-86D3-710E3C9E3B60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0159B4D-F83E-4C26-BA4F-BCE6EFE8257D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE20E32-D5E4-4701-98EB-ACBAE19094D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1807F71-DF77-4FCE-9CD2-55E9FB521AB5}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="1123">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="1151">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -3394,6 +3394,90 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">swochhal@gmail.com </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Noppawan ฺฺBuamithup</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">noppawandc@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">epidemiology</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Government officer ;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yuni Resti</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">yuni.resti@apps.ipb.ac.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mahameru</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ana Carolina Schmidt</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Carolina_schmidt@hotmail.com </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brasil </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">LEB1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Gerhard van Niekerk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">gerhard.van.niekerk@msd.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Flock Health Analytics</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Undergraduate Student;Professional;Visonary;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yaswanth Senthil Kumar Thilagavathi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">yaswanthst9734@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Noah Bos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">noahbos.mail@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Netherlands</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr V Bhanu Rekha </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bhanurekhav@river.edu.in</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RIVER VCRC team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Anton van der Gaag</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">anton7503@hotmail.nl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Haley Ma</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hy.haley.ma@gmail.com</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3490,8 +3574,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M337" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M337"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M346" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M346"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -16293,304 +16377,344 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="338" hidden="0">
+      <x:c r="A338">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B338" s="2">
+        <x:v>46148.6392824074</x:v>
+      </x:c>
+      <x:c r="C338" s="2">
+        <x:v>46148.6430439815</x:v>
+      </x:c>
+      <x:c r="D338" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E338" s="10" t="s"/>
+      <x:c r="F338" s="2"/>
+      <x:c r="G338" s="10" t="s">
+        <x:v>1123</x:v>
+      </x:c>
+      <x:c r="H338" s="10" t="s">
+        <x:v>1124</x:v>
+      </x:c>
+      <x:c r="I338" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J338" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K338" s="10" t="s">
+        <x:v>1125</x:v>
+      </x:c>
+      <x:c r="L338" s="10" t="s">
+        <x:v>1126</x:v>
+      </x:c>
+      <x:c r="M338" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" hidden="0">
+      <x:c r="A339">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="B339" s="2">
+        <x:v>46148.728587963</x:v>
+      </x:c>
+      <x:c r="C339" s="2">
+        <x:v>46148.7380324074</x:v>
+      </x:c>
+      <x:c r="D339" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E339" s="10" t="s"/>
+      <x:c r="F339" s="2"/>
+      <x:c r="G339" s="10" t="s">
+        <x:v>1127</x:v>
+      </x:c>
+      <x:c r="H339" s="10" t="s">
+        <x:v>1128</x:v>
+      </x:c>
+      <x:c r="I339" s="10" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J339" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K339" s="10" t="s">
+        <x:v>1129</x:v>
+      </x:c>
+      <x:c r="L339" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M339" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" hidden="0">
+      <x:c r="A340">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B340" s="2">
+        <x:v>46148.9201157407</x:v>
+      </x:c>
+      <x:c r="C340" s="2">
+        <x:v>46148.9214930556</x:v>
+      </x:c>
+      <x:c r="D340" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E340" s="10" t="s"/>
+      <x:c r="F340" s="2"/>
+      <x:c r="G340" s="10" t="s">
+        <x:v>1130</x:v>
+      </x:c>
+      <x:c r="H340" s="10" t="s">
+        <x:v>1131</x:v>
+      </x:c>
+      <x:c r="I340" s="10" t="s">
+        <x:v>1132</x:v>
+      </x:c>
+      <x:c r="J340" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K340" s="10" t="s">
+        <x:v>1133</x:v>
+      </x:c>
+      <x:c r="L340" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M340" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" hidden="0">
+      <x:c r="A341">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="B341" s="2">
+        <x:v>46149.5173611111</x:v>
+      </x:c>
+      <x:c r="C341" s="2">
+        <x:v>46149.5200231481</x:v>
+      </x:c>
+      <x:c r="D341" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E341" s="10" t="s"/>
+      <x:c r="F341" s="2"/>
+      <x:c r="G341" s="10" t="s">
+        <x:v>1134</x:v>
+      </x:c>
+      <x:c r="H341" s="10" t="s">
+        <x:v>1135</x:v>
+      </x:c>
+      <x:c r="I341" s="10" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="J341" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K341" s="10" t="s">
+        <x:v>1136</x:v>
+      </x:c>
+      <x:c r="L341" s="10" t="s">
+        <x:v>1137</x:v>
+      </x:c>
+      <x:c r="M341" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" hidden="0">
+      <x:c r="A342">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B342" s="2">
+        <x:v>46149.6287152778</x:v>
+      </x:c>
+      <x:c r="C342" s="2">
+        <x:v>46149.6294560185</x:v>
+      </x:c>
+      <x:c r="D342" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E342" s="10" t="s"/>
+      <x:c r="F342" s="2"/>
+      <x:c r="G342" s="10" t="s">
+        <x:v>1138</x:v>
+      </x:c>
+      <x:c r="H342" s="10" t="s">
+        <x:v>1139</x:v>
+      </x:c>
+      <x:c r="I342" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J342" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K342" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L342" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M342" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" hidden="0">
+      <x:c r="A343">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B343" s="2">
+        <x:v>46149.6892708333</x:v>
+      </x:c>
+      <x:c r="C343" s="2">
+        <x:v>46149.6896064815</x:v>
+      </x:c>
+      <x:c r="D343" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E343" s="10" t="s"/>
+      <x:c r="F343" s="2"/>
+      <x:c r="G343" s="10" t="s">
+        <x:v>1140</x:v>
+      </x:c>
+      <x:c r="H343" s="10" t="s">
+        <x:v>1141</x:v>
+      </x:c>
+      <x:c r="I343" s="10" t="s">
+        <x:v>1142</x:v>
+      </x:c>
+      <x:c r="J343" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K343" s="10" t="s">
+        <x:v>1143</x:v>
+      </x:c>
+      <x:c r="L343" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M343" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" hidden="0">
+      <x:c r="A344">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B344" s="2">
+        <x:v>46149.7407638889</x:v>
+      </x:c>
+      <x:c r="C344" s="2">
+        <x:v>46149.7437615741</x:v>
+      </x:c>
+      <x:c r="D344" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E344" s="10" t="s"/>
+      <x:c r="F344" s="2"/>
+      <x:c r="G344" s="10" t="s">
+        <x:v>1144</x:v>
+      </x:c>
+      <x:c r="H344" s="10" t="s">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="I344" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J344" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K344" s="10" t="s">
+        <x:v>1146</x:v>
+      </x:c>
+      <x:c r="L344" s="10" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M344" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" hidden="0">
+      <x:c r="A345">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B345" s="2">
+        <x:v>46149.7546064815</x:v>
+      </x:c>
+      <x:c r="C345" s="2">
+        <x:v>46149.7563425926</x:v>
+      </x:c>
+      <x:c r="D345" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E345" s="10" t="s"/>
+      <x:c r="F345" s="2"/>
+      <x:c r="G345" s="10" t="s">
+        <x:v>1147</x:v>
+      </x:c>
+      <x:c r="H345" s="10" t="s">
+        <x:v>1148</x:v>
+      </x:c>
+      <x:c r="I345" s="10" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="J345" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K345" s="7" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="L345" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M345" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" hidden="0">
+      <x:c r="A346">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B346" s="2">
+        <x:v>46150.2672337963</x:v>
+      </x:c>
+      <x:c r="C346" s="2">
+        <x:v>46150.2682986111</x:v>
+      </x:c>
+      <x:c r="D346" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E346" s="10" t="s"/>
+      <x:c r="F346" s="2"/>
+      <x:c r="G346" s="10" t="s">
+        <x:v>1149</x:v>
+      </x:c>
+      <x:c r="H346" s="10" t="s">
+        <x:v>1150</x:v>
+      </x:c>
+      <x:c r="I346" s="10" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J346" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K346" s="10" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L346" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M346" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Rb2438a8849d14d33"/>
+    <x:tablePart r:id="R0ca2662babf64034"/>
   </x:tableParts>
 </x:worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096F5A18ADBDD9E4D8F394AC4B3466405" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e59e3e6d23932d1d7525b22f7d7f3a7d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" xmlns:ns3="76b4ec34-0f89-435f-928a-b7c414764614" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d88756df8cabe05f154bf6d416a348" ns2:_="" ns3:_="">
-    <xsd:import namespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb"/>
-    <xsd:import namespace="76b4ec34-0f89-435f-928a-b7c414764614"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ad0b2da7-f7f1-4ade-bc4d-78491eef27d0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="76b4ec34-0f89-435f-928a-b7c414764614" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c696ee1e-5302-4bbd-96b7-dbc90bffde0f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="76b4ec34-0f89-435f-928a-b7c414764614">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="76b4ec34-0f89-435f-928a-b7c414764614" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E27EF0C2-196B-4C71-ADA6-CAFA6316F259}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0159B4D-F83E-4C26-BA4F-BCE6EFE8257D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1807F71-DF77-4FCE-9CD2-55E9FB521AB5}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="1151">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="1203">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -3478,6 +3478,162 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">hy.haley.ma@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Shreeya Sharma</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">shreeys@clemson.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Avengers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aayush Poudel</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">aayush.poudel@ucalgary.ca</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Navin Pandey</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">navinpandey953@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Otitochukwuka Olaoluwakitan Osakuni</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Osakunishade@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bolor Bold</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bolor.bold.ch@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mongolia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Association of Human and Animal Health Epidemiology</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Researcher;Data Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Desalegn Zemene Demesash</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">desalegnzemene2008@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ethiopia, Amhara region</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lay Armachiho animal health tiwinning</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Gashaw abebe (Dr)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">agashaw2003abebe@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal health and welfare group</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr Haymanot Endalew Aynalem</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">haymanotendalew1212@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No.individual </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal health tewinning</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal Health Scientist;Veterinary epidemiologist ;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr Tsehayneh Cheklie Gebeyehu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tsehaynehcheklie8@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Veterinary clinic</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ethiopia;bahir dar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AKIN AYDIN AKSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">aaksel7@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Turkey</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr Aemro Awoke</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">newmanbest80@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Gojjam Epidemiologist</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr.Addisu Gedif Demie</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">addisugedif22@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ethiopia,Amhara</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Animal Health Scientist;Animal Health Surveillance Expert";</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Marie Teshager Tsehay</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">teshagermarie@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Field veterinarian </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Abaynew Gelaye Mehretu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">abaynewgelaye@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Abaynew Gelaye (DVM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Nad E Ali </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">nadeali1440@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Undergraduate Student;Final Year Internship Trainee ;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yasesew Wale</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">yayesewwale@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">For data management purpose</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3574,8 +3730,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M346" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M346"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M365" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M365"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -16710,11 +16866,1007 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="347" hidden="0">
+      <x:c r="A347">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B347" s="2">
+        <x:v>46151.0677314815</x:v>
+      </x:c>
+      <x:c r="C347" s="2">
+        <x:v>46151.0683680556</x:v>
+      </x:c>
+      <x:c r="D347" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E347" s="10" t="s"/>
+      <x:c r="F347" s="2"/>
+      <x:c r="G347" s="10" t="s">
+        <x:v>1151</x:v>
+      </x:c>
+      <x:c r="H347" s="10" t="s">
+        <x:v>1152</x:v>
+      </x:c>
+      <x:c r="I347" s="10" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="J347" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K347" s="10" t="s">
+        <x:v>1153</x:v>
+      </x:c>
+      <x:c r="L347" s="10" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="M347" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" hidden="0">
+      <x:c r="A348">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="B348" s="2">
+        <x:v>46151.1475694444</x:v>
+      </x:c>
+      <x:c r="C348" s="2">
+        <x:v>46151.1482638889</x:v>
+      </x:c>
+      <x:c r="D348" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E348" s="10" t="s"/>
+      <x:c r="F348" s="2"/>
+      <x:c r="G348" s="10" t="s">
+        <x:v>1154</x:v>
+      </x:c>
+      <x:c r="H348" s="10" t="s">
+        <x:v>1155</x:v>
+      </x:c>
+      <x:c r="I348" s="10" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J348" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K348" s="10" t="s">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="L348" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M348" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" hidden="0">
+      <x:c r="A349">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B349" s="2">
+        <x:v>46151.2439236111</x:v>
+      </x:c>
+      <x:c r="C349" s="2">
+        <x:v>46151.2448611111</x:v>
+      </x:c>
+      <x:c r="D349" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E349" s="10" t="s"/>
+      <x:c r="F349" s="2"/>
+      <x:c r="G349" s="10" t="s">
+        <x:v>1156</x:v>
+      </x:c>
+      <x:c r="H349" s="10" t="s">
+        <x:v>1157</x:v>
+      </x:c>
+      <x:c r="I349" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J349" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K349" s="10" t="s">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="L349" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M349" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" hidden="0">
+      <x:c r="A350">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B350" s="2">
+        <x:v>46151.3533796296</x:v>
+      </x:c>
+      <x:c r="C350" s="2">
+        <x:v>46151.3540856481</x:v>
+      </x:c>
+      <x:c r="D350" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E350" s="10" t="s"/>
+      <x:c r="F350" s="2"/>
+      <x:c r="G350" s="10" t="s">
+        <x:v>1158</x:v>
+      </x:c>
+      <x:c r="H350" s="10" t="s">
+        <x:v>1159</x:v>
+      </x:c>
+      <x:c r="I350" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J350" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K350" s="10" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="L350" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M350" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" hidden="0">
+      <x:c r="A351">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B351" s="2">
+        <x:v>46151.4404513889</x:v>
+      </x:c>
+      <x:c r="C351" s="2">
+        <x:v>46151.4431712963</x:v>
+      </x:c>
+      <x:c r="D351" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E351" s="10" t="s"/>
+      <x:c r="F351" s="2"/>
+      <x:c r="G351" s="10" t="s">
+        <x:v>1160</x:v>
+      </x:c>
+      <x:c r="H351" s="10" t="s">
+        <x:v>1161</x:v>
+      </x:c>
+      <x:c r="I351" s="10" t="s">
+        <x:v>1162</x:v>
+      </x:c>
+      <x:c r="J351" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K351" s="10" t="s">
+        <x:v>1163</x:v>
+      </x:c>
+      <x:c r="L351" s="10" t="s">
+        <x:v>1164</x:v>
+      </x:c>
+      <x:c r="M351" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" hidden="0">
+      <x:c r="A352">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B352" s="2">
+        <x:v>46151.7477893519</x:v>
+      </x:c>
+      <x:c r="C352" s="2">
+        <x:v>46151.750162037</x:v>
+      </x:c>
+      <x:c r="D352" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E352" s="10" t="s"/>
+      <x:c r="F352" s="2"/>
+      <x:c r="G352" s="10" t="s">
+        <x:v>1165</x:v>
+      </x:c>
+      <x:c r="H352" s="10" t="s">
+        <x:v>1166</x:v>
+      </x:c>
+      <x:c r="I352" s="10" t="s">
+        <x:v>1167</x:v>
+      </x:c>
+      <x:c r="J352" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K352" s="10" t="s">
+        <x:v>1168</x:v>
+      </x:c>
+      <x:c r="L352" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M352" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" hidden="0">
+      <x:c r="A353">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B353" s="2">
+        <x:v>46151.769537037</x:v>
+      </x:c>
+      <x:c r="C353" s="2">
+        <x:v>46151.7778819444</x:v>
+      </x:c>
+      <x:c r="D353" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E353" s="10" t="s"/>
+      <x:c r="F353" s="2"/>
+      <x:c r="G353" s="10" t="s">
+        <x:v>1169</x:v>
+      </x:c>
+      <x:c r="H353" s="10" t="s">
+        <x:v>1170</x:v>
+      </x:c>
+      <x:c r="I353" s="10" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="J353" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K353" s="10" t="s">
+        <x:v>1171</x:v>
+      </x:c>
+      <x:c r="L353" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M353" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" hidden="0">
+      <x:c r="A354">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B354" s="2">
+        <x:v>46151.8046643518</x:v>
+      </x:c>
+      <x:c r="C354" s="2">
+        <x:v>46151.8061342593</x:v>
+      </x:c>
+      <x:c r="D354" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E354" s="10" t="s"/>
+      <x:c r="F354" s="2"/>
+      <x:c r="G354" s="10" t="s">
+        <x:v>1172</x:v>
+      </x:c>
+      <x:c r="H354" s="10" t="s">
+        <x:v>1173</x:v>
+      </x:c>
+      <x:c r="I354" s="10" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J354" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K354" s="10" t="s">
+        <x:v>1174</x:v>
+      </x:c>
+      <x:c r="L354" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M354" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" hidden="0">
+      <x:c r="A355">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B355" s="2">
+        <x:v>46151.806099537</x:v>
+      </x:c>
+      <x:c r="C355" s="2">
+        <x:v>46151.8076736111</x:v>
+      </x:c>
+      <x:c r="D355" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E355" s="10" t="s"/>
+      <x:c r="F355" s="2"/>
+      <x:c r="G355" s="10" t="s">
+        <x:v>1165</x:v>
+      </x:c>
+      <x:c r="H355" s="10" t="s">
+        <x:v>1166</x:v>
+      </x:c>
+      <x:c r="I355" s="10" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J355" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K355" s="10" t="s">
+        <x:v>1175</x:v>
+      </x:c>
+      <x:c r="L355" s="10" t="s">
+        <x:v>1176</x:v>
+      </x:c>
+      <x:c r="M355" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" hidden="0">
+      <x:c r="A356">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B356" s="2">
+        <x:v>46151.8419328704</x:v>
+      </x:c>
+      <x:c r="C356" s="2">
+        <x:v>46151.844375</x:v>
+      </x:c>
+      <x:c r="D356" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E356" s="10" t="s"/>
+      <x:c r="F356" s="2"/>
+      <x:c r="G356" s="10" t="s">
+        <x:v>1177</x:v>
+      </x:c>
+      <x:c r="H356" s="10" t="s">
+        <x:v>1178</x:v>
+      </x:c>
+      <x:c r="I356" s="10" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="J356" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K356" s="10" t="s">
+        <x:v>1179</x:v>
+      </x:c>
+      <x:c r="L356" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M356" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" hidden="0">
+      <x:c r="A357">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B357" s="2">
+        <x:v>46151.8458333333</x:v>
+      </x:c>
+      <x:c r="C357" s="2">
+        <x:v>46151.8475810185</x:v>
+      </x:c>
+      <x:c r="D357" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E357" s="10" t="s"/>
+      <x:c r="F357" s="2"/>
+      <x:c r="G357" s="10" t="s">
+        <x:v>1177</x:v>
+      </x:c>
+      <x:c r="H357" s="10" t="s">
+        <x:v>1178</x:v>
+      </x:c>
+      <x:c r="I357" s="10" t="s">
+        <x:v>1180</x:v>
+      </x:c>
+      <x:c r="J357" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K357" s="10" t="s">
+        <x:v>1179</x:v>
+      </x:c>
+      <x:c r="L357" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M357" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" hidden="0">
+      <x:c r="A358">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="B358" s="2">
+        <x:v>46151.8875347222</x:v>
+      </x:c>
+      <x:c r="C358" s="2">
+        <x:v>46151.8885185185</x:v>
+      </x:c>
+      <x:c r="D358" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E358" s="10" t="s"/>
+      <x:c r="F358" s="2"/>
+      <x:c r="G358" s="10" t="s">
+        <x:v>1181</x:v>
+      </x:c>
+      <x:c r="H358" s="10" t="s">
+        <x:v>1182</x:v>
+      </x:c>
+      <x:c r="I358" s="10" t="s">
+        <x:v>1183</x:v>
+      </x:c>
+      <x:c r="J358" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K358" s="10" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L358" s="10" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="M358" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" hidden="0">
+      <x:c r="A359">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B359" s="2">
+        <x:v>46152.2396296296</x:v>
+      </x:c>
+      <x:c r="C359" s="2">
+        <x:v>46152.242662037</x:v>
+      </x:c>
+      <x:c r="D359" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E359" s="10" t="s"/>
+      <x:c r="F359" s="2"/>
+      <x:c r="G359" s="10" t="s">
+        <x:v>1184</x:v>
+      </x:c>
+      <x:c r="H359" s="10" t="s">
+        <x:v>1185</x:v>
+      </x:c>
+      <x:c r="I359" s="10" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J359" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K359" s="10" t="s">
+        <x:v>1186</x:v>
+      </x:c>
+      <x:c r="L359" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M359" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" hidden="0">
+      <x:c r="A360">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="B360" s="2">
+        <x:v>46152.3205671296</x:v>
+      </x:c>
+      <x:c r="C360" s="2">
+        <x:v>46152.323912037</x:v>
+      </x:c>
+      <x:c r="D360" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E360" s="10" t="s"/>
+      <x:c r="F360" s="2"/>
+      <x:c r="G360" s="10" t="s">
+        <x:v>1187</x:v>
+      </x:c>
+      <x:c r="H360" s="10" t="s">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="I360" s="10" t="s">
+        <x:v>1189</x:v>
+      </x:c>
+      <x:c r="J360" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K360" s="10" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L360" s="10" t="s">
+        <x:v>1190</x:v>
+      </x:c>
+      <x:c r="M360" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" hidden="0">
+      <x:c r="A361">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B361" s="2">
+        <x:v>46152.4293865741</x:v>
+      </x:c>
+      <x:c r="C361" s="2">
+        <x:v>46152.431412037</x:v>
+      </x:c>
+      <x:c r="D361" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E361" s="10" t="s"/>
+      <x:c r="F361" s="2"/>
+      <x:c r="G361" s="10" t="s">
+        <x:v>1191</x:v>
+      </x:c>
+      <x:c r="H361" s="10" t="s">
+        <x:v>1192</x:v>
+      </x:c>
+      <x:c r="I361" s="10" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="J361" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K361" s="10" t="s">
+        <x:v>1193</x:v>
+      </x:c>
+      <x:c r="L361" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M361" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" hidden="0">
+      <x:c r="A362">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="B362" s="2">
+        <x:v>46152.5694328704</x:v>
+      </x:c>
+      <x:c r="C362" s="2">
+        <x:v>46152.5715277778</x:v>
+      </x:c>
+      <x:c r="D362" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E362" s="10" t="s"/>
+      <x:c r="F362" s="2"/>
+      <x:c r="G362" s="10" t="s">
+        <x:v>1194</x:v>
+      </x:c>
+      <x:c r="H362" s="10" t="s">
+        <x:v>1195</x:v>
+      </x:c>
+      <x:c r="I362" s="10" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="J362" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K362" s="10" t="s">
+        <x:v>1196</x:v>
+      </x:c>
+      <x:c r="L362" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M362" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" hidden="0">
+      <x:c r="A363">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="B363" s="2">
+        <x:v>46152.7003356481</x:v>
+      </x:c>
+      <x:c r="C363" s="2">
+        <x:v>46152.7019328704</x:v>
+      </x:c>
+      <x:c r="D363" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E363" s="10" t="s"/>
+      <x:c r="F363" s="2"/>
+      <x:c r="G363" s="10" t="s">
+        <x:v>1197</x:v>
+      </x:c>
+      <x:c r="H363" s="10" t="s">
+        <x:v>1198</x:v>
+      </x:c>
+      <x:c r="I363" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J363" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K363" s="10" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L363" s="10" t="s">
+        <x:v>1199</x:v>
+      </x:c>
+      <x:c r="M363" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" hidden="0">
+      <x:c r="A364">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="B364" s="2">
+        <x:v>46152.7839467593</x:v>
+      </x:c>
+      <x:c r="C364" s="2">
+        <x:v>46152.7856597222</x:v>
+      </x:c>
+      <x:c r="D364" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E364" s="10" t="s"/>
+      <x:c r="F364" s="2"/>
+      <x:c r="G364" s="10" t="s">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="H364" s="10" t="s">
+        <x:v>1201</x:v>
+      </x:c>
+      <x:c r="I364" s="10" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="J364" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K364" s="10" t="s">
+        <x:v>1202</x:v>
+      </x:c>
+      <x:c r="L364" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M364" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" hidden="0">
+      <x:c r="A365">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B365" s="2">
+        <x:v>46153.3441782407</x:v>
+      </x:c>
+      <x:c r="C365" s="2">
+        <x:v>46153.3449768518</x:v>
+      </x:c>
+      <x:c r="D365" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E365" s="10" t="s"/>
+      <x:c r="F365" s="2"/>
+      <x:c r="G365" s="10" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="H365" s="10" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="I365" s="10" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="J365" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K365" s="10" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="L365" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M365" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R0ca2662babf64034"/>
+    <x:tablePart r:id="R896fce2e14864f3e"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096F5A18ADBDD9E4D8F394AC4B3466405" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e59e3e6d23932d1d7525b22f7d7f3a7d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" xmlns:ns3="76b4ec34-0f89-435f-928a-b7c414764614" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d88756df8cabe05f154bf6d416a348" ns2:_="" ns3:_="">
+    <xsd:import namespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb"/>
+    <xsd:import namespace="76b4ec34-0f89-435f-928a-b7c414764614"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ad0b2da7-f7f1-4ade-bc4d-78491eef27d0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="76b4ec34-0f89-435f-928a-b7c414764614" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c696ee1e-5302-4bbd-96b7-dbc90bffde0f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="76b4ec34-0f89-435f-928a-b7c414764614">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="76b4ec34-0f89-435f-928a-b7c414764614" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03025063-43EE-46EA-B058-1A56C00E8E1C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48999026-CC5C-4ADE-A2CD-50E8FBA01F8F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ADCBE58-5E06-4FFA-8EF5-175382303B25}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="1203">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="1376">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -3634,6 +3634,525 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">For data management purpose</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rosen Kazakov</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">rosen.kazakov@huvepharma.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Asressa Alemu Yeneneh</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">yeneasa@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ethiopia (Amhara region)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">One health</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sikesh Manandhar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">disezcksh@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Everest</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Suhel KC</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">suhel.kc@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Shubham Narwal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">shubhamnarwal0@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vetmath</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aliou khoule</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">alioukhoule2@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Senegal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">khoule</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Relebogile</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">relebogiletholwana@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BoarVision</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lucia Reguillo </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vetsapiensconsultoria@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vetsapiens </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Professional;phD;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr Elijah Kolawole Oladipo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">koladipo2k3@yahoo.co.uk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Helix Biogen Team </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Taiwo Fatodu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">fatoduolawande@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Stephen Obol Opiyo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">so13839@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">United State of America </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Orange-Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Peace Proscovia Aber</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">peaceaber@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Magma</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Data Scientist;Professional;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Redie Kidane Ghebrehawariat </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">rediehac1983@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sujan Rana</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sujanrana@yahoo.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Neelam Suwal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ssuwalneelam@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Public health professional;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Manuel Ruiz-Aravena</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">m.ruiz.aravena@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Andes Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">An-Chu Yang</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">yangvetlab@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr Genet Bezie Mengistu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">beziegenet9@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ethiopia /Amhara region </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Individually not have group</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Thierry EYNEM </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AxisVet</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Gizachew GelawvAyalew</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">gizachewgelaw94@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agventure</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Jestina Venance Katandukila </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jestina.katandukila2@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tanzania, East Africa</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Animal Health Scientist;Researcher;Academic Supervisor ;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aleksandar Trajchovski</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">aleksandar.trajchovski@fvm.ukim.edu.mk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">North Macedonia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal Health Scientist;Graduate Student;Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AxisChad Solution</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Giulia Bitti</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">giubitti@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vectors</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Patrícia Isabel Martins Branco</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">patriciabranco_12@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Portugal </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ubuntu </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Faye Al-Nakeeb</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">fayeal-nakeeb@worldhorsewelfare.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">England</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">World Horse Welfare</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Budina Eka Prasetia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">budinaeka@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">indonesia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">indoepivet</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Elena Yana</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">suarez.tania@pucp.pe</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Peru</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yana1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yana2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yana3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Taiwo Olawande Fatodu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dabo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Igor Markovic</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">igor.markovic@ivbis.at</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Austria</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ivbis</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rafael Romero Nicolino</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">rafael.nicolino@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brazil - South America</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Center for Epidemiology, Statistics, and Public Health (NEEST/UFMG)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Animal Health Scientist;Specialist in Applied Statistics;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Érica Lorenza Martins Araújo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ericalmaraujo@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Maria Eduarda Lourenço Martins</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">marialourenco.aluno@unipampa.edu.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brazil </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ana Luisa Martins Brum</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">analuisambrum@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Marcelo Teixeira Paiva</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">marcelo_thelin@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Gabriel Phua Junrong</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">gabrielphua@live.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Singapore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GSplot</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Shannon Kwok En Yi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">shannonkwok24@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Isadora Martins Pinto Coelho</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">isadorac@iastate.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graduate Student;Data Scientist;Animal Health Scientist;Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Belén Antonia Pinto Yañez</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">belen.pinto@uchile.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Science FAVET</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sebastián Elías Zavala Marín</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sebastian.zavala@uchile.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Scientist;Professional;Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aldo Eugenio Maddaleno Toledo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">amaddaleno@veterinaria.uchile.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Norma Rocio Forero Munoz </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Canada - Ontario</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Panthera onca</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">JESUS DAVID FORERO MUÑOZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">davidforero@mi.unc.edu.ar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">COLOMBIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Juan D. Umaña-Caro</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jd.umana10@uniandes.edu.co</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Olufunbi Olaoye </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">olaoyeolufunbi@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Team Nature</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Gabriel David Pinilla Monsalve</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">gd.pinilla@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nephtalie THELIUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">theliusnephtalie@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graduate Student;Animal Science Specialist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Grace Amole</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graceamole30@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Netherlands </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zoha Khan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">zoha.khan30@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graduate Student;Researcher;Infectious Disease and One Health Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Keval Mehta</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">kevalvmehta@proton.me</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">kaecore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Frantz JEAN BAPTISTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Frantzj043@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Taimour Taj Shami</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">taimour.shami@sysreformsint.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Team SysReforms</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Marat Beksultanov</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">maratb@precisionagro.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">USA and Kazakhstan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgriTech Hub</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Scientist;Professional;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rabina Prajapati</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vetrabinaprajapati7@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lydia Ghozlane</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ghozlanelydia@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zoodomena</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graduate Student;Data Scientist;Researcher;Animal Health Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Alejandro Zaldivar Gomez</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">alejandro.zaldivar.i@senasica.gob.mx</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The SEIRious Data</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3730,8 +4249,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M365" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M365"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M426" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M426"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -17569,11 +18088,2266 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="366" hidden="0">
+      <x:c r="A366">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B366" s="2">
+        <x:v>46153.4631365741</x:v>
+      </x:c>
+      <x:c r="C366" s="2">
+        <x:v>46153.4658564815</x:v>
+      </x:c>
+      <x:c r="D366" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E366" s="10" t="s"/>
+      <x:c r="F366" s="2"/>
+      <x:c r="G366" s="10" t="s">
+        <x:v>1203</x:v>
+      </x:c>
+      <x:c r="H366" s="10" t="s">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="I366" s="10" t="s"/>
+      <x:c r="J366" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K366" s="10" t="s">
+        <x:v>1205</x:v>
+      </x:c>
+      <x:c r="L366" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M366" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" hidden="0">
+      <x:c r="A367">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="B367" s="2">
+        <x:v>46153.4766666667</x:v>
+      </x:c>
+      <x:c r="C367" s="2">
+        <x:v>46153.4819444444</x:v>
+      </x:c>
+      <x:c r="D367" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E367" s="10" t="s"/>
+      <x:c r="F367" s="2"/>
+      <x:c r="G367" s="10" t="s">
+        <x:v>1206</x:v>
+      </x:c>
+      <x:c r="H367" s="10" t="s">
+        <x:v>1207</x:v>
+      </x:c>
+      <x:c r="I367" s="10" t="s">
+        <x:v>1208</x:v>
+      </x:c>
+      <x:c r="J367" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K367" s="10" t="s">
+        <x:v>1209</x:v>
+      </x:c>
+      <x:c r="L367" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M367" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" hidden="0">
+      <x:c r="A368">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="B368" s="2">
+        <x:v>46153.5897337963</x:v>
+      </x:c>
+      <x:c r="C368" s="2">
+        <x:v>46153.6199537037</x:v>
+      </x:c>
+      <x:c r="D368" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E368" s="10" t="s"/>
+      <x:c r="F368" s="2"/>
+      <x:c r="G368" s="10" t="s">
+        <x:v>1210</x:v>
+      </x:c>
+      <x:c r="H368" s="10" t="s">
+        <x:v>1211</x:v>
+      </x:c>
+      <x:c r="I368" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="J368" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K368" s="10" t="s">
+        <x:v>1212</x:v>
+      </x:c>
+      <x:c r="L368" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M368" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" hidden="0">
+      <x:c r="A369">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B369" s="2">
+        <x:v>46153.6200231481</x:v>
+      </x:c>
+      <x:c r="C369" s="2">
+        <x:v>46153.6204513889</x:v>
+      </x:c>
+      <x:c r="D369" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E369" s="10" t="s"/>
+      <x:c r="F369" s="2"/>
+      <x:c r="G369" s="10" t="s">
+        <x:v>1213</x:v>
+      </x:c>
+      <x:c r="H369" s="10" t="s">
+        <x:v>1214</x:v>
+      </x:c>
+      <x:c r="I369" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="J369" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K369" s="10" t="s">
+        <x:v>1212</x:v>
+      </x:c>
+      <x:c r="L369" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M369" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" hidden="0">
+      <x:c r="A370">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="B370" s="2">
+        <x:v>46153.7584722222</x:v>
+      </x:c>
+      <x:c r="C370" s="2">
+        <x:v>46153.7590162037</x:v>
+      </x:c>
+      <x:c r="D370" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E370" s="10" t="s"/>
+      <x:c r="F370" s="2"/>
+      <x:c r="G370" s="10" t="s">
+        <x:v>1215</x:v>
+      </x:c>
+      <x:c r="H370" s="10" t="s">
+        <x:v>1216</x:v>
+      </x:c>
+      <x:c r="I370" s="10" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="J370" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K370" s="10" t="s">
+        <x:v>1217</x:v>
+      </x:c>
+      <x:c r="L370" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M370" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" hidden="0">
+      <x:c r="A371">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B371" s="2">
+        <x:v>46153.8253472222</x:v>
+      </x:c>
+      <x:c r="C371" s="2">
+        <x:v>46153.8266435185</x:v>
+      </x:c>
+      <x:c r="D371" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E371" s="10" t="s"/>
+      <x:c r="F371" s="2"/>
+      <x:c r="G371" s="10" t="s">
+        <x:v>1218</x:v>
+      </x:c>
+      <x:c r="H371" s="10" t="s">
+        <x:v>1219</x:v>
+      </x:c>
+      <x:c r="I371" s="10" t="s">
+        <x:v>1220</x:v>
+      </x:c>
+      <x:c r="J371" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K371" s="10" t="s">
+        <x:v>1221</x:v>
+      </x:c>
+      <x:c r="L371" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M371" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" hidden="0">
+      <x:c r="A372">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="B372" s="2">
+        <x:v>46154.3471643518</x:v>
+      </x:c>
+      <x:c r="C372" s="2">
+        <x:v>46154.3487384259</x:v>
+      </x:c>
+      <x:c r="D372" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E372" s="10" t="s"/>
+      <x:c r="F372" s="2"/>
+      <x:c r="G372" s="10" t="s">
+        <x:v>1222</x:v>
+      </x:c>
+      <x:c r="H372" s="10" t="s">
+        <x:v>1223</x:v>
+      </x:c>
+      <x:c r="I372" s="10" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="J372" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K372" s="10" t="s">
+        <x:v>1224</x:v>
+      </x:c>
+      <x:c r="L372" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M372" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" hidden="0">
+      <x:c r="A373">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B373" s="2">
+        <x:v>46154.4027893519</x:v>
+      </x:c>
+      <x:c r="C373" s="2">
+        <x:v>46154.4038194444</x:v>
+      </x:c>
+      <x:c r="D373" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E373" s="10" t="s"/>
+      <x:c r="F373" s="2"/>
+      <x:c r="G373" s="10" t="s">
+        <x:v>1225</x:v>
+      </x:c>
+      <x:c r="H373" s="10" t="s">
+        <x:v>1226</x:v>
+      </x:c>
+      <x:c r="I373" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J373" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K373" s="10" t="s">
+        <x:v>1227</x:v>
+      </x:c>
+      <x:c r="L373" s="10" t="s">
+        <x:v>1228</x:v>
+      </x:c>
+      <x:c r="M373" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" hidden="0">
+      <x:c r="A374">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="B374" s="2">
+        <x:v>46154.6558912037</x:v>
+      </x:c>
+      <x:c r="C374" s="2">
+        <x:v>46154.6602662037</x:v>
+      </x:c>
+      <x:c r="D374" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E374" s="10" t="s"/>
+      <x:c r="F374" s="2"/>
+      <x:c r="G374" s="10" t="s">
+        <x:v>1229</x:v>
+      </x:c>
+      <x:c r="H374" s="10" t="s">
+        <x:v>1230</x:v>
+      </x:c>
+      <x:c r="I374" s="10" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J374" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K374" s="10" t="s">
+        <x:v>1231</x:v>
+      </x:c>
+      <x:c r="L374" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M374" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" hidden="0">
+      <x:c r="A375">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="B375" s="2">
+        <x:v>46154.6733217593</x:v>
+      </x:c>
+      <x:c r="C375" s="2">
+        <x:v>46154.6760185185</x:v>
+      </x:c>
+      <x:c r="D375" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E375" s="10" t="s"/>
+      <x:c r="F375" s="2"/>
+      <x:c r="G375" s="10" t="s">
+        <x:v>1232</x:v>
+      </x:c>
+      <x:c r="H375" s="10" t="s">
+        <x:v>1233</x:v>
+      </x:c>
+      <x:c r="I375" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J375" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K375" s="10" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="L375" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M375" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" hidden="0">
+      <x:c r="A376">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="B376" s="2">
+        <x:v>46154.6788657407</x:v>
+      </x:c>
+      <x:c r="C376" s="2">
+        <x:v>46154.6820717593</x:v>
+      </x:c>
+      <x:c r="D376" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E376" s="10" t="s"/>
+      <x:c r="F376" s="2"/>
+      <x:c r="G376" s="10" t="s">
+        <x:v>1234</x:v>
+      </x:c>
+      <x:c r="H376" s="10" t="s">
+        <x:v>1235</x:v>
+      </x:c>
+      <x:c r="I376" s="10" t="s">
+        <x:v>1236</x:v>
+      </x:c>
+      <x:c r="J376" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K376" s="10" t="s">
+        <x:v>1237</x:v>
+      </x:c>
+      <x:c r="L376" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M376" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" hidden="0">
+      <x:c r="A377">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="B377" s="2">
+        <x:v>46154.6825231481</x:v>
+      </x:c>
+      <x:c r="C377" s="2">
+        <x:v>46154.6845486111</x:v>
+      </x:c>
+      <x:c r="D377" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E377" s="10" t="s"/>
+      <x:c r="F377" s="2"/>
+      <x:c r="G377" s="10" t="s">
+        <x:v>1238</x:v>
+      </x:c>
+      <x:c r="H377" s="10" t="s">
+        <x:v>1239</x:v>
+      </x:c>
+      <x:c r="I377" s="10" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="J377" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K377" s="10" t="s">
+        <x:v>1240</x:v>
+      </x:c>
+      <x:c r="L377" s="10" t="s">
+        <x:v>1241</x:v>
+      </x:c>
+      <x:c r="M377" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" hidden="0">
+      <x:c r="A378">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="B378" s="2">
+        <x:v>46154.6984606481</x:v>
+      </x:c>
+      <x:c r="C378" s="2">
+        <x:v>46154.7020138889</x:v>
+      </x:c>
+      <x:c r="D378" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E378" s="10" t="s"/>
+      <x:c r="F378" s="2"/>
+      <x:c r="G378" s="10" t="s">
+        <x:v>1242</x:v>
+      </x:c>
+      <x:c r="H378" s="10" t="s">
+        <x:v>1243</x:v>
+      </x:c>
+      <x:c r="I378" s="10" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="J378" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K378" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L378" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M378" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" hidden="0">
+      <x:c r="A379">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="B379" s="2">
+        <x:v>46154.8883912037</x:v>
+      </x:c>
+      <x:c r="C379" s="2">
+        <x:v>46154.8889583333</x:v>
+      </x:c>
+      <x:c r="D379" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E379" s="10" t="s"/>
+      <x:c r="F379" s="2"/>
+      <x:c r="G379" s="10" t="s">
+        <x:v>1244</x:v>
+      </x:c>
+      <x:c r="H379" s="10" t="s">
+        <x:v>1245</x:v>
+      </x:c>
+      <x:c r="I379" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="J379" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K379" s="10" t="s">
+        <x:v>1212</x:v>
+      </x:c>
+      <x:c r="L379" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M379" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" hidden="0">
+      <x:c r="A380">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="B380" s="2">
+        <x:v>46155.2317708333</x:v>
+      </x:c>
+      <x:c r="C380" s="2">
+        <x:v>46155.2344328704</x:v>
+      </x:c>
+      <x:c r="D380" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E380" s="10" t="s"/>
+      <x:c r="F380" s="2"/>
+      <x:c r="G380" s="10" t="s">
+        <x:v>1246</x:v>
+      </x:c>
+      <x:c r="H380" s="10" t="s">
+        <x:v>1247</x:v>
+      </x:c>
+      <x:c r="I380" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="J380" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K380" s="7" t="s">
+        <x:v>1248</x:v>
+      </x:c>
+      <x:c r="L380" s="10" t="s">
+        <x:v>1249</x:v>
+      </x:c>
+      <x:c r="M380" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" hidden="0">
+      <x:c r="A381">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B381" s="2">
+        <x:v>46155.3072337963</x:v>
+      </x:c>
+      <x:c r="C381" s="2">
+        <x:v>46155.3085416667</x:v>
+      </x:c>
+      <x:c r="D381" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E381" s="10" t="s"/>
+      <x:c r="F381" s="2"/>
+      <x:c r="G381" s="10" t="s">
+        <x:v>1250</x:v>
+      </x:c>
+      <x:c r="H381" s="10" t="s">
+        <x:v>1251</x:v>
+      </x:c>
+      <x:c r="I381" s="10" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="J381" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K381" s="10" t="s">
+        <x:v>1252</x:v>
+      </x:c>
+      <x:c r="L381" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M381" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" hidden="0">
+      <x:c r="A382">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="B382" s="2">
+        <x:v>46155.4661458333</x:v>
+      </x:c>
+      <x:c r="C382" s="2">
+        <x:v>46155.4747106481</x:v>
+      </x:c>
+      <x:c r="D382" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E382" s="10" t="s"/>
+      <x:c r="F382" s="2"/>
+      <x:c r="G382" s="10" t="s">
+        <x:v>1253</x:v>
+      </x:c>
+      <x:c r="H382" s="10" t="s">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="I382" s="10" t="s">
+        <x:v>1070</x:v>
+      </x:c>
+      <x:c r="J382" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K382" s="10" t="s">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c r="L382" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M382" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" hidden="0">
+      <x:c r="A383">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B383" s="2">
+        <x:v>46155.6137268519</x:v>
+      </x:c>
+      <x:c r="C383" s="2">
+        <x:v>46155.6189351852</x:v>
+      </x:c>
+      <x:c r="D383" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E383" s="10" t="s"/>
+      <x:c r="F383" s="2"/>
+      <x:c r="G383" s="10" t="s">
+        <x:v>1255</x:v>
+      </x:c>
+      <x:c r="H383" s="10" t="s">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I383" s="10" t="s">
+        <x:v>1257</x:v>
+      </x:c>
+      <x:c r="J383" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K383" s="10" t="s">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="L383" s="10" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="M383" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" hidden="0">
+      <x:c r="A384">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="B384" s="2">
+        <x:v>46155.7172800926</x:v>
+      </x:c>
+      <x:c r="C384" s="2">
+        <x:v>46155.7196759259</x:v>
+      </x:c>
+      <x:c r="D384" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E384" s="10" t="s"/>
+      <x:c r="F384" s="2"/>
+      <x:c r="G384" s="10" t="s">
+        <x:v>1259</x:v>
+      </x:c>
+      <x:c r="H384" s="10" t="s">
+        <x:v>1076</x:v>
+      </x:c>
+      <x:c r="I384" s="10" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J384" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K384" s="10" t="s">
+        <x:v>1260</x:v>
+      </x:c>
+      <x:c r="L384" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M384" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" hidden="0">
+      <x:c r="A385">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B385" s="2">
+        <x:v>46155.7958680556</x:v>
+      </x:c>
+      <x:c r="C385" s="2">
+        <x:v>46155.7975231481</x:v>
+      </x:c>
+      <x:c r="D385" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E385" s="10" t="s"/>
+      <x:c r="F385" s="2"/>
+      <x:c r="G385" s="10" t="s">
+        <x:v>1261</x:v>
+      </x:c>
+      <x:c r="H385" s="10" t="s">
+        <x:v>1262</x:v>
+      </x:c>
+      <x:c r="I385" s="10" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J385" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K385" s="10" t="s">
+        <x:v>1263</x:v>
+      </x:c>
+      <x:c r="L385" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M385" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" hidden="0">
+      <x:c r="A386">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B386" s="2">
+        <x:v>46155.8303935185</x:v>
+      </x:c>
+      <x:c r="C386" s="2">
+        <x:v>46155.853275463</x:v>
+      </x:c>
+      <x:c r="D386" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E386" s="10" t="s"/>
+      <x:c r="F386" s="2"/>
+      <x:c r="G386" s="10" t="s">
+        <x:v>1264</x:v>
+      </x:c>
+      <x:c r="H386" s="10" t="s">
+        <x:v>1265</x:v>
+      </x:c>
+      <x:c r="I386" s="10" t="s">
+        <x:v>1266</x:v>
+      </x:c>
+      <x:c r="J386" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K386" s="10" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L386" s="10" t="s">
+        <x:v>1267</x:v>
+      </x:c>
+      <x:c r="M386" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" hidden="0">
+      <x:c r="A387">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B387" s="2">
+        <x:v>46155.9306712963</x:v>
+      </x:c>
+      <x:c r="C387" s="2">
+        <x:v>46155.932662037</x:v>
+      </x:c>
+      <x:c r="D387" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E387" s="10" t="s"/>
+      <x:c r="F387" s="2"/>
+      <x:c r="G387" s="10" t="s">
+        <x:v>1268</x:v>
+      </x:c>
+      <x:c r="H387" s="10" t="s">
+        <x:v>1269</x:v>
+      </x:c>
+      <x:c r="I387" s="10" t="s">
+        <x:v>1270</x:v>
+      </x:c>
+      <x:c r="J387" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K387" s="10" t="s">
+        <x:v>1271</x:v>
+      </x:c>
+      <x:c r="L387" s="10" t="s">
+        <x:v>1272</x:v>
+      </x:c>
+      <x:c r="M387" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" hidden="0">
+      <x:c r="A388">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="B388" s="2">
+        <x:v>46156.2994560185</x:v>
+      </x:c>
+      <x:c r="C388" s="2">
+        <x:v>46156.3044560185</x:v>
+      </x:c>
+      <x:c r="D388" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E388" s="10" t="s"/>
+      <x:c r="F388" s="2"/>
+      <x:c r="G388" s="10" t="s">
+        <x:v>1259</x:v>
+      </x:c>
+      <x:c r="H388" s="10" t="s">
+        <x:v>1076</x:v>
+      </x:c>
+      <x:c r="I388" s="10" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J388" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K388" s="10" t="s">
+        <x:v>1273</x:v>
+      </x:c>
+      <x:c r="L388" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M388" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" hidden="0">
+      <x:c r="A389">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B389" s="2">
+        <x:v>46156.3195486111</x:v>
+      </x:c>
+      <x:c r="C389" s="2">
+        <x:v>46156.3241435185</x:v>
+      </x:c>
+      <x:c r="D389" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E389" s="10" t="s"/>
+      <x:c r="F389" s="2"/>
+      <x:c r="G389" s="10" t="s">
+        <x:v>1274</x:v>
+      </x:c>
+      <x:c r="H389" s="10" t="s">
+        <x:v>1275</x:v>
+      </x:c>
+      <x:c r="I389" s="10" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="J389" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K389" s="10" t="s">
+        <x:v>1276</x:v>
+      </x:c>
+      <x:c r="L389" s="10" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="M389" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" hidden="0">
+      <x:c r="A390">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B390" s="2">
+        <x:v>46156.5274074074</x:v>
+      </x:c>
+      <x:c r="C390" s="2">
+        <x:v>46156.5285069444</x:v>
+      </x:c>
+      <x:c r="D390" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E390" s="10" t="s"/>
+      <x:c r="F390" s="2"/>
+      <x:c r="G390" s="10" t="s">
+        <x:v>1277</x:v>
+      </x:c>
+      <x:c r="H390" s="10" t="s">
+        <x:v>1278</x:v>
+      </x:c>
+      <x:c r="I390" s="10" t="s">
+        <x:v>1279</x:v>
+      </x:c>
+      <x:c r="J390" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K390" s="10" t="s">
+        <x:v>1280</x:v>
+      </x:c>
+      <x:c r="L390" s="10" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="M390" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" hidden="0">
+      <x:c r="A391">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="B391" s="2">
+        <x:v>46156.5554861111</x:v>
+      </x:c>
+      <x:c r="C391" s="2">
+        <x:v>46156.5559837963</x:v>
+      </x:c>
+      <x:c r="D391" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E391" s="10" t="s"/>
+      <x:c r="F391" s="2"/>
+      <x:c r="G391" s="10" t="s">
+        <x:v>1281</x:v>
+      </x:c>
+      <x:c r="H391" s="10" t="s">
+        <x:v>1282</x:v>
+      </x:c>
+      <x:c r="I391" s="10" t="s">
+        <x:v>1283</x:v>
+      </x:c>
+      <x:c r="J391" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K391" s="10" t="s">
+        <x:v>1284</x:v>
+      </x:c>
+      <x:c r="L391" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M391" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" hidden="0">
+      <x:c r="A392">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B392" s="2">
+        <x:v>46156.6545601852</x:v>
+      </x:c>
+      <x:c r="C392" s="2">
+        <x:v>46156.6560185185</x:v>
+      </x:c>
+      <x:c r="D392" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E392" s="10" t="s"/>
+      <x:c r="F392" s="2"/>
+      <x:c r="G392" s="10" t="s">
+        <x:v>1285</x:v>
+      </x:c>
+      <x:c r="H392" s="10" t="s">
+        <x:v>1286</x:v>
+      </x:c>
+      <x:c r="I392" s="10" t="s">
+        <x:v>1287</x:v>
+      </x:c>
+      <x:c r="J392" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K392" s="10" t="s">
+        <x:v>1288</x:v>
+      </x:c>
+      <x:c r="L392" s="10" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M392" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" hidden="0">
+      <x:c r="A393">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B393" s="2">
+        <x:v>46156.8453935185</x:v>
+      </x:c>
+      <x:c r="C393" s="2">
+        <x:v>46156.8515277778</x:v>
+      </x:c>
+      <x:c r="D393" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E393" s="10" t="s"/>
+      <x:c r="F393" s="2"/>
+      <x:c r="G393" s="10" t="s">
+        <x:v>1289</x:v>
+      </x:c>
+      <x:c r="H393" s="10" t="s">
+        <x:v>1290</x:v>
+      </x:c>
+      <x:c r="I393" s="10" t="s">
+        <x:v>1291</x:v>
+      </x:c>
+      <x:c r="J393" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K393" s="10" t="s">
+        <x:v>1292</x:v>
+      </x:c>
+      <x:c r="L393" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M393" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" hidden="0">
+      <x:c r="A394">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="B394" s="2">
+        <x:v>46156.8515509259</x:v>
+      </x:c>
+      <x:c r="C394" s="2">
+        <x:v>46156.8519097222</x:v>
+      </x:c>
+      <x:c r="D394" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E394" s="10" t="s"/>
+      <x:c r="F394" s="2"/>
+      <x:c r="G394" s="10" t="s">
+        <x:v>1289</x:v>
+      </x:c>
+      <x:c r="H394" s="10" t="s">
+        <x:v>1290</x:v>
+      </x:c>
+      <x:c r="I394" s="10" t="s">
+        <x:v>1291</x:v>
+      </x:c>
+      <x:c r="J394" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K394" s="10" t="s">
+        <x:v>1292</x:v>
+      </x:c>
+      <x:c r="L394" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M394" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" hidden="0">
+      <x:c r="A395">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B395" s="2">
+        <x:v>46156.8519907407</x:v>
+      </x:c>
+      <x:c r="C395" s="2">
+        <x:v>46156.8524421296</x:v>
+      </x:c>
+      <x:c r="D395" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E395" s="10" t="s"/>
+      <x:c r="F395" s="2"/>
+      <x:c r="G395" s="10" t="s">
+        <x:v>1289</x:v>
+      </x:c>
+      <x:c r="H395" s="10" t="s">
+        <x:v>1290</x:v>
+      </x:c>
+      <x:c r="I395" s="10" t="s">
+        <x:v>1291</x:v>
+      </x:c>
+      <x:c r="J395" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K395" s="10" t="s">
+        <x:v>1293</x:v>
+      </x:c>
+      <x:c r="L395" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M395" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" hidden="0">
+      <x:c r="A396">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="B396" s="2">
+        <x:v>46156.854224537</x:v>
+      </x:c>
+      <x:c r="C396" s="2">
+        <x:v>46156.8545717593</x:v>
+      </x:c>
+      <x:c r="D396" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E396" s="10" t="s"/>
+      <x:c r="F396" s="2"/>
+      <x:c r="G396" s="10" t="s">
+        <x:v>1289</x:v>
+      </x:c>
+      <x:c r="H396" s="10" t="s">
+        <x:v>1290</x:v>
+      </x:c>
+      <x:c r="I396" s="10" t="s">
+        <x:v>1291</x:v>
+      </x:c>
+      <x:c r="J396" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K396" s="10" t="s">
+        <x:v>1294</x:v>
+      </x:c>
+      <x:c r="L396" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M396" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" hidden="0">
+      <x:c r="A397">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B397" s="2">
+        <x:v>46157.1135185185</x:v>
+      </x:c>
+      <x:c r="C397" s="2">
+        <x:v>46157.1151388889</x:v>
+      </x:c>
+      <x:c r="D397" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E397" s="10" t="s"/>
+      <x:c r="F397" s="2"/>
+      <x:c r="G397" s="10" t="s">
+        <x:v>1295</x:v>
+      </x:c>
+      <x:c r="H397" s="10" t="s">
+        <x:v>1233</x:v>
+      </x:c>
+      <x:c r="I397" s="10" t="s">
+        <x:v>1283</x:v>
+      </x:c>
+      <x:c r="J397" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K397" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L397" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M397" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" hidden="0">
+      <x:c r="A398">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="B398" s="2">
+        <x:v>46157.4966203704</x:v>
+      </x:c>
+      <x:c r="C398" s="2">
+        <x:v>46157.4975694444</x:v>
+      </x:c>
+      <x:c r="D398" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E398" s="10" t="s"/>
+      <x:c r="F398" s="2"/>
+      <x:c r="G398" s="10" t="s">
+        <x:v>788</x:v>
+      </x:c>
+      <x:c r="H398" s="10" t="s">
+        <x:v>789</x:v>
+      </x:c>
+      <x:c r="I398" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J398" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K398" s="10" t="s">
+        <x:v>1296</x:v>
+      </x:c>
+      <x:c r="L398" s="10" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="M398" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" hidden="0">
+      <x:c r="A399">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B399" s="2">
+        <x:v>46157.5577083333</x:v>
+      </x:c>
+      <x:c r="C399" s="2">
+        <x:v>46157.5585416667</x:v>
+      </x:c>
+      <x:c r="D399" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E399" s="10" t="s"/>
+      <x:c r="F399" s="2"/>
+      <x:c r="G399" s="10" t="s">
+        <x:v>1297</x:v>
+      </x:c>
+      <x:c r="H399" s="10" t="s">
+        <x:v>1298</x:v>
+      </x:c>
+      <x:c r="I399" s="10" t="s">
+        <x:v>1299</x:v>
+      </x:c>
+      <x:c r="J399" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K399" s="10" t="s">
+        <x:v>1300</x:v>
+      </x:c>
+      <x:c r="L399" s="10" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="M399" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" hidden="0">
+      <x:c r="A400">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="B400" s="2">
+        <x:v>46157.5788773148</x:v>
+      </x:c>
+      <x:c r="C400" s="2">
+        <x:v>46157.5819444444</x:v>
+      </x:c>
+      <x:c r="D400" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E400" s="10" t="s"/>
+      <x:c r="F400" s="2"/>
+      <x:c r="G400" s="10" t="s">
+        <x:v>1301</x:v>
+      </x:c>
+      <x:c r="H400" s="10" t="s">
+        <x:v>1302</x:v>
+      </x:c>
+      <x:c r="I400" s="10" t="s">
+        <x:v>1303</x:v>
+      </x:c>
+      <x:c r="J400" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K400" s="10" t="s">
+        <x:v>1304</x:v>
+      </x:c>
+      <x:c r="L400" s="10" t="s">
+        <x:v>1305</x:v>
+      </x:c>
+      <x:c r="M400" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" hidden="0">
+      <x:c r="A401">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B401" s="2">
+        <x:v>46157.5769444444</x:v>
+      </x:c>
+      <x:c r="C401" s="2">
+        <x:v>46157.5825</x:v>
+      </x:c>
+      <x:c r="D401" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E401" s="10" t="s"/>
+      <x:c r="F401" s="2"/>
+      <x:c r="G401" s="10" t="s">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="H401" s="10" t="s">
+        <x:v>1307</x:v>
+      </x:c>
+      <x:c r="I401" s="10" t="s">
+        <x:v>1303</x:v>
+      </x:c>
+      <x:c r="J401" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K401" s="10" t="s">
+        <x:v>1304</x:v>
+      </x:c>
+      <x:c r="L401" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M401" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" hidden="0">
+      <x:c r="A402">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B402" s="2">
+        <x:v>46157.5850231481</x:v>
+      </x:c>
+      <x:c r="C402" s="2">
+        <x:v>46157.5860532407</x:v>
+      </x:c>
+      <x:c r="D402" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E402" s="10" t="s"/>
+      <x:c r="F402" s="2"/>
+      <x:c r="G402" s="10" t="s">
+        <x:v>1308</x:v>
+      </x:c>
+      <x:c r="H402" s="10" t="s">
+        <x:v>1309</x:v>
+      </x:c>
+      <x:c r="I402" s="10" t="s">
+        <x:v>1310</x:v>
+      </x:c>
+      <x:c r="J402" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K402" s="10" t="s">
+        <x:v>1304</x:v>
+      </x:c>
+      <x:c r="L402" s="10" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="M402" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" hidden="0">
+      <x:c r="A403">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="B403" s="2">
+        <x:v>46157.5899768519</x:v>
+      </x:c>
+      <x:c r="C403" s="2">
+        <x:v>46157.5941319444</x:v>
+      </x:c>
+      <x:c r="D403" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E403" s="10" t="s"/>
+      <x:c r="F403" s="2"/>
+      <x:c r="G403" s="10" t="s">
+        <x:v>1311</x:v>
+      </x:c>
+      <x:c r="H403" s="10" t="s">
+        <x:v>1312</x:v>
+      </x:c>
+      <x:c r="I403" s="10" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J403" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K403" s="10" t="s">
+        <x:v>1304</x:v>
+      </x:c>
+      <x:c r="L403" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M403" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" hidden="0">
+      <x:c r="A404">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B404" s="2">
+        <x:v>46157.6676388889</x:v>
+      </x:c>
+      <x:c r="C404" s="2">
+        <x:v>46157.6693402778</x:v>
+      </x:c>
+      <x:c r="D404" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E404" s="10" t="s"/>
+      <x:c r="F404" s="2"/>
+      <x:c r="G404" s="10" t="s">
+        <x:v>1313</x:v>
+      </x:c>
+      <x:c r="H404" s="10" t="s">
+        <x:v>1314</x:v>
+      </x:c>
+      <x:c r="I404" s="10" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J404" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K404" s="10" t="s">
+        <x:v>1304</x:v>
+      </x:c>
+      <x:c r="L404" s="10" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="M404" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" hidden="0">
+      <x:c r="A405">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B405" s="2">
+        <x:v>46157.6806134259</x:v>
+      </x:c>
+      <x:c r="C405" s="2">
+        <x:v>46157.6824421296</x:v>
+      </x:c>
+      <x:c r="D405" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E405" s="10" t="s"/>
+      <x:c r="F405" s="2"/>
+      <x:c r="G405" s="10" t="s">
+        <x:v>1315</x:v>
+      </x:c>
+      <x:c r="H405" s="10" t="s">
+        <x:v>1316</x:v>
+      </x:c>
+      <x:c r="I405" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J405" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K405" s="10" t="s">
+        <x:v>1318</x:v>
+      </x:c>
+      <x:c r="L405" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M405" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" hidden="0">
+      <x:c r="A406">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B406" s="2">
+        <x:v>46157.6824768518</x:v>
+      </x:c>
+      <x:c r="C406" s="2">
+        <x:v>46157.6830671296</x:v>
+      </x:c>
+      <x:c r="D406" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E406" s="10" t="s"/>
+      <x:c r="F406" s="2"/>
+      <x:c r="G406" s="10" t="s">
+        <x:v>1319</x:v>
+      </x:c>
+      <x:c r="H406" s="10" t="s">
+        <x:v>1320</x:v>
+      </x:c>
+      <x:c r="I406" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J406" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K406" s="10" t="s">
+        <x:v>1318</x:v>
+      </x:c>
+      <x:c r="L406" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M406" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" hidden="0">
+      <x:c r="A407">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B407" s="2">
+        <x:v>46157.8667476852</x:v>
+      </x:c>
+      <x:c r="C407" s="2">
+        <x:v>46157.8671412037</x:v>
+      </x:c>
+      <x:c r="D407" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E407" s="10" t="s"/>
+      <x:c r="F407" s="2"/>
+      <x:c r="G407" s="10" t="s">
+        <x:v>1321</x:v>
+      </x:c>
+      <x:c r="H407" s="10" t="s">
+        <x:v>1322</x:v>
+      </x:c>
+      <x:c r="I407" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J407" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K407" s="10" t="s">
+        <x:v>1304</x:v>
+      </x:c>
+      <x:c r="L407" s="10" t="s">
+        <x:v>1323</x:v>
+      </x:c>
+      <x:c r="M407" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" hidden="0">
+      <x:c r="A408">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B408" s="2">
+        <x:v>46157.8905439815</x:v>
+      </x:c>
+      <x:c r="C408" s="2">
+        <x:v>46157.8919212963</x:v>
+      </x:c>
+      <x:c r="D408" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E408" s="10" t="s"/>
+      <x:c r="F408" s="2"/>
+      <x:c r="G408" s="10" t="s">
+        <x:v>1324</x:v>
+      </x:c>
+      <x:c r="H408" s="10" t="s">
+        <x:v>1325</x:v>
+      </x:c>
+      <x:c r="I408" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="J408" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K408" s="10" t="s">
+        <x:v>1326</x:v>
+      </x:c>
+      <x:c r="L408" s="10" t="s">
+        <x:v>1164</x:v>
+      </x:c>
+      <x:c r="M408" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" hidden="0">
+      <x:c r="A409">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B409" s="2">
+        <x:v>46157.8909953704</x:v>
+      </x:c>
+      <x:c r="C409" s="2">
+        <x:v>46157.8919791667</x:v>
+      </x:c>
+      <x:c r="D409" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E409" s="10" t="s"/>
+      <x:c r="F409" s="2"/>
+      <x:c r="G409" s="10" t="s">
+        <x:v>1327</x:v>
+      </x:c>
+      <x:c r="H409" s="10" t="s">
+        <x:v>1328</x:v>
+      </x:c>
+      <x:c r="I409" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="J409" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K409" s="10" t="s">
+        <x:v>1326</x:v>
+      </x:c>
+      <x:c r="L409" s="10" t="s">
+        <x:v>1329</x:v>
+      </x:c>
+      <x:c r="M409" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" hidden="0">
+      <x:c r="A410">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="B410" s="2">
+        <x:v>46157.8924305556</x:v>
+      </x:c>
+      <x:c r="C410" s="2">
+        <x:v>46157.8959953704</x:v>
+      </x:c>
+      <x:c r="D410" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E410" s="10" t="s"/>
+      <x:c r="F410" s="2"/>
+      <x:c r="G410" s="10" t="s">
+        <x:v>1330</x:v>
+      </x:c>
+      <x:c r="H410" s="10" t="s">
+        <x:v>1331</x:v>
+      </x:c>
+      <x:c r="I410" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="J410" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K410" s="10" t="s">
+        <x:v>1326</x:v>
+      </x:c>
+      <x:c r="L410" s="10" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="M410" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" hidden="0">
+      <x:c r="A411">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B411" s="2">
+        <x:v>46158.3896759259</x:v>
+      </x:c>
+      <x:c r="C411" s="2">
+        <x:v>46158.3987384259</x:v>
+      </x:c>
+      <x:c r="D411" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E411" s="10" t="s"/>
+      <x:c r="F411" s="2"/>
+      <x:c r="G411" s="10" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="H411" s="10" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="I411" s="10" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="J411" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K411" s="7" t="s">
+        <x:v>1248</x:v>
+      </x:c>
+      <x:c r="L411" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M411" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" hidden="0">
+      <x:c r="A412">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="B412" s="2">
+        <x:v>46158.6674652778</x:v>
+      </x:c>
+      <x:c r="C412" s="2">
+        <x:v>46158.6684027778</x:v>
+      </x:c>
+      <x:c r="D412" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E412" s="10" t="s"/>
+      <x:c r="F412" s="2"/>
+      <x:c r="G412" s="10" t="s">
+        <x:v>1332</x:v>
+      </x:c>
+      <x:c r="H412" s="10" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I412" s="10" t="s">
+        <x:v>1333</x:v>
+      </x:c>
+      <x:c r="J412" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K412" s="10" t="s">
+        <x:v>1334</x:v>
+      </x:c>
+      <x:c r="L412" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M412" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" hidden="0">
+      <x:c r="A413">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B413" s="2">
+        <x:v>46158.6733333333</x:v>
+      </x:c>
+      <x:c r="C413" s="2">
+        <x:v>46158.6742824074</x:v>
+      </x:c>
+      <x:c r="D413" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E413" s="10" t="s"/>
+      <x:c r="F413" s="2"/>
+      <x:c r="G413" s="10" t="s">
+        <x:v>1335</x:v>
+      </x:c>
+      <x:c r="H413" s="10" t="s">
+        <x:v>1336</x:v>
+      </x:c>
+      <x:c r="I413" s="10" t="s">
+        <x:v>1337</x:v>
+      </x:c>
+      <x:c r="J413" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K413" s="10" t="s">
+        <x:v>1334</x:v>
+      </x:c>
+      <x:c r="L413" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M413" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" hidden="0">
+      <x:c r="A414">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B414" s="2">
+        <x:v>46158.8112152778</x:v>
+      </x:c>
+      <x:c r="C414" s="2">
+        <x:v>46158.8117939815</x:v>
+      </x:c>
+      <x:c r="D414" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E414" s="10" t="s"/>
+      <x:c r="F414" s="2"/>
+      <x:c r="G414" s="10" t="s">
+        <x:v>1338</x:v>
+      </x:c>
+      <x:c r="H414" s="10" t="s">
+        <x:v>1339</x:v>
+      </x:c>
+      <x:c r="I414" s="10" t="s">
+        <x:v>881</x:v>
+      </x:c>
+      <x:c r="J414" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K414" s="10" t="s">
+        <x:v>1334</x:v>
+      </x:c>
+      <x:c r="L414" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M414" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" hidden="0">
+      <x:c r="A415">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="B415" s="2">
+        <x:v>46159.8166087963</x:v>
+      </x:c>
+      <x:c r="C415" s="2">
+        <x:v>46159.8177662037</x:v>
+      </x:c>
+      <x:c r="D415" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E415" s="10" t="s"/>
+      <x:c r="F415" s="2"/>
+      <x:c r="G415" s="10" t="s">
+        <x:v>1340</x:v>
+      </x:c>
+      <x:c r="H415" s="10" t="s">
+        <x:v>1341</x:v>
+      </x:c>
+      <x:c r="I415" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J415" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K415" s="10" t="s">
+        <x:v>1342</x:v>
+      </x:c>
+      <x:c r="L415" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M415" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" hidden="0">
+      <x:c r="A416">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B416" s="2">
+        <x:v>46159.9673148148</x:v>
+      </x:c>
+      <x:c r="C416" s="2">
+        <x:v>46159.9680439815</x:v>
+      </x:c>
+      <x:c r="D416" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E416" s="10" t="s"/>
+      <x:c r="F416" s="2"/>
+      <x:c r="G416" s="10" t="s">
+        <x:v>1343</x:v>
+      </x:c>
+      <x:c r="H416" s="10" t="s">
+        <x:v>1344</x:v>
+      </x:c>
+      <x:c r="I416" s="10" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J416" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K416" s="10" t="s">
+        <x:v>1334</x:v>
+      </x:c>
+      <x:c r="L416" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M416" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" hidden="0">
+      <x:c r="A417">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B417" s="2">
+        <x:v>46160.0342824074</x:v>
+      </x:c>
+      <x:c r="C417" s="2">
+        <x:v>46160.0393402778</x:v>
+      </x:c>
+      <x:c r="D417" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E417" s="10" t="s"/>
+      <x:c r="F417" s="2"/>
+      <x:c r="G417" s="10" t="s">
+        <x:v>1345</x:v>
+      </x:c>
+      <x:c r="H417" s="10" t="s">
+        <x:v>1346</x:v>
+      </x:c>
+      <x:c r="I417" s="10" t="s">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="J417" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K417" s="10" t="s">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="L417" s="10" t="s">
+        <x:v>1347</x:v>
+      </x:c>
+      <x:c r="M417" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" hidden="0">
+      <x:c r="A418">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="B418" s="2">
+        <x:v>46160.4171412037</x:v>
+      </x:c>
+      <x:c r="C418" s="2">
+        <x:v>46160.4176736111</x:v>
+      </x:c>
+      <x:c r="D418" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E418" s="10" t="s"/>
+      <x:c r="F418" s="2"/>
+      <x:c r="G418" s="10" t="s">
+        <x:v>1348</x:v>
+      </x:c>
+      <x:c r="H418" s="10" t="s">
+        <x:v>1349</x:v>
+      </x:c>
+      <x:c r="I418" s="10" t="s">
+        <x:v>1350</x:v>
+      </x:c>
+      <x:c r="J418" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K418" s="10" t="s">
+        <x:v>1342</x:v>
+      </x:c>
+      <x:c r="L418" s="10" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="M418" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" hidden="0">
+      <x:c r="A419">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B419" s="2">
+        <x:v>46160.7205555556</x:v>
+      </x:c>
+      <x:c r="C419" s="2">
+        <x:v>46160.7215625</x:v>
+      </x:c>
+      <x:c r="D419" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E419" s="10" t="s"/>
+      <x:c r="F419" s="2"/>
+      <x:c r="G419" s="10" t="s">
+        <x:v>1351</x:v>
+      </x:c>
+      <x:c r="H419" s="10" t="s">
+        <x:v>1352</x:v>
+      </x:c>
+      <x:c r="I419" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J419" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K419" s="10" t="s">
+        <x:v>1342</x:v>
+      </x:c>
+      <x:c r="L419" s="10" t="s">
+        <x:v>1353</x:v>
+      </x:c>
+      <x:c r="M419" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" hidden="0">
+      <x:c r="A420">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="B420" s="2">
+        <x:v>46160.8179398148</x:v>
+      </x:c>
+      <x:c r="C420" s="2">
+        <x:v>46160.8184027778</x:v>
+      </x:c>
+      <x:c r="D420" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E420" s="10" t="s"/>
+      <x:c r="F420" s="2"/>
+      <x:c r="G420" s="10" t="s">
+        <x:v>1354</x:v>
+      </x:c>
+      <x:c r="H420" s="10" t="s">
+        <x:v>1355</x:v>
+      </x:c>
+      <x:c r="I420" s="10" t="s">
+        <x:v>1142</x:v>
+      </x:c>
+      <x:c r="J420" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K420" s="10" t="s">
+        <x:v>1356</x:v>
+      </x:c>
+      <x:c r="L420" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M420" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" hidden="0">
+      <x:c r="A421">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B421" s="2">
+        <x:v>46161.2558333333</x:v>
+      </x:c>
+      <x:c r="C421" s="2">
+        <x:v>46161.259212963</x:v>
+      </x:c>
+      <x:c r="D421" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E421" s="10" t="s"/>
+      <x:c r="F421" s="2"/>
+      <x:c r="G421" s="10" t="s">
+        <x:v>1357</x:v>
+      </x:c>
+      <x:c r="H421" s="10" t="s">
+        <x:v>1358</x:v>
+      </x:c>
+      <x:c r="I421" s="10" t="s">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="J421" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K421" s="10" t="s">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="L421" s="10" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="M421" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" hidden="0">
+      <x:c r="A422">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B422" s="2">
+        <x:v>46161.4603240741</x:v>
+      </x:c>
+      <x:c r="C422" s="2">
+        <x:v>46161.4620601852</x:v>
+      </x:c>
+      <x:c r="D422" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E422" s="10" t="s"/>
+      <x:c r="F422" s="2"/>
+      <x:c r="G422" s="10" t="s">
+        <x:v>1359</x:v>
+      </x:c>
+      <x:c r="H422" s="10" t="s">
+        <x:v>1360</x:v>
+      </x:c>
+      <x:c r="I422" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J422" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K422" s="10" t="s">
+        <x:v>1361</x:v>
+      </x:c>
+      <x:c r="L422" s="10" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="M422" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" hidden="0">
+      <x:c r="A423">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="B423" s="2">
+        <x:v>46161.5612268519</x:v>
+      </x:c>
+      <x:c r="C423" s="2">
+        <x:v>46161.5619328704</x:v>
+      </x:c>
+      <x:c r="D423" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E423" s="10" t="s"/>
+      <x:c r="F423" s="2"/>
+      <x:c r="G423" s="10" t="s">
+        <x:v>1362</x:v>
+      </x:c>
+      <x:c r="H423" s="10" t="s">
+        <x:v>1363</x:v>
+      </x:c>
+      <x:c r="I423" s="10" t="s">
+        <x:v>1364</x:v>
+      </x:c>
+      <x:c r="J423" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K423" s="10" t="s">
+        <x:v>1365</x:v>
+      </x:c>
+      <x:c r="L423" s="10" t="s">
+        <x:v>1366</x:v>
+      </x:c>
+      <x:c r="M423" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" hidden="0">
+      <x:c r="A424">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B424" s="2">
+        <x:v>46161.6443518518</x:v>
+      </x:c>
+      <x:c r="C424" s="2">
+        <x:v>46161.6452546296</x:v>
+      </x:c>
+      <x:c r="D424" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E424" s="10" t="s"/>
+      <x:c r="F424" s="2"/>
+      <x:c r="G424" s="10" t="s">
+        <x:v>1367</x:v>
+      </x:c>
+      <x:c r="H424" s="10" t="s">
+        <x:v>1368</x:v>
+      </x:c>
+      <x:c r="I424" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="J424" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K424" s="10" t="s">
+        <x:v>1342</x:v>
+      </x:c>
+      <x:c r="L424" s="10" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="M424" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" hidden="0">
+      <x:c r="A425">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="B425" s="2">
+        <x:v>46161.6809259259</x:v>
+      </x:c>
+      <x:c r="C425" s="2">
+        <x:v>46161.7114699074</x:v>
+      </x:c>
+      <x:c r="D425" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E425" s="10" t="s"/>
+      <x:c r="F425" s="2"/>
+      <x:c r="G425" s="10" t="s">
+        <x:v>1369</x:v>
+      </x:c>
+      <x:c r="H425" s="10" t="s">
+        <x:v>1370</x:v>
+      </x:c>
+      <x:c r="I425" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J425" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K425" s="10" t="s">
+        <x:v>1371</x:v>
+      </x:c>
+      <x:c r="L425" s="10" t="s">
+        <x:v>1372</x:v>
+      </x:c>
+      <x:c r="M425" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" hidden="0">
+      <x:c r="A426">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="B426" s="2">
+        <x:v>46161.8663888889</x:v>
+      </x:c>
+      <x:c r="C426" s="2">
+        <x:v>46161.8713888889</x:v>
+      </x:c>
+      <x:c r="D426" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E426" s="10" t="s"/>
+      <x:c r="F426" s="2"/>
+      <x:c r="G426" s="10" t="s">
+        <x:v>1373</x:v>
+      </x:c>
+      <x:c r="H426" s="10" t="s">
+        <x:v>1374</x:v>
+      </x:c>
+      <x:c r="I426" s="10" t="s">
+        <x:v>976</x:v>
+      </x:c>
+      <x:c r="J426" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K426" s="10" t="s">
+        <x:v>1375</x:v>
+      </x:c>
+      <x:c r="L426" s="10" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="M426" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R896fce2e14864f3e"/>
+    <x:tablePart r:id="R963054c96e454490"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17860,13 +20634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03025063-43EE-46EA-B058-1A56C00E8E1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59FB3B1B-83DA-4E10-9156-44FB27A7D612}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48999026-CC5C-4ADE-A2CD-50E8FBA01F8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B0A0416-97E6-4DE8-8D69-50DD0FEF949C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ADCBE58-5E06-4FFA-8EF5-175382303B25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56DE6174-3C27-4D4D-986E-244D1816473C}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="1376">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="1403">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -4153,6 +4153,87 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">The SEIRious Data</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Salsabila Rashid</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">salsabilarashid8@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rabi Prajapati</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">cvile.last8@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Javier Tan Meng Wee</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">e1120971@u.nus.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">livelaughwildlife</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nurul Putri Fajriani</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">nur.put.f@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EpiEngine</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ewa Pacholewicz</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ewa.pacholewicz@wur.nl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WBVR-VIDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal Health Scientist;Data Scientist;Professional;Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nicola Martinelli</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">nickmart@alice.it</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Winnifred Akello </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">akellowinnifred116@gmail.com </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PathoPredict </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kaho Shinozaki</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">shinozaki.ka@jihs.go.jp</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Japan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Team NIID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Thanicha Chanchaidechachai</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">thanicha.c@chula.ac.th</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">UNICORN</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Veterinary Epidemiologist;</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4249,8 +4330,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M426" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M426"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M436" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M436"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -20343,11 +20424,381 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="427" hidden="0">
+      <x:c r="A427">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B427" s="2">
+        <x:v>46162.4627430556</x:v>
+      </x:c>
+      <x:c r="C427" s="2">
+        <x:v>46162.4642592593</x:v>
+      </x:c>
+      <x:c r="D427" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E427" s="10" t="s"/>
+      <x:c r="F427" s="2"/>
+      <x:c r="G427" s="10" t="s">
+        <x:v>1376</x:v>
+      </x:c>
+      <x:c r="H427" s="10" t="s">
+        <x:v>1377</x:v>
+      </x:c>
+      <x:c r="I427" s="10" t="s">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="J427" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K427" s="10" t="s">
+        <x:v>1342</x:v>
+      </x:c>
+      <x:c r="L427" s="10" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="M427" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" hidden="0">
+      <x:c r="A428">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="B428" s="2">
+        <x:v>46162.7021643519</x:v>
+      </x:c>
+      <x:c r="C428" s="2">
+        <x:v>46162.7026157407</x:v>
+      </x:c>
+      <x:c r="D428" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E428" s="10" t="s"/>
+      <x:c r="F428" s="2"/>
+      <x:c r="G428" s="10" t="s">
+        <x:v>1378</x:v>
+      </x:c>
+      <x:c r="H428" s="10" t="s">
+        <x:v>1379</x:v>
+      </x:c>
+      <x:c r="I428" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J428" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K428" s="10" t="s">
+        <x:v>1342</x:v>
+      </x:c>
+      <x:c r="L428" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M428" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" hidden="0">
+      <x:c r="A429">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="B429" s="2">
+        <x:v>46162.7637962963</x:v>
+      </x:c>
+      <x:c r="C429" s="2">
+        <x:v>46162.7671064815</x:v>
+      </x:c>
+      <x:c r="D429" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E429" s="10" t="s"/>
+      <x:c r="F429" s="2"/>
+      <x:c r="G429" s="10" t="s">
+        <x:v>1380</x:v>
+      </x:c>
+      <x:c r="H429" s="10" t="s">
+        <x:v>1381</x:v>
+      </x:c>
+      <x:c r="I429" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J429" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K429" s="10" t="s">
+        <x:v>1382</x:v>
+      </x:c>
+      <x:c r="L429" s="10" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="M429" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" hidden="0">
+      <x:c r="A430">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B430" s="2">
+        <x:v>46163.4275</x:v>
+      </x:c>
+      <x:c r="C430" s="2">
+        <x:v>46163.4310648148</x:v>
+      </x:c>
+      <x:c r="D430" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E430" s="10" t="s"/>
+      <x:c r="F430" s="2"/>
+      <x:c r="G430" s="10" t="s">
+        <x:v>1383</x:v>
+      </x:c>
+      <x:c r="H430" s="10" t="s">
+        <x:v>1384</x:v>
+      </x:c>
+      <x:c r="I430" s="10" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J430" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K430" s="10" t="s">
+        <x:v>1385</x:v>
+      </x:c>
+      <x:c r="L430" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M430" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" hidden="0">
+      <x:c r="A431">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B431" s="2">
+        <x:v>46163.5941435185</x:v>
+      </x:c>
+      <x:c r="C431" s="2">
+        <x:v>46163.6107986111</x:v>
+      </x:c>
+      <x:c r="D431" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E431" s="10" t="s"/>
+      <x:c r="F431" s="2"/>
+      <x:c r="G431" s="10" t="s">
+        <x:v>1386</x:v>
+      </x:c>
+      <x:c r="H431" s="10" t="s">
+        <x:v>1387</x:v>
+      </x:c>
+      <x:c r="I431" s="10" t="s">
+        <x:v>1142</x:v>
+      </x:c>
+      <x:c r="J431" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K431" s="10" t="s">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="L431" s="10" t="s">
+        <x:v>1389</x:v>
+      </x:c>
+      <x:c r="M431" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" hidden="0">
+      <x:c r="A432">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B432" s="2">
+        <x:v>46163.6112152778</x:v>
+      </x:c>
+      <x:c r="C432" s="2">
+        <x:v>46163.6119907407</x:v>
+      </x:c>
+      <x:c r="D432" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E432" s="10" t="s"/>
+      <x:c r="F432" s="2"/>
+      <x:c r="G432" s="10" t="s">
+        <x:v>1390</x:v>
+      </x:c>
+      <x:c r="H432" s="10" t="s">
+        <x:v>1391</x:v>
+      </x:c>
+      <x:c r="I432" s="10" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="J432" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K432" s="10" t="s">
+        <x:v>1276</x:v>
+      </x:c>
+      <x:c r="L432" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M432" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" hidden="0">
+      <x:c r="A433">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="B433" s="2">
+        <x:v>46164.2711689815</x:v>
+      </x:c>
+      <x:c r="C433" s="2">
+        <x:v>46164.2728819444</x:v>
+      </x:c>
+      <x:c r="D433" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E433" s="10" t="s"/>
+      <x:c r="F433" s="2"/>
+      <x:c r="G433" s="10" t="s">
+        <x:v>1392</x:v>
+      </x:c>
+      <x:c r="H433" s="10" t="s">
+        <x:v>1393</x:v>
+      </x:c>
+      <x:c r="I433" s="10" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="J433" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K433" s="10" t="s">
+        <x:v>1394</x:v>
+      </x:c>
+      <x:c r="L433" s="10" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="M433" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" hidden="0">
+      <x:c r="A434">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B434" s="2">
+        <x:v>46164.276099537</x:v>
+      </x:c>
+      <x:c r="C434" s="2">
+        <x:v>46164.2766782407</x:v>
+      </x:c>
+      <x:c r="D434" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E434" s="10" t="s"/>
+      <x:c r="F434" s="2"/>
+      <x:c r="G434" s="10" t="s">
+        <x:v>1392</x:v>
+      </x:c>
+      <x:c r="H434" s="10" t="s">
+        <x:v>1393</x:v>
+      </x:c>
+      <x:c r="I434" s="10" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="J434" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K434" s="10" t="s">
+        <x:v>1394</x:v>
+      </x:c>
+      <x:c r="L434" s="10" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="M434" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" hidden="0">
+      <x:c r="A435">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="B435" s="2">
+        <x:v>46164.0821296296</x:v>
+      </x:c>
+      <x:c r="C435" s="2">
+        <x:v>46164.3226736111</x:v>
+      </x:c>
+      <x:c r="D435" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E435" s="10" t="s"/>
+      <x:c r="F435" s="2"/>
+      <x:c r="G435" s="10" t="s">
+        <x:v>1395</x:v>
+      </x:c>
+      <x:c r="H435" s="10" t="s">
+        <x:v>1396</x:v>
+      </x:c>
+      <x:c r="I435" s="10" t="s">
+        <x:v>1397</x:v>
+      </x:c>
+      <x:c r="J435" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K435" s="10" t="s">
+        <x:v>1398</x:v>
+      </x:c>
+      <x:c r="L435" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M435" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" hidden="0">
+      <x:c r="A436">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="B436" s="2">
+        <x:v>46164.4021875</x:v>
+      </x:c>
+      <x:c r="C436" s="2">
+        <x:v>46164.4030439815</x:v>
+      </x:c>
+      <x:c r="D436" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E436" s="10" t="s"/>
+      <x:c r="F436" s="2"/>
+      <x:c r="G436" s="10" t="s">
+        <x:v>1399</x:v>
+      </x:c>
+      <x:c r="H436" s="10" t="s">
+        <x:v>1400</x:v>
+      </x:c>
+      <x:c r="I436" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J436" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K436" s="10" t="s">
+        <x:v>1401</x:v>
+      </x:c>
+      <x:c r="L436" s="10" t="s">
+        <x:v>1402</x:v>
+      </x:c>
+      <x:c r="M436" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R963054c96e454490"/>
+    <x:tablePart r:id="R313f17e864974943"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20634,13 +21085,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59FB3B1B-83DA-4E10-9156-44FB27A7D612}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE7FEBA2-DDE2-425D-A545-2F59DDBAC020}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B0A0416-97E6-4DE8-8D69-50DD0FEF949C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4DE97DA-88DE-449D-905A-53218233FC81}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56DE6174-3C27-4D4D-986E-244D1816473C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFD4A625-8EAB-41DA-A8DE-E7ED601136CA}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="1403">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1542">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -4234,6 +4234,423 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Veterinary Epidemiologist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Chaidate Inchaisri</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">chaidate.i@chula.ac.th</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Researcher;Animal Health Scientist;Data Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tenzin TENZIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">t.tenzin@woah.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mauritanie -  France - Sénégal - Niger</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Wahyu Hidayat </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">wahyuhidya@mail.ugm.ac.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Indonesia </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">I don’t have a team yet.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Doan thi da linh</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Phonglinh163@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Epi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PuduOneHealth</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr. S. Rajagunalan </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">drgunavet@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal Health Scientist;Assistant Professor ;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Amala R</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">amalar.statistics@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">R Venkataramanan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">venkyvet@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PuduOnehealth</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Saravana Ganesh Manoharan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">saravanaganesh18@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Arturo Solis Rodriguez </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">asolisrodriguez1993@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ciudad de México </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mwajuma H Bankineza</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">drmwajbanks@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brave M</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> Saleh Abdullah Alrashedi    -    Mohammed Babiker Mohammed Hassan </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> salrashedi@weqaa.gov.sa    -    mhassan@mewa.gov.sa     </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> (KSA) Kingdom of Saudi Arabia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">  Data PulseTeam </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal Health Scientist;Professional;Data Scientist;Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Maithili Gaikwad </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">maithiligaikwad131@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mumbai , India.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AMR Sentinel </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muruye Praise Deborah </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">muruyep@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graduate Student;One health enthusiast ;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ayebare Patience Tukamushaba</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ayebarepatiencet@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Akol Godfrey</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">akolgodfrey21@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aekaluck leklerdsiriwonv</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aekalek@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Giuseppe Bitti</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">giuseppe.bitti@aslsassari.it</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">italia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vectors</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> Mohamed Abdelazim Mohamed Abdelazim</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">m.abdelazim60@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">One health Frontier</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Data Scientist;Animal Health Scientist;Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PUSTstat</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AHMED MAHMOUD SAYED</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AHMEDHASHISH84@GMAIL.COM</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EGYPT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Animal Health Scientist;Data Scientist;Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ahmad Alfarobi Jauharul Ilmi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ahmadalfarobi01@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">NusaOH</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graduate Student;Professional;One Health Policy Analyst;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Eke-Chibuzor Ikechukwu </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ekechibuzoralex@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">I.k</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sara Foddai</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sfoddai@extrainformatica.it</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Italia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> ele-vet-ors</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lawrence Amadi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">amlaw.ke@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kenya, East Africa</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KENYA VETERINARY ASSOCIATION TECHNICAL WORKING GROUP ON ARTIFICIAL INTELIGENCE, BIG DATA AND DIGITALIZATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal Health Scientist;Graduate Student;Chaiperson to the KENYA VETERINARY ASSOCIATION TECHNICAL WORKING GROUP ON ARTIFICIAL INTELIGENCE, BIG DATA AND DIGITALIZATION;Researcher;Professional;Data Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Miguel Trindade de Melo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">melomig@proton.me</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Melo^2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DENNIS KARIUKI MURIITHI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dkariuki@chuka.ac.ke</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KENYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CDAM-Chuka University Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Simon Levi Gamboa Rengifo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sgamboar@sfu.ca</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dauda Ayomide Onawola</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dauda@ohiainitiative.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BioBit</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Wildlife Veterinarian ;Professional;Animal Health Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Joseph Kimatu Samuel </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jkimatu33@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tania Elena Suarez Yana</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tania@ajisefini.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ajisefini7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">MACHOKA BRENDA WANJIRU</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">brendamachoka@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ayodele Majekodunmi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ayodele@ajisefini.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ajisefini5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Data Scientist;Animal Health Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Esther Enioto Oyewole </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">esther@ajisefini.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Coleta Cherono Sang</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cheronocoleta44@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kenya Veterinary Associaton Technical Working Group on artificial Inteligence, Big Data and Digitalization</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Joy Mulinge</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Joy@ajisefini.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Paul@ajisefini.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Data Scientist;Researcher;Public Health Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Teresia Wangare </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">wangareteresia@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">David Chebutia Kemboi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dkemboi@chuka.ac.ke</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Promise Izuchukwu Okoroafor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">promise@ajisefini.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Data Scientist;Biostatistician;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Precious Oladipo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">precious@ajisefini.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">nigeria</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Maryam Said fouad dowidar </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data analysis team </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nantapatt Pridsadangbud</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">nantapatt.cuvet@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pilar Rius Munoz</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pilar.riusmunoz@fao.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Epi Impact</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Abdul kabir </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sindh Agriculture University Tandojam </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KP Pakistan </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Jittrapol Sutejitsiri</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jittrapol.s.imp@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ascension</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Gavrila Amadea Puspitarani</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">gavrila.puspitarani@vetmeduni.ac.at</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Health Across Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Hernan Botero</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hernan.botero@adas.co.uk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PAE (Policy and Economic Team)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4330,8 +4747,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M436" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M436"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M492" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M492"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -20794,304 +21211,2083 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="437" hidden="0">
+      <x:c r="A437">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B437" s="2">
+        <x:v>46164.5071064815</x:v>
+      </x:c>
+      <x:c r="C437" s="2">
+        <x:v>46164.513587963</x:v>
+      </x:c>
+      <x:c r="D437" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E437" s="10" t="s"/>
+      <x:c r="F437" s="2"/>
+      <x:c r="G437" s="10" t="s">
+        <x:v>1403</x:v>
+      </x:c>
+      <x:c r="H437" s="10" t="s">
+        <x:v>1404</x:v>
+      </x:c>
+      <x:c r="I437" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J437" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K437" s="10" t="s">
+        <x:v>1401</x:v>
+      </x:c>
+      <x:c r="L437" s="10" t="s">
+        <x:v>1405</x:v>
+      </x:c>
+      <x:c r="M437" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" hidden="0">
+      <x:c r="A438">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="B438" s="2">
+        <x:v>46164.5806944444</x:v>
+      </x:c>
+      <x:c r="C438" s="2">
+        <x:v>46164.5816666667</x:v>
+      </x:c>
+      <x:c r="D438" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E438" s="10" t="s"/>
+      <x:c r="F438" s="2"/>
+      <x:c r="G438" s="10" t="s">
+        <x:v>1406</x:v>
+      </x:c>
+      <x:c r="H438" s="10" t="s">
+        <x:v>1407</x:v>
+      </x:c>
+      <x:c r="I438" s="10" t="s">
+        <x:v>734</x:v>
+      </x:c>
+      <x:c r="J438" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K438" s="10" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="L438" s="10" t="s">
+        <x:v>725</x:v>
+      </x:c>
+      <x:c r="M438" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" hidden="0">
+      <x:c r="A439">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="B439" s="2">
+        <x:v>46164.7163657407</x:v>
+      </x:c>
+      <x:c r="C439" s="2">
+        <x:v>46164.7171990741</x:v>
+      </x:c>
+      <x:c r="D439" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E439" s="10" t="s"/>
+      <x:c r="F439" s="2"/>
+      <x:c r="G439" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H439" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I439" s="10" t="s">
+        <x:v>1408</x:v>
+      </x:c>
+      <x:c r="J439" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K439" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L439" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M439" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" hidden="0">
+      <x:c r="A440">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B440" s="2">
+        <x:v>46164.8886574074</x:v>
+      </x:c>
+      <x:c r="C440" s="2">
+        <x:v>46164.8901157407</x:v>
+      </x:c>
+      <x:c r="D440" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E440" s="10" t="s"/>
+      <x:c r="F440" s="2"/>
+      <x:c r="G440" s="10" t="s">
+        <x:v>1409</x:v>
+      </x:c>
+      <x:c r="H440" s="10" t="s">
+        <x:v>1410</x:v>
+      </x:c>
+      <x:c r="I440" s="10" t="s">
+        <x:v>1411</x:v>
+      </x:c>
+      <x:c r="J440" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K440" s="10" t="s">
+        <x:v>1412</x:v>
+      </x:c>
+      <x:c r="L440" s="10" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="M440" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" hidden="0">
+      <x:c r="A441">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B441" s="2">
+        <x:v>46165.1221875</x:v>
+      </x:c>
+      <x:c r="C441" s="2">
+        <x:v>46165.1226041667</x:v>
+      </x:c>
+      <x:c r="D441" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E441" s="10" t="s"/>
+      <x:c r="F441" s="2"/>
+      <x:c r="G441" s="10" t="s">
+        <x:v>1413</x:v>
+      </x:c>
+      <x:c r="H441" s="10" t="s">
+        <x:v>1414</x:v>
+      </x:c>
+      <x:c r="I441" s="10" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="J441" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K441" s="10" t="s">
+        <x:v>1415</x:v>
+      </x:c>
+      <x:c r="L441" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M441" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" hidden="0">
+      <x:c r="A442">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="B442" s="2">
+        <x:v>46165.3984259259</x:v>
+      </x:c>
+      <x:c r="C442" s="2">
+        <x:v>46165.399224537</x:v>
+      </x:c>
+      <x:c r="D442" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E442" s="10" t="s"/>
+      <x:c r="F442" s="2"/>
+      <x:c r="G442" s="10" t="s">
+        <x:v>1144</x:v>
+      </x:c>
+      <x:c r="H442" s="10" t="s">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="I442" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J442" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K442" s="10" t="s">
+        <x:v>1416</x:v>
+      </x:c>
+      <x:c r="L442" s="10" t="s">
+        <x:v>725</x:v>
+      </x:c>
+      <x:c r="M442" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" hidden="0">
+      <x:c r="A443">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B443" s="2">
+        <x:v>46165.4130555556</x:v>
+      </x:c>
+      <x:c r="C443" s="2">
+        <x:v>46165.4147800926</x:v>
+      </x:c>
+      <x:c r="D443" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E443" s="10" t="s"/>
+      <x:c r="F443" s="2"/>
+      <x:c r="G443" s="10" t="s">
+        <x:v>1417</x:v>
+      </x:c>
+      <x:c r="H443" s="10" t="s">
+        <x:v>1418</x:v>
+      </x:c>
+      <x:c r="I443" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J443" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K443" s="10" t="s">
+        <x:v>1416</x:v>
+      </x:c>
+      <x:c r="L443" s="10" t="s">
+        <x:v>1419</x:v>
+      </x:c>
+      <x:c r="M443" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" hidden="0">
+      <x:c r="A444">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="B444" s="2">
+        <x:v>46165.4365393519</x:v>
+      </x:c>
+      <x:c r="C444" s="2">
+        <x:v>46165.437662037</x:v>
+      </x:c>
+      <x:c r="D444" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E444" s="10" t="s"/>
+      <x:c r="F444" s="2"/>
+      <x:c r="G444" s="10" t="s">
+        <x:v>1420</x:v>
+      </x:c>
+      <x:c r="H444" s="10" t="s">
+        <x:v>1421</x:v>
+      </x:c>
+      <x:c r="I444" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J444" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K444" s="10" t="s">
+        <x:v>1416</x:v>
+      </x:c>
+      <x:c r="L444" s="10" t="s">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="M444" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" hidden="0">
+      <x:c r="A445">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B445" s="2">
+        <x:v>46165.5025115741</x:v>
+      </x:c>
+      <x:c r="C445" s="2">
+        <x:v>46165.5047106481</x:v>
+      </x:c>
+      <x:c r="D445" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E445" s="10" t="s"/>
+      <x:c r="F445" s="2"/>
+      <x:c r="G445" s="10" t="s">
+        <x:v>1422</x:v>
+      </x:c>
+      <x:c r="H445" s="10" t="s">
+        <x:v>1423</x:v>
+      </x:c>
+      <x:c r="I445" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J445" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K445" s="10" t="s">
+        <x:v>1424</x:v>
+      </x:c>
+      <x:c r="L445" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M445" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" hidden="0">
+      <x:c r="A446">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B446" s="2">
+        <x:v>46165.5280555556</x:v>
+      </x:c>
+      <x:c r="C446" s="2">
+        <x:v>46165.5286111111</x:v>
+      </x:c>
+      <x:c r="D446" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E446" s="10" t="s"/>
+      <x:c r="F446" s="2"/>
+      <x:c r="G446" s="10" t="s">
+        <x:v>1425</x:v>
+      </x:c>
+      <x:c r="H446" s="10" t="s">
+        <x:v>1426</x:v>
+      </x:c>
+      <x:c r="I446" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J446" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K446" s="10" t="s">
+        <x:v>1416</x:v>
+      </x:c>
+      <x:c r="L446" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M446" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" hidden="0">
+      <x:c r="A447">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B447" s="2">
+        <x:v>46166.2047569444</x:v>
+      </x:c>
+      <x:c r="C447" s="2">
+        <x:v>46166.2110763889</x:v>
+      </x:c>
+      <x:c r="D447" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E447" s="10" t="s"/>
+      <x:c r="F447" s="2"/>
+      <x:c r="G447" s="10" t="s">
+        <x:v>1427</x:v>
+      </x:c>
+      <x:c r="H447" s="10" t="s">
+        <x:v>1428</x:v>
+      </x:c>
+      <x:c r="I447" s="10" t="s">
+        <x:v>1429</x:v>
+      </x:c>
+      <x:c r="J447" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K447" s="10" t="s">
+        <x:v>1375</x:v>
+      </x:c>
+      <x:c r="L447" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M447" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" hidden="0">
+      <x:c r="A448">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="B448" s="2">
+        <x:v>46166.3698726852</x:v>
+      </x:c>
+      <x:c r="C448" s="2">
+        <x:v>46166.3713888889</x:v>
+      </x:c>
+      <x:c r="D448" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E448" s="10" t="s"/>
+      <x:c r="F448" s="2"/>
+      <x:c r="G448" s="10" t="s">
+        <x:v>1430</x:v>
+      </x:c>
+      <x:c r="H448" s="10" t="s">
+        <x:v>1431</x:v>
+      </x:c>
+      <x:c r="I448" s="10" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="J448" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K448" s="10" t="s">
+        <x:v>1432</x:v>
+      </x:c>
+      <x:c r="L448" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M448" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" hidden="0">
+      <x:c r="A449">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B449" s="2">
+        <x:v>46161.5730439815</x:v>
+      </x:c>
+      <x:c r="C449" s="2">
+        <x:v>46166.4593171296</x:v>
+      </x:c>
+      <x:c r="D449" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E449" s="10" t="s"/>
+      <x:c r="F449" s="2"/>
+      <x:c r="G449" s="10" t="s">
+        <x:v>1433</x:v>
+      </x:c>
+      <x:c r="H449" s="10" t="s">
+        <x:v>1434</x:v>
+      </x:c>
+      <x:c r="I449" s="10" t="s">
+        <x:v>1435</x:v>
+      </x:c>
+      <x:c r="J449" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K449" s="10" t="s">
+        <x:v>1436</x:v>
+      </x:c>
+      <x:c r="L449" s="10" t="s">
+        <x:v>1437</x:v>
+      </x:c>
+      <x:c r="M449" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" hidden="0">
+      <x:c r="A450">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="B450" s="2">
+        <x:v>46166.9608680556</x:v>
+      </x:c>
+      <x:c r="C450" s="2">
+        <x:v>46166.9630787037</x:v>
+      </x:c>
+      <x:c r="D450" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E450" s="10" t="s"/>
+      <x:c r="F450" s="2"/>
+      <x:c r="G450" s="10" t="s">
+        <x:v>1438</x:v>
+      </x:c>
+      <x:c r="H450" s="10" t="s">
+        <x:v>1439</x:v>
+      </x:c>
+      <x:c r="I450" s="10" t="s">
+        <x:v>1440</x:v>
+      </x:c>
+      <x:c r="J450" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K450" s="10" t="s">
+        <x:v>1441</x:v>
+      </x:c>
+      <x:c r="L450" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M450" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" hidden="0">
+      <x:c r="A451">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B451" s="2">
+        <x:v>46167.2158217593</x:v>
+      </x:c>
+      <x:c r="C451" s="2">
+        <x:v>46167.2176388889</x:v>
+      </x:c>
+      <x:c r="D451" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E451" s="10" t="s"/>
+      <x:c r="F451" s="2"/>
+      <x:c r="G451" s="10" t="s">
+        <x:v>1442</x:v>
+      </x:c>
+      <x:c r="H451" s="10" t="s">
+        <x:v>1443</x:v>
+      </x:c>
+      <x:c r="I451" s="10" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="J451" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K451" s="10" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="L451" s="10" t="s">
+        <x:v>1444</x:v>
+      </x:c>
+      <x:c r="M451" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" hidden="0">
+      <x:c r="A452">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B452" s="2">
+        <x:v>46167.2193171296</x:v>
+      </x:c>
+      <x:c r="C452" s="2">
+        <x:v>46167.221400463</x:v>
+      </x:c>
+      <x:c r="D452" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E452" s="10" t="s"/>
+      <x:c r="F452" s="2"/>
+      <x:c r="G452" s="10" t="s">
+        <x:v>1445</x:v>
+      </x:c>
+      <x:c r="H452" s="10" t="s">
+        <x:v>1446</x:v>
+      </x:c>
+      <x:c r="I452" s="10" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="J452" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K452" s="10" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="L452" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M452" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" hidden="0">
+      <x:c r="A453">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B453" s="2">
+        <x:v>46167.2210763889</x:v>
+      </x:c>
+      <x:c r="C453" s="2">
+        <x:v>46167.2221875</x:v>
+      </x:c>
+      <x:c r="D453" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E453" s="10" t="s"/>
+      <x:c r="F453" s="2"/>
+      <x:c r="G453" s="10" t="s">
+        <x:v>1447</x:v>
+      </x:c>
+      <x:c r="H453" s="10" t="s">
+        <x:v>1448</x:v>
+      </x:c>
+      <x:c r="I453" s="10" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="J453" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K453" s="10" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="L453" s="10" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="M453" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" hidden="0">
+      <x:c r="A454">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B454" s="2">
+        <x:v>46167.3833449074</x:v>
+      </x:c>
+      <x:c r="C454" s="2">
+        <x:v>46167.3841898148</x:v>
+      </x:c>
+      <x:c r="D454" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E454" s="10" t="s"/>
+      <x:c r="F454" s="2"/>
+      <x:c r="G454" s="10" t="s">
+        <x:v>1449</x:v>
+      </x:c>
+      <x:c r="H454" s="10" t="s">
+        <x:v>1450</x:v>
+      </x:c>
+      <x:c r="I454" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J454" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K454" s="10" t="s">
+        <x:v>1401</x:v>
+      </x:c>
+      <x:c r="L454" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M454" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" hidden="0">
+      <x:c r="A455">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B455" s="2">
+        <x:v>46167.4469791667</x:v>
+      </x:c>
+      <x:c r="C455" s="2">
+        <x:v>46167.4483564815</x:v>
+      </x:c>
+      <x:c r="D455" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E455" s="10" t="s"/>
+      <x:c r="F455" s="2"/>
+      <x:c r="G455" s="10" t="s">
+        <x:v>1451</x:v>
+      </x:c>
+      <x:c r="H455" s="10" t="s">
+        <x:v>1452</x:v>
+      </x:c>
+      <x:c r="I455" s="10" t="s">
+        <x:v>1453</x:v>
+      </x:c>
+      <x:c r="J455" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K455" s="10" t="s">
+        <x:v>1454</x:v>
+      </x:c>
+      <x:c r="L455" s="10" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="M455" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" hidden="0">
+      <x:c r="A456">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B456" s="2">
+        <x:v>46167.4520023148</x:v>
+      </x:c>
+      <x:c r="C456" s="2">
+        <x:v>46167.4756134259</x:v>
+      </x:c>
+      <x:c r="D456" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E456" s="10" t="s"/>
+      <x:c r="F456" s="2"/>
+      <x:c r="G456" s="10" t="s">
+        <x:v>1455</x:v>
+      </x:c>
+      <x:c r="H456" s="10" t="s">
+        <x:v>1456</x:v>
+      </x:c>
+      <x:c r="I456" s="10" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="J456" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K456" s="10" t="s">
+        <x:v>1457</x:v>
+      </x:c>
+      <x:c r="L456" s="10" t="s">
+        <x:v>1458</x:v>
+      </x:c>
+      <x:c r="M456" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" hidden="0">
+      <x:c r="A457">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B457" s="2">
+        <x:v>46167.4787615741</x:v>
+      </x:c>
+      <x:c r="C457" s="2">
+        <x:v>46167.4796064815</x:v>
+      </x:c>
+      <x:c r="D457" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E457" s="10" t="s"/>
+      <x:c r="F457" s="2"/>
+      <x:c r="G457" s="10" t="s">
+        <x:v>1065</x:v>
+      </x:c>
+      <x:c r="H457" s="10" t="s">
+        <x:v>1066</x:v>
+      </x:c>
+      <x:c r="I457" s="10" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="J457" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K457" s="10" t="s">
+        <x:v>1459</x:v>
+      </x:c>
+      <x:c r="L457" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M457" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" hidden="0">
+      <x:c r="A458">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="B458" s="2">
+        <x:v>46167.4905902778</x:v>
+      </x:c>
+      <x:c r="C458" s="2">
+        <x:v>46167.4932291667</x:v>
+      </x:c>
+      <x:c r="D458" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E458" s="10" t="s"/>
+      <x:c r="F458" s="2"/>
+      <x:c r="G458" s="10" t="s">
+        <x:v>1460</x:v>
+      </x:c>
+      <x:c r="H458" s="10" t="s">
+        <x:v>1461</x:v>
+      </x:c>
+      <x:c r="I458" s="10" t="s">
+        <x:v>1462</x:v>
+      </x:c>
+      <x:c r="J458" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K458" s="10" t="s">
+        <x:v>1457</x:v>
+      </x:c>
+      <x:c r="L458" s="10" t="s">
+        <x:v>1463</x:v>
+      </x:c>
+      <x:c r="M458" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" hidden="0">
+      <x:c r="A459">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B459" s="2">
+        <x:v>46167.4935069444</x:v>
+      </x:c>
+      <x:c r="C459" s="2">
+        <x:v>46167.4999074074</x:v>
+      </x:c>
+      <x:c r="D459" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E459" s="10" t="s"/>
+      <x:c r="F459" s="2"/>
+      <x:c r="G459" s="10" t="s">
+        <x:v>1464</x:v>
+      </x:c>
+      <x:c r="H459" s="10" t="s">
+        <x:v>1465</x:v>
+      </x:c>
+      <x:c r="I459" s="10" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J459" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K459" s="10" t="s">
+        <x:v>1466</x:v>
+      </x:c>
+      <x:c r="L459" s="10" t="s">
+        <x:v>1467</x:v>
+      </x:c>
+      <x:c r="M459" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" hidden="0">
+      <x:c r="A460">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B460" s="2">
+        <x:v>46167.5258796296</x:v>
+      </x:c>
+      <x:c r="C460" s="2">
+        <x:v>46167.5266666667</x:v>
+      </x:c>
+      <x:c r="D460" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E460" s="10" t="s"/>
+      <x:c r="F460" s="2"/>
+      <x:c r="G460" s="10" t="s">
+        <x:v>1468</x:v>
+      </x:c>
+      <x:c r="H460" s="10" t="s">
+        <x:v>1469</x:v>
+      </x:c>
+      <x:c r="I460" s="10" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J460" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K460" s="10" t="s">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L460" s="10" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="M460" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" hidden="0">
+      <x:c r="A461">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B461" s="2">
+        <x:v>46167.5215509259</x:v>
+      </x:c>
+      <x:c r="C461" s="2">
+        <x:v>46167.5695601852</x:v>
+      </x:c>
+      <x:c r="D461" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E461" s="10" t="s"/>
+      <x:c r="F461" s="2"/>
+      <x:c r="G461" s="10" t="s">
+        <x:v>1471</x:v>
+      </x:c>
+      <x:c r="H461" s="10" t="s">
+        <x:v>1472</x:v>
+      </x:c>
+      <x:c r="I461" s="10" t="s">
+        <x:v>1473</x:v>
+      </x:c>
+      <x:c r="J461" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K461" s="10" t="s">
+        <x:v>1276</x:v>
+      </x:c>
+      <x:c r="L461" s="10" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="M461" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" hidden="0">
+      <x:c r="A462">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B462" s="2">
+        <x:v>46167.5784837963</x:v>
+      </x:c>
+      <x:c r="C462" s="2">
+        <x:v>46167.5980787037</x:v>
+      </x:c>
+      <x:c r="D462" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E462" s="10" t="s"/>
+      <x:c r="F462" s="2"/>
+      <x:c r="G462" s="10" t="s">
+        <x:v>1354</x:v>
+      </x:c>
+      <x:c r="H462" s="10" t="s">
+        <x:v>1355</x:v>
+      </x:c>
+      <x:c r="I462" s="10" t="s">
+        <x:v>1142</x:v>
+      </x:c>
+      <x:c r="J462" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K462" s="10" t="s">
+        <x:v>1474</x:v>
+      </x:c>
+      <x:c r="L462" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M462" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" hidden="0">
+      <x:c r="A463">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B463" s="2">
+        <x:v>46167.6627083333</x:v>
+      </x:c>
+      <x:c r="C463" s="2">
+        <x:v>46167.6674537037</x:v>
+      </x:c>
+      <x:c r="D463" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E463" s="10" t="s"/>
+      <x:c r="F463" s="2"/>
+      <x:c r="G463" s="10" t="s">
+        <x:v>1475</x:v>
+      </x:c>
+      <x:c r="H463" s="10" t="s">
+        <x:v>1476</x:v>
+      </x:c>
+      <x:c r="I463" s="10" t="s">
+        <x:v>1477</x:v>
+      </x:c>
+      <x:c r="J463" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K463" s="10" t="s">
+        <x:v>1478</x:v>
+      </x:c>
+      <x:c r="L463" s="10" t="s">
+        <x:v>1479</x:v>
+      </x:c>
+      <x:c r="M463" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" hidden="0">
+      <x:c r="A464">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="B464" s="2">
+        <x:v>46167.6809259259</x:v>
+      </x:c>
+      <x:c r="C464" s="2">
+        <x:v>46167.6859722222</x:v>
+      </x:c>
+      <x:c r="D464" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E464" s="10" t="s"/>
+      <x:c r="F464" s="2"/>
+      <x:c r="G464" s="10" t="s">
+        <x:v>1480</x:v>
+      </x:c>
+      <x:c r="H464" s="10" t="s">
+        <x:v>1481</x:v>
+      </x:c>
+      <x:c r="I464" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J464" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K464" s="10" t="s">
+        <x:v>1482</x:v>
+      </x:c>
+      <x:c r="L464" s="10" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="M464" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" hidden="0">
+      <x:c r="A465">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="B465" s="2">
+        <x:v>46167.7204513889</x:v>
+      </x:c>
+      <x:c r="C465" s="2">
+        <x:v>46167.7215046296</x:v>
+      </x:c>
+      <x:c r="D465" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E465" s="10" t="s"/>
+      <x:c r="F465" s="2"/>
+      <x:c r="G465" s="10" t="s">
+        <x:v>1483</x:v>
+      </x:c>
+      <x:c r="H465" s="10" t="s">
+        <x:v>1484</x:v>
+      </x:c>
+      <x:c r="I465" s="10" t="s">
+        <x:v>1485</x:v>
+      </x:c>
+      <x:c r="J465" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K465" s="10" t="s">
+        <x:v>1486</x:v>
+      </x:c>
+      <x:c r="L465" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M465" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" hidden="0">
+      <x:c r="A466">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B466" s="2">
+        <x:v>46167.7211805556</x:v>
+      </x:c>
+      <x:c r="C466" s="2">
+        <x:v>46167.7219907407</x:v>
+      </x:c>
+      <x:c r="D466" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E466" s="10" t="s"/>
+      <x:c r="F466" s="2"/>
+      <x:c r="G466" s="10" t="s">
+        <x:v>1487</x:v>
+      </x:c>
+      <x:c r="H466" s="10" t="s">
+        <x:v>1488</x:v>
+      </x:c>
+      <x:c r="I466" s="10" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J466" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K466" s="10" t="s">
+        <x:v>1334</x:v>
+      </x:c>
+      <x:c r="L466" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M466" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" hidden="0">
+      <x:c r="A467">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B467" s="2">
+        <x:v>46167.5824884259</x:v>
+      </x:c>
+      <x:c r="C467" s="2">
+        <x:v>46167.7534259259</x:v>
+      </x:c>
+      <x:c r="D467" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E467" s="10" t="s"/>
+      <x:c r="F467" s="2"/>
+      <x:c r="G467" s="10" t="s">
+        <x:v>1489</x:v>
+      </x:c>
+      <x:c r="H467" s="10" t="s">
+        <x:v>1490</x:v>
+      </x:c>
+      <x:c r="I467" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J467" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K467" s="10" t="s">
+        <x:v>1491</x:v>
+      </x:c>
+      <x:c r="L467" s="10" t="s">
+        <x:v>1492</x:v>
+      </x:c>
+      <x:c r="M467" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" hidden="0">
+      <x:c r="A468">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="B468" s="2">
+        <x:v>46167.7536921296</x:v>
+      </x:c>
+      <x:c r="C468" s="2">
+        <x:v>46167.754212963</x:v>
+      </x:c>
+      <x:c r="D468" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E468" s="10" t="s"/>
+      <x:c r="F468" s="2"/>
+      <x:c r="G468" s="10" t="s">
+        <x:v>1489</x:v>
+      </x:c>
+      <x:c r="H468" s="10" t="s">
+        <x:v>1490</x:v>
+      </x:c>
+      <x:c r="I468" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J468" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K468" s="10" t="s">
+        <x:v>1491</x:v>
+      </x:c>
+      <x:c r="L468" s="10" t="s">
+        <x:v>746</x:v>
+      </x:c>
+      <x:c r="M468" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" hidden="0">
+      <x:c r="A469">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B469" s="2">
+        <x:v>46167.7542361111</x:v>
+      </x:c>
+      <x:c r="C469" s="2">
+        <x:v>46167.7575</x:v>
+      </x:c>
+      <x:c r="D469" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E469" s="10" t="s"/>
+      <x:c r="F469" s="2"/>
+      <x:c r="G469" s="10" t="s">
+        <x:v>1493</x:v>
+      </x:c>
+      <x:c r="H469" s="10" t="s">
+        <x:v>1494</x:v>
+      </x:c>
+      <x:c r="I469" s="10" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J469" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K469" s="10" t="s">
+        <x:v>1478</x:v>
+      </x:c>
+      <x:c r="L469" s="10" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="M469" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" hidden="0">
+      <x:c r="A470">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="B470" s="2">
+        <x:v>46167.7774537037</x:v>
+      </x:c>
+      <x:c r="C470" s="2">
+        <x:v>46167.7783912037</x:v>
+      </x:c>
+      <x:c r="D470" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E470" s="10" t="s"/>
+      <x:c r="F470" s="2"/>
+      <x:c r="G470" s="10" t="s">
+        <x:v>1495</x:v>
+      </x:c>
+      <x:c r="H470" s="10" t="s">
+        <x:v>1496</x:v>
+      </x:c>
+      <x:c r="I470" s="10" t="s">
+        <x:v>1291</x:v>
+      </x:c>
+      <x:c r="J470" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K470" s="10" t="s">
+        <x:v>1497</x:v>
+      </x:c>
+      <x:c r="L470" s="10" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M470" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" hidden="0">
+      <x:c r="A471">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="B471" s="2">
+        <x:v>46167.7806481481</x:v>
+      </x:c>
+      <x:c r="C471" s="2">
+        <x:v>46167.7815162037</x:v>
+      </x:c>
+      <x:c r="D471" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E471" s="10" t="s"/>
+      <x:c r="F471" s="2"/>
+      <x:c r="G471" s="10" t="s">
+        <x:v>1498</x:v>
+      </x:c>
+      <x:c r="H471" s="10" t="s">
+        <x:v>1499</x:v>
+      </x:c>
+      <x:c r="I471" s="10" t="s">
+        <x:v>1485</x:v>
+      </x:c>
+      <x:c r="J471" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K471" s="10" t="s">
+        <x:v>1478</x:v>
+      </x:c>
+      <x:c r="L471" s="10" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M471" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472" hidden="0">
+      <x:c r="A472">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B472" s="2">
+        <x:v>46167.7863310185</x:v>
+      </x:c>
+      <x:c r="C472" s="2">
+        <x:v>46167.7873032407</x:v>
+      </x:c>
+      <x:c r="D472" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E472" s="10" t="s"/>
+      <x:c r="F472" s="2"/>
+      <x:c r="G472" s="10" t="s">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="H472" s="10" t="s">
+        <x:v>1501</x:v>
+      </x:c>
+      <x:c r="I472" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J472" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K472" s="10" t="s">
+        <x:v>1502</x:v>
+      </x:c>
+      <x:c r="L472" s="10" t="s">
+        <x:v>1503</x:v>
+      </x:c>
+      <x:c r="M472" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" hidden="0">
+      <x:c r="A473">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="B473" s="2">
+        <x:v>46167.7935763889</x:v>
+      </x:c>
+      <x:c r="C473" s="2">
+        <x:v>46167.7939236111</x:v>
+      </x:c>
+      <x:c r="D473" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E473" s="10" t="s"/>
+      <x:c r="F473" s="2"/>
+      <x:c r="G473" s="10" t="s">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="H473" s="10" t="s">
+        <x:v>1501</x:v>
+      </x:c>
+      <x:c r="I473" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J473" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K473" s="10" t="s">
+        <x:v>1497</x:v>
+      </x:c>
+      <x:c r="L473" s="10" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M473" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" hidden="0">
+      <x:c r="A474">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="B474" s="2">
+        <x:v>46167.7969328704</x:v>
+      </x:c>
+      <x:c r="C474" s="2">
+        <x:v>46167.7987152778</x:v>
+      </x:c>
+      <x:c r="D474" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E474" s="10" t="s"/>
+      <x:c r="F474" s="2"/>
+      <x:c r="G474" s="10" t="s">
+        <x:v>1504</x:v>
+      </x:c>
+      <x:c r="H474" s="10" t="s">
+        <x:v>1505</x:v>
+      </x:c>
+      <x:c r="I474" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J474" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K474" s="10" t="s">
+        <x:v>1502</x:v>
+      </x:c>
+      <x:c r="L474" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M474" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" hidden="0">
+      <x:c r="A475">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="B475" s="2">
+        <x:v>46167.7975925926</x:v>
+      </x:c>
+      <x:c r="C475" s="2">
+        <x:v>46167.8001851852</x:v>
+      </x:c>
+      <x:c r="D475" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E475" s="10" t="s"/>
+      <x:c r="F475" s="2"/>
+      <x:c r="G475" s="10" t="s">
+        <x:v>1506</x:v>
+      </x:c>
+      <x:c r="H475" s="10" t="s">
+        <x:v>1507</x:v>
+      </x:c>
+      <x:c r="I475" s="10" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J475" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K475" s="10" t="s">
+        <x:v>1508</x:v>
+      </x:c>
+      <x:c r="L475" s="10" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="M475" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" hidden="0">
+      <x:c r="A476">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B476" s="2">
+        <x:v>46167.8159837963</x:v>
+      </x:c>
+      <x:c r="C476" s="2">
+        <x:v>46167.8305208333</x:v>
+      </x:c>
+      <x:c r="D476" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E476" s="10" t="s"/>
+      <x:c r="F476" s="2"/>
+      <x:c r="G476" s="10" t="s">
+        <x:v>1509</x:v>
+      </x:c>
+      <x:c r="H476" s="10" t="s">
+        <x:v>1510</x:v>
+      </x:c>
+      <x:c r="I476" s="10" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J476" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K476" s="10" t="s">
+        <x:v>1502</x:v>
+      </x:c>
+      <x:c r="L476" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M476" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" hidden="0">
+      <x:c r="A477">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="B477" s="2">
+        <x:v>46167.829537037</x:v>
+      </x:c>
+      <x:c r="C477" s="2">
+        <x:v>46167.8309143518</x:v>
+      </x:c>
+      <x:c r="D477" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E477" s="10" t="s"/>
+      <x:c r="F477" s="2"/>
+      <x:c r="G477" s="10" t="s">
+        <x:v>939</x:v>
+      </x:c>
+      <x:c r="H477" s="10" t="s">
+        <x:v>1511</x:v>
+      </x:c>
+      <x:c r="I477" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J477" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K477" s="10" t="s">
+        <x:v>1502</x:v>
+      </x:c>
+      <x:c r="L477" s="10" t="s">
+        <x:v>1512</x:v>
+      </x:c>
+      <x:c r="M477" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" hidden="0">
+      <x:c r="A478">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="B478" s="2">
+        <x:v>46167.8309143518</x:v>
+      </x:c>
+      <x:c r="C478" s="2">
+        <x:v>46167.8319791667</x:v>
+      </x:c>
+      <x:c r="D478" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E478" s="10" t="s"/>
+      <x:c r="F478" s="2"/>
+      <x:c r="G478" s="10" t="s">
+        <x:v>1509</x:v>
+      </x:c>
+      <x:c r="H478" s="10" t="s">
+        <x:v>1510</x:v>
+      </x:c>
+      <x:c r="I478" s="10" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J478" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K478" s="10" t="s">
+        <x:v>1497</x:v>
+      </x:c>
+      <x:c r="L478" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M478" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" hidden="0">
+      <x:c r="A479">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="B479" s="2">
+        <x:v>46167.9113194444</x:v>
+      </x:c>
+      <x:c r="C479" s="2">
+        <x:v>46167.9163194444</x:v>
+      </x:c>
+      <x:c r="D479" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E479" s="10" t="s"/>
+      <x:c r="F479" s="2"/>
+      <x:c r="G479" s="10" t="s">
+        <x:v>1513</x:v>
+      </x:c>
+      <x:c r="H479" s="10" t="s">
+        <x:v>1514</x:v>
+      </x:c>
+      <x:c r="I479" s="10" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J479" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K479" s="10" t="s">
+        <x:v>1478</x:v>
+      </x:c>
+      <x:c r="L479" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M479" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" hidden="0">
+      <x:c r="A480">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="B480" s="2">
+        <x:v>46167.9177314815</x:v>
+      </x:c>
+      <x:c r="C480" s="2">
+        <x:v>46167.9191782407</x:v>
+      </x:c>
+      <x:c r="D480" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E480" s="10" t="s"/>
+      <x:c r="F480" s="2"/>
+      <x:c r="G480" s="10" t="s">
+        <x:v>1515</x:v>
+      </x:c>
+      <x:c r="H480" s="10" t="s">
+        <x:v>1516</x:v>
+      </x:c>
+      <x:c r="I480" s="10" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J480" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K480" s="10" t="s">
+        <x:v>1486</x:v>
+      </x:c>
+      <x:c r="L480" s="10" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M480" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" hidden="0">
+      <x:c r="A481">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B481" s="2">
+        <x:v>46167.9371875</x:v>
+      </x:c>
+      <x:c r="C481" s="2">
+        <x:v>46167.9401967593</x:v>
+      </x:c>
+      <x:c r="D481" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E481" s="10" t="s"/>
+      <x:c r="F481" s="2"/>
+      <x:c r="G481" s="10" t="s">
+        <x:v>1517</x:v>
+      </x:c>
+      <x:c r="H481" s="10" t="s">
+        <x:v>1518</x:v>
+      </x:c>
+      <x:c r="I481" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J481" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K481" s="10" t="s">
+        <x:v>1497</x:v>
+      </x:c>
+      <x:c r="L481" s="10" t="s">
+        <x:v>1519</x:v>
+      </x:c>
+      <x:c r="M481" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" hidden="0">
+      <x:c r="A482">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B482" s="2">
+        <x:v>46168.0447800926</x:v>
+      </x:c>
+      <x:c r="C482" s="2">
+        <x:v>46168.0461458333</x:v>
+      </x:c>
+      <x:c r="D482" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E482" s="10" t="s"/>
+      <x:c r="F482" s="2"/>
+      <x:c r="G482" s="10" t="s">
+        <x:v>1520</x:v>
+      </x:c>
+      <x:c r="H482" s="10" t="s">
+        <x:v>1521</x:v>
+      </x:c>
+      <x:c r="I482" s="10" t="s">
+        <x:v>1522</x:v>
+      </x:c>
+      <x:c r="J482" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K482" s="10" t="s">
+        <x:v>1502</x:v>
+      </x:c>
+      <x:c r="L482" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M482" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" hidden="0">
+      <x:c r="A483">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B483" s="2">
+        <x:v>46168.0463541667</x:v>
+      </x:c>
+      <x:c r="C483" s="2">
+        <x:v>46168.0468055556</x:v>
+      </x:c>
+      <x:c r="D483" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E483" s="10" t="s"/>
+      <x:c r="F483" s="2"/>
+      <x:c r="G483" s="10" t="s">
+        <x:v>1520</x:v>
+      </x:c>
+      <x:c r="H483" s="10" t="s">
+        <x:v>1521</x:v>
+      </x:c>
+      <x:c r="I483" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J483" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K483" s="10" t="s">
+        <x:v>1497</x:v>
+      </x:c>
+      <x:c r="L483" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M483" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" hidden="0">
+      <x:c r="A484">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="B484" s="2">
+        <x:v>46168.0890046296</x:v>
+      </x:c>
+      <x:c r="C484" s="2">
+        <x:v>46168.0898148148</x:v>
+      </x:c>
+      <x:c r="D484" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E484" s="10" t="s"/>
+      <x:c r="F484" s="2"/>
+      <x:c r="G484" s="10" t="s">
+        <x:v>1523</x:v>
+      </x:c>
+      <x:c r="H484" s="10" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="I484" s="10" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="J484" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K484" s="10" t="s">
+        <x:v>1524</x:v>
+      </x:c>
+      <x:c r="L484" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M484" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" hidden="0">
+      <x:c r="A485">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B485" s="2">
+        <x:v>46168.2128009259</x:v>
+      </x:c>
+      <x:c r="C485" s="2">
+        <x:v>46168.2136921296</x:v>
+      </x:c>
+      <x:c r="D485" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E485" s="10" t="s"/>
+      <x:c r="F485" s="2"/>
+      <x:c r="G485" s="10" t="s">
+        <x:v>1525</x:v>
+      </x:c>
+      <x:c r="H485" s="10" t="s">
+        <x:v>1526</x:v>
+      </x:c>
+      <x:c r="I485" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J485" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K485" s="10" t="s">
+        <x:v>1401</x:v>
+      </x:c>
+      <x:c r="L485" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M485" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" hidden="0">
+      <x:c r="A486">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="B486" s="2">
+        <x:v>46168.2586805556</x:v>
+      </x:c>
+      <x:c r="C486" s="2">
+        <x:v>46168.259224537</x:v>
+      </x:c>
+      <x:c r="D486" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E486" s="10" t="s"/>
+      <x:c r="F486" s="2"/>
+      <x:c r="G486" s="10" t="s">
+        <x:v>1156</x:v>
+      </x:c>
+      <x:c r="H486" s="10" t="s">
+        <x:v>1157</x:v>
+      </x:c>
+      <x:c r="I486" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J486" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K486" s="10" t="s">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="L486" s="10" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="M486" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" hidden="0">
+      <x:c r="A487">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B487" s="2">
+        <x:v>46168.3753819444</x:v>
+      </x:c>
+      <x:c r="C487" s="2">
+        <x:v>46168.3801388889</x:v>
+      </x:c>
+      <x:c r="D487" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E487" s="10" t="s"/>
+      <x:c r="F487" s="2"/>
+      <x:c r="G487" s="10" t="s">
+        <x:v>1527</x:v>
+      </x:c>
+      <x:c r="H487" s="10" t="s">
+        <x:v>1528</x:v>
+      </x:c>
+      <x:c r="I487" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J487" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K487" s="10" t="s">
+        <x:v>1529</x:v>
+      </x:c>
+      <x:c r="L487" s="10" t="s">
+        <x:v>1366</x:v>
+      </x:c>
+      <x:c r="M487" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" hidden="0">
+      <x:c r="A488">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B488" s="2">
+        <x:v>46168.2414814815</x:v>
+      </x:c>
+      <x:c r="C488" s="2">
+        <x:v>46168.3826388889</x:v>
+      </x:c>
+      <x:c r="D488" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E488" s="10" t="s"/>
+      <x:c r="F488" s="2"/>
+      <x:c r="G488" s="10" t="s">
+        <x:v>1530</x:v>
+      </x:c>
+      <x:c r="H488" s="10" t="s">
+        <x:v>1531</x:v>
+      </x:c>
+      <x:c r="I488" s="10" t="s">
+        <x:v>1532</x:v>
+      </x:c>
+      <x:c r="J488" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K488" s="10" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L488" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M488" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" hidden="0">
+      <x:c r="A489">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="B489" s="2">
+        <x:v>46168.4008680556</x:v>
+      </x:c>
+      <x:c r="C489" s="2">
+        <x:v>46168.4016550926</x:v>
+      </x:c>
+      <x:c r="D489" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E489" s="10" t="s"/>
+      <x:c r="F489" s="2"/>
+      <x:c r="G489" s="10" t="s">
+        <x:v>1533</x:v>
+      </x:c>
+      <x:c r="H489" s="10" t="s">
+        <x:v>1534</x:v>
+      </x:c>
+      <x:c r="I489" s="10" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="J489" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K489" s="10" t="s">
+        <x:v>1535</x:v>
+      </x:c>
+      <x:c r="L489" s="10" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="M489" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" hidden="0">
+      <x:c r="A490">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="B490" s="2">
+        <x:v>46168.4578009259</x:v>
+      </x:c>
+      <x:c r="C490" s="2">
+        <x:v>46168.4585532407</x:v>
+      </x:c>
+      <x:c r="D490" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E490" s="10" t="s"/>
+      <x:c r="F490" s="2"/>
+      <x:c r="G490" s="10" t="s">
+        <x:v>1536</x:v>
+      </x:c>
+      <x:c r="H490" s="10" t="s">
+        <x:v>1537</x:v>
+      </x:c>
+      <x:c r="I490" s="10" t="s">
+        <x:v>1299</x:v>
+      </x:c>
+      <x:c r="J490" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K490" s="10" t="s">
+        <x:v>1538</x:v>
+      </x:c>
+      <x:c r="L490" s="10" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M490" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" hidden="0">
+      <x:c r="A491">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B491" s="2">
+        <x:v>46168.5226851852</x:v>
+      </x:c>
+      <x:c r="C491" s="2">
+        <x:v>46168.5236689815</x:v>
+      </x:c>
+      <x:c r="D491" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E491" s="10" t="s"/>
+      <x:c r="F491" s="2"/>
+      <x:c r="G491" s="10" t="s">
+        <x:v>1539</x:v>
+      </x:c>
+      <x:c r="H491" s="10" t="s">
+        <x:v>1540</x:v>
+      </x:c>
+      <x:c r="I491" s="10" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="J491" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K491" s="10" t="s">
+        <x:v>1541</x:v>
+      </x:c>
+      <x:c r="L491" s="10" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M491" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" hidden="0">
+      <x:c r="A492">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="B492" s="2">
+        <x:v>46168.5805787037</x:v>
+      </x:c>
+      <x:c r="C492" s="2">
+        <x:v>46168.5810300926</x:v>
+      </x:c>
+      <x:c r="D492" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E492" s="10" t="s"/>
+      <x:c r="F492" s="2"/>
+      <x:c r="G492" s="10" t="s">
+        <x:v>1386</x:v>
+      </x:c>
+      <x:c r="H492" s="10" t="s">
+        <x:v>1387</x:v>
+      </x:c>
+      <x:c r="I492" s="10" t="s">
+        <x:v>1142</x:v>
+      </x:c>
+      <x:c r="J492" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K492" s="10" t="s">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="L492" s="10" t="s">
+        <x:v>1463</x:v>
+      </x:c>
+      <x:c r="M492" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R313f17e864974943"/>
+    <x:tablePart r:id="R974ee14605e349cd"/>
   </x:tableParts>
 </x:worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096F5A18ADBDD9E4D8F394AC4B3466405" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e59e3e6d23932d1d7525b22f7d7f3a7d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" xmlns:ns3="76b4ec34-0f89-435f-928a-b7c414764614" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d88756df8cabe05f154bf6d416a348" ns2:_="" ns3:_="">
-    <xsd:import namespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb"/>
-    <xsd:import namespace="76b4ec34-0f89-435f-928a-b7c414764614"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ad0b2da7-f7f1-4ade-bc4d-78491eef27d0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="76b4ec34-0f89-435f-928a-b7c414764614" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c696ee1e-5302-4bbd-96b7-dbc90bffde0f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="76b4ec34-0f89-435f-928a-b7c414764614">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="76b4ec34-0f89-435f-928a-b7c414764614" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE7FEBA2-DDE2-425D-A545-2F59DDBAC020}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4DE97DA-88DE-449D-905A-53218233FC81}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFD4A625-8EAB-41DA-A8DE-E7ED601136CA}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1542">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1755">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -4651,6 +4651,645 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">PAE (Policy and Economic Team)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bernard Otu Assim-ita</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Comms@ajisefini.org</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nigeria, West Africa </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rodrigo Ignacio Marín Nahuelpi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">rodrigo.marin@ug.uchile.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Scientist;Professional;Graduate Student;Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Jousepth Gallardo Hidalgo </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jousepth.gallardo@uchile.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vito Antonio Mastrochirico Filho</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vito.oceano@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Data Scientist;Public Health Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ana Maria Perez Arredondo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ana.perez@vetmeduni.ac.at</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brunele Weber Chaves</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">brunele-chaves@agricultura.rs.gov.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Defesa RS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Amélie Desvars-Larrive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">amelie.desvars@vetmeduni.ac.at</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Corlena Patterson</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">corlena@pruvit.tech</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SignalBridge Analytics</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mobolaji Abdulateef Ayoola </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mobolajiabdulateef@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Biobit</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Matilde Maçãs Nogueiro Capote</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">matildecapote@edu.ulisboa.pt</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Heavenly bacon</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Telmo Pina Nunes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tnunes@fmv.ulisboa.pt</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cat's tongue</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yuliana de Jesús Zárate Rodríguez </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">yuliana.zarate@rcastellanos.cdmx.gob.mx</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">México, ciudad de México </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Teacher of data scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Víctor Arellano de la Cruz</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">victor.arellano@rcastellano.cdmx.gob.mx</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PathoLogic Insight</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">P.H.D. Mathematics ;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Team NIID-JIHS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Madalena Paulino Neves</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">neves.madalena22@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mafalda Pedro Mil-Homens</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mafalda.pedro@uab.cat</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Animal Health Scientist;Epidemiologist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sayoko HANAMOTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hanamoto-sayoko0908@g.ecc.u-tokyo.ac.jp</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sebastian Van Wyk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sebastianvw04@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Anna Caroline Pontel de Almeida</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">anna.pontel@vetmeduni.ac.at</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Giovanna Campus</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">giovanna.campus@aslsassari.it</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Animal Health Scientist;Data Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Francesco Sgarangella</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">francesco.sgarangella@aslsassari.it</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Matilde de Melo Rodrigues Galvão Teles</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">teles.matilde.0125@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Carsten Kirkeby</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ckir@sund.ku.dk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Denmark</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">What the Cluck</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TAPENDRA SAINI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tsaini.9461@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Eventoed</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RITESH VISHWAKARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ritesh.mammals@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Quantitative biologist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Francisco Trindade de Melo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">francisco@edgen.co</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Carolina Mendes Galante Merca</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">carolinamgmerca@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Copenhagen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Scientist;Veterinary Epidemiologist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Angel Monsivais Lara</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">angel.monsivais.lara@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">México</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Undergraduate Student;Data Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Daniela Ochoa Romero</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dani.ochoa1608@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Daniela Pais André</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">danielapaisandre@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cat's Tongue</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sandra Filipa Oliveira Carapeto</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sandra.carapeto@sund.ku.dk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Renata de Lara Muylaert </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">renata.muylaert@sydney.edu.au </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Thi Thuy Hoang</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">thi-thuy.hoang@sydney.edu.au</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nadya W</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nadya.w@colostate.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SEAblings</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lee Zhi Mei Maria </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">zhimei@colostate.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SEAblings/ sang kancil</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Janet Andrea Fuertes Lino</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">janetfuerteslino@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lima, Perú</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Farhan Akorede </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Farhanakoreder@gmail.com </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ayano Nishino</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">nishino.a@jihs.go.jp</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Chris Baker </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">cbaker1@unimelb.edu.au</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">HASTE project</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Simon Firestone</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">simon.firestone@unimelb.edu.au</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Simin Lee</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">simin.lee1@student.unimelb.edu.au</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Thao P Le</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tk.le@unimelb.edu.au</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">James Oyindamola Ogunsanya</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">oyindamolajames@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Braynstormers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lene Jung Kjær</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lenju@sund.ku.dk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Gollo Amina Halkano</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">amina.h.gollo@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RANGELAND ARMIDA LTD</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Xin Hou</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">xin.hou@pasteur.fr</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Eberechukwu Queensley Chinedu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ebyqueensley1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Michael Ward</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">michael.ward@sydney.edu.au</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Banes Sossou Peter </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FUSIONTHINKERS </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Li Chuin Chong</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lichuin.chong@twincore.de</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Braynstromers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Louis Chih-Ming Lee</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">louis@louisclee.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ele-vet-ors</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Success Isuman</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Successisuman9@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yanshi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">y.yanshi@uu.nl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graduate Student;Researcher;Epidemiologist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Charbel Marcy Otokpè HOUNHOUENOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hcharbelmarcy@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Benin </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cheetabj</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Eugênio Dias Ribeiro Neto</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ediasribeiro@lirmm.fr</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Montpellier, France</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">VoGuLoTiEuka</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Katerina Albrechtova</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">albrechtovakaterina@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">VoGuLoTiEuKa</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Guillaume Fourret</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">guillaume.fourret@lirmm.fr</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tiwonge Tinto Kalua</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tiwongekalua@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Belgium </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">VoGuloTiEuKa</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FUJII Eri</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">fujii.e@jihs.go.jp</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kelvin Ho Koun Tak</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kelvinhom@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Singapore </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Biorisk and Biosurveillance Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Taro Kamigaki</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">kamigaki.t@jihs.go.jp</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Osamu Fujita</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">fujita.o@jihs.go.jp</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Meryl Theng</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">meryl.theng@unimelb.edu.au</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Milena Soares Pinto Merat</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">milenamerat@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EpiSquad</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Daniela Dutra de Oliveira</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">danieladutra.vet@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Maria Alice de Oliveira Matos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">malice.omatos@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sweet rice</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nyelsen Fernandes de Oliveira</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">nyelsenfernandes2@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Flavia Andrade de Souza </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">flaviaa.desouza0701@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fernanda da Silva Lopes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lopesfernanda021@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Jehú Aarón Ortega Martínez</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jehu-gu@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">NewsBrakers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Francisco Javier Granados Paz </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">franciscojaviergranadospaz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The NewsBrakers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lolokote Sainyugu </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sesia.agrovet@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brian Tan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brian_tan@nparks.gov.sg</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Insights Alchemists</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Charlene Judith Fernandez </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Charlene_fernandez@nparks.gov.sg</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brian Tan Zi Yan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Charlene Judith Fernandez</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Charlene_Fernandez@nparks.gov.sg</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Raquel Costa </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">raqueldelobocosta@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Marta Martínez Avilés</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">martinez.marta@inia.csic.es</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">spain</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EYSA (Epidemiology and Environmental Health)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lee Chee Wai</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lee_chee_wai@nparks.gov.sg</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Denise Yu Ching Yi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">denise_yu@nparks.gov.sg</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">IRene </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">iglesias@inia.csic.es</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EySA</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fidel Hernández Jiménez </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fidel.hernandez@inia.csic.es</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Spain, Europe</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EySA (Epidemiology and Enviromental Health)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4747,8 +5386,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M492" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M492"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M576" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M576"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -23283,11 +23922,3410 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="493" hidden="0">
+      <x:c r="A493">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="B493" s="2">
+        <x:v>46168.6722569444</x:v>
+      </x:c>
+      <x:c r="C493" s="2">
+        <x:v>46168.6727662037</x:v>
+      </x:c>
+      <x:c r="D493" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E493" s="10" t="s"/>
+      <x:c r="F493" s="2"/>
+      <x:c r="G493" s="10" t="s">
+        <x:v>1542</x:v>
+      </x:c>
+      <x:c r="H493" s="10" t="s">
+        <x:v>1543</x:v>
+      </x:c>
+      <x:c r="I493" s="10" t="s">
+        <x:v>1544</x:v>
+      </x:c>
+      <x:c r="J493" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K493" s="10" t="s">
+        <x:v>1502</x:v>
+      </x:c>
+      <x:c r="L493" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M493" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" hidden="0">
+      <x:c r="A494">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B494" s="2">
+        <x:v>46168.6992592593</x:v>
+      </x:c>
+      <x:c r="C494" s="2">
+        <x:v>46168.699849537</x:v>
+      </x:c>
+      <x:c r="D494" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E494" s="10" t="s"/>
+      <x:c r="F494" s="2"/>
+      <x:c r="G494" s="10" t="s">
+        <x:v>1545</x:v>
+      </x:c>
+      <x:c r="H494" s="10" t="s">
+        <x:v>1546</x:v>
+      </x:c>
+      <x:c r="I494" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="J494" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K494" s="10" t="s">
+        <x:v>1326</x:v>
+      </x:c>
+      <x:c r="L494" s="10" t="s">
+        <x:v>1547</x:v>
+      </x:c>
+      <x:c r="M494" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" hidden="0">
+      <x:c r="A495">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="B495" s="2">
+        <x:v>46168.6992361111</x:v>
+      </x:c>
+      <x:c r="C495" s="2">
+        <x:v>46168.7011574074</x:v>
+      </x:c>
+      <x:c r="D495" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E495" s="10" t="s"/>
+      <x:c r="F495" s="2"/>
+      <x:c r="G495" s="10" t="s">
+        <x:v>1548</x:v>
+      </x:c>
+      <x:c r="H495" s="10" t="s">
+        <x:v>1549</x:v>
+      </x:c>
+      <x:c r="I495" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="J495" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K495" s="10" t="s">
+        <x:v>1326</x:v>
+      </x:c>
+      <x:c r="L495" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M495" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" hidden="0">
+      <x:c r="A496">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="B496" s="2">
+        <x:v>46168.7008796296</x:v>
+      </x:c>
+      <x:c r="C496" s="2">
+        <x:v>46168.7020833333</x:v>
+      </x:c>
+      <x:c r="D496" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E496" s="10" t="s"/>
+      <x:c r="F496" s="2"/>
+      <x:c r="G496" s="10" t="s">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="H496" s="10" t="s">
+        <x:v>1551</x:v>
+      </x:c>
+      <x:c r="I496" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="J496" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K496" s="10" t="s">
+        <x:v>1326</x:v>
+      </x:c>
+      <x:c r="L496" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M496" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" hidden="0">
+      <x:c r="A497">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B497" s="2">
+        <x:v>46168.7349537037</x:v>
+      </x:c>
+      <x:c r="C497" s="2">
+        <x:v>46168.7361226852</x:v>
+      </x:c>
+      <x:c r="D497" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E497" s="10" t="s"/>
+      <x:c r="F497" s="2"/>
+      <x:c r="G497" s="10" t="s">
+        <x:v>939</x:v>
+      </x:c>
+      <x:c r="H497" s="10" t="s">
+        <x:v>1511</x:v>
+      </x:c>
+      <x:c r="I497" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J497" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K497" s="10" t="s">
+        <x:v>1497</x:v>
+      </x:c>
+      <x:c r="L497" s="10" t="s">
+        <x:v>1552</x:v>
+      </x:c>
+      <x:c r="M497" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" hidden="0">
+      <x:c r="A498">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="B498" s="2">
+        <x:v>46168.7694444444</x:v>
+      </x:c>
+      <x:c r="C498" s="2">
+        <x:v>46168.7701041667</x:v>
+      </x:c>
+      <x:c r="D498" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E498" s="10" t="s"/>
+      <x:c r="F498" s="2"/>
+      <x:c r="G498" s="10" t="s">
+        <x:v>1553</x:v>
+      </x:c>
+      <x:c r="H498" s="10" t="s">
+        <x:v>1554</x:v>
+      </x:c>
+      <x:c r="I498" s="10" t="s">
+        <x:v>1299</x:v>
+      </x:c>
+      <x:c r="J498" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K498" s="10" t="s">
+        <x:v>1538</x:v>
+      </x:c>
+      <x:c r="L498" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M498" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" hidden="0">
+      <x:c r="A499">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="B499" s="2">
+        <x:v>46168.8232523148</x:v>
+      </x:c>
+      <x:c r="C499" s="2">
+        <x:v>46168.8645601852</x:v>
+      </x:c>
+      <x:c r="D499" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E499" s="10" t="s"/>
+      <x:c r="F499" s="2"/>
+      <x:c r="G499" s="10" t="s">
+        <x:v>1555</x:v>
+      </x:c>
+      <x:c r="H499" s="10" t="s">
+        <x:v>1556</x:v>
+      </x:c>
+      <x:c r="I499" s="10" t="s">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="J499" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K499" s="10" t="s">
+        <x:v>1557</x:v>
+      </x:c>
+      <x:c r="L499" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M499" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" hidden="0">
+      <x:c r="A500">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="B500" s="2">
+        <x:v>46168.868599537</x:v>
+      </x:c>
+      <x:c r="C500" s="2">
+        <x:v>46168.8693171296</x:v>
+      </x:c>
+      <x:c r="D500" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E500" s="10" t="s"/>
+      <x:c r="F500" s="2"/>
+      <x:c r="G500" s="10" t="s">
+        <x:v>1558</x:v>
+      </x:c>
+      <x:c r="H500" s="10" t="s">
+        <x:v>1559</x:v>
+      </x:c>
+      <x:c r="I500" s="10" t="s">
+        <x:v>1299</x:v>
+      </x:c>
+      <x:c r="J500" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K500" s="10" t="s">
+        <x:v>1538</x:v>
+      </x:c>
+      <x:c r="L500" s="10" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="M500" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" hidden="0">
+      <x:c r="A501">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="B501" s="2">
+        <x:v>46168.8949537037</x:v>
+      </x:c>
+      <x:c r="C501" s="2">
+        <x:v>46168.8960763889</x:v>
+      </x:c>
+      <x:c r="D501" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E501" s="10" t="s"/>
+      <x:c r="F501" s="2"/>
+      <x:c r="G501" s="10" t="s">
+        <x:v>1560</x:v>
+      </x:c>
+      <x:c r="H501" s="10" t="s">
+        <x:v>1561</x:v>
+      </x:c>
+      <x:c r="I501" s="10" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J501" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K501" s="10" t="s">
+        <x:v>1562</x:v>
+      </x:c>
+      <x:c r="L501" s="10" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="M501" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" hidden="0">
+      <x:c r="A502">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B502" s="2">
+        <x:v>46168.9608796296</x:v>
+      </x:c>
+      <x:c r="C502" s="2">
+        <x:v>46168.9614814815</x:v>
+      </x:c>
+      <x:c r="D502" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E502" s="10" t="s"/>
+      <x:c r="F502" s="2"/>
+      <x:c r="G502" s="10" t="s">
+        <x:v>1563</x:v>
+      </x:c>
+      <x:c r="H502" s="10" t="s">
+        <x:v>1564</x:v>
+      </x:c>
+      <x:c r="I502" s="10" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J502" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K502" s="10" t="s">
+        <x:v>1565</x:v>
+      </x:c>
+      <x:c r="L502" s="10" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M502" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" hidden="0">
+      <x:c r="A503">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B503" s="2">
+        <x:v>46168.9992939815</x:v>
+      </x:c>
+      <x:c r="C503" s="2">
+        <x:v>46169.0017824074</x:v>
+      </x:c>
+      <x:c r="D503" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E503" s="10" t="s"/>
+      <x:c r="F503" s="2"/>
+      <x:c r="G503" s="10" t="s">
+        <x:v>1566</x:v>
+      </x:c>
+      <x:c r="H503" s="10" t="s">
+        <x:v>1567</x:v>
+      </x:c>
+      <x:c r="I503" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J503" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K503" s="10" t="s">
+        <x:v>1568</x:v>
+      </x:c>
+      <x:c r="L503" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M503" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" hidden="0">
+      <x:c r="A504">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="B504" s="2">
+        <x:v>46169.0083101852</x:v>
+      </x:c>
+      <x:c r="C504" s="2">
+        <x:v>46169.0090972222</x:v>
+      </x:c>
+      <x:c r="D504" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E504" s="10" t="s"/>
+      <x:c r="F504" s="2"/>
+      <x:c r="G504" s="10" t="s">
+        <x:v>1569</x:v>
+      </x:c>
+      <x:c r="H504" s="10" t="s">
+        <x:v>1570</x:v>
+      </x:c>
+      <x:c r="I504" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J504" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K504" s="10" t="s">
+        <x:v>1571</x:v>
+      </x:c>
+      <x:c r="L504" s="10" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="M504" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" hidden="0">
+      <x:c r="A505">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="B505" s="2">
+        <x:v>46169.1474421296</x:v>
+      </x:c>
+      <x:c r="C505" s="2">
+        <x:v>46169.1489236111</x:v>
+      </x:c>
+      <x:c r="D505" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E505" s="10" t="s"/>
+      <x:c r="F505" s="2"/>
+      <x:c r="G505" s="10" t="s">
+        <x:v>1572</x:v>
+      </x:c>
+      <x:c r="H505" s="10" t="s">
+        <x:v>1573</x:v>
+      </x:c>
+      <x:c r="I505" s="10" t="s">
+        <x:v>1574</x:v>
+      </x:c>
+      <x:c r="J505" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K505" s="10" t="s">
+        <x:v>1375</x:v>
+      </x:c>
+      <x:c r="L505" s="10" t="s">
+        <x:v>1575</x:v>
+      </x:c>
+      <x:c r="M505" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" hidden="0">
+      <x:c r="A506">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B506" s="2">
+        <x:v>46169.1491435185</x:v>
+      </x:c>
+      <x:c r="C506" s="2">
+        <x:v>46169.1508449074</x:v>
+      </x:c>
+      <x:c r="D506" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E506" s="10" t="s"/>
+      <x:c r="F506" s="2"/>
+      <x:c r="G506" s="10" t="s">
+        <x:v>1576</x:v>
+      </x:c>
+      <x:c r="H506" s="10" t="s">
+        <x:v>1577</x:v>
+      </x:c>
+      <x:c r="I506" s="10" t="s">
+        <x:v>1574</x:v>
+      </x:c>
+      <x:c r="J506" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K506" s="10" t="s">
+        <x:v>1578</x:v>
+      </x:c>
+      <x:c r="L506" s="10" t="s">
+        <x:v>1579</x:v>
+      </x:c>
+      <x:c r="M506" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" hidden="0">
+      <x:c r="A507">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="B507" s="2">
+        <x:v>46169.2989467593</x:v>
+      </x:c>
+      <x:c r="C507" s="2">
+        <x:v>46169.2996064815</x:v>
+      </x:c>
+      <x:c r="D507" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E507" s="10" t="s"/>
+      <x:c r="F507" s="2"/>
+      <x:c r="G507" s="10" t="s">
+        <x:v>1395</x:v>
+      </x:c>
+      <x:c r="H507" s="10" t="s">
+        <x:v>1396</x:v>
+      </x:c>
+      <x:c r="I507" s="10" t="s">
+        <x:v>1397</x:v>
+      </x:c>
+      <x:c r="J507" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K507" s="10" t="s">
+        <x:v>1580</x:v>
+      </x:c>
+      <x:c r="L507" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M507" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" hidden="0">
+      <x:c r="A508">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="B508" s="2">
+        <x:v>46169.3411689815</x:v>
+      </x:c>
+      <x:c r="C508" s="2">
+        <x:v>46169.3421064815</x:v>
+      </x:c>
+      <x:c r="D508" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E508" s="10" t="s"/>
+      <x:c r="F508" s="2"/>
+      <x:c r="G508" s="10" t="s">
+        <x:v>1581</x:v>
+      </x:c>
+      <x:c r="H508" s="10" t="s">
+        <x:v>1582</x:v>
+      </x:c>
+      <x:c r="I508" s="10" t="s">
+        <x:v>1279</x:v>
+      </x:c>
+      <x:c r="J508" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K508" s="10" t="s">
+        <x:v>1568</x:v>
+      </x:c>
+      <x:c r="L508" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M508" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" hidden="0">
+      <x:c r="A509">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B509" s="2">
+        <x:v>46169.3741319444</x:v>
+      </x:c>
+      <x:c r="C509" s="2">
+        <x:v>46169.3756828704</x:v>
+      </x:c>
+      <x:c r="D509" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E509" s="10" t="s"/>
+      <x:c r="F509" s="2"/>
+      <x:c r="G509" s="10" t="s">
+        <x:v>1583</x:v>
+      </x:c>
+      <x:c r="H509" s="10" t="s">
+        <x:v>1584</x:v>
+      </x:c>
+      <x:c r="I509" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J509" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K509" s="10" t="s">
+        <x:v>1568</x:v>
+      </x:c>
+      <x:c r="L509" s="10" t="s">
+        <x:v>1585</x:v>
+      </x:c>
+      <x:c r="M509" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" hidden="0">
+      <x:c r="A510">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="B510" s="2">
+        <x:v>46169.3943865741</x:v>
+      </x:c>
+      <x:c r="C510" s="2">
+        <x:v>46169.4029976852</x:v>
+      </x:c>
+      <x:c r="D510" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E510" s="10" t="s"/>
+      <x:c r="F510" s="2"/>
+      <x:c r="G510" s="10" t="s">
+        <x:v>1586</x:v>
+      </x:c>
+      <x:c r="H510" s="10" t="s">
+        <x:v>1587</x:v>
+      </x:c>
+      <x:c r="I510" s="10" t="s">
+        <x:v>1397</x:v>
+      </x:c>
+      <x:c r="J510" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K510" s="10" t="s">
+        <x:v>1580</x:v>
+      </x:c>
+      <x:c r="L510" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M510" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" hidden="0">
+      <x:c r="A511">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="B511" s="2">
+        <x:v>46169.4236574074</x:v>
+      </x:c>
+      <x:c r="C511" s="2">
+        <x:v>46169.4253240741</x:v>
+      </x:c>
+      <x:c r="D511" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E511" s="10" t="s"/>
+      <x:c r="F511" s="2"/>
+      <x:c r="G511" s="10" t="s">
+        <x:v>1588</x:v>
+      </x:c>
+      <x:c r="H511" s="10" t="s">
+        <x:v>1589</x:v>
+      </x:c>
+      <x:c r="I511" s="10" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="J511" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K511" s="10" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="L511" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M511" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" hidden="0">
+      <x:c r="A512">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="B512" s="2">
+        <x:v>46169.47875</x:v>
+      </x:c>
+      <x:c r="C512" s="2">
+        <x:v>46169.4792939815</x:v>
+      </x:c>
+      <x:c r="D512" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E512" s="10" t="s"/>
+      <x:c r="F512" s="2"/>
+      <x:c r="G512" s="10" t="s">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="H512" s="10" t="s">
+        <x:v>1591</x:v>
+      </x:c>
+      <x:c r="I512" s="10" t="s">
+        <x:v>1299</x:v>
+      </x:c>
+      <x:c r="J512" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K512" s="10" t="s">
+        <x:v>1538</x:v>
+      </x:c>
+      <x:c r="L512" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M512" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" hidden="0">
+      <x:c r="A513">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="B513" s="2">
+        <x:v>46169.5001157407</x:v>
+      </x:c>
+      <x:c r="C513" s="2">
+        <x:v>46169.5009259259</x:v>
+      </x:c>
+      <x:c r="D513" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E513" s="10" t="s"/>
+      <x:c r="F513" s="2"/>
+      <x:c r="G513" s="10" t="s">
+        <x:v>1592</x:v>
+      </x:c>
+      <x:c r="H513" s="10" t="s">
+        <x:v>1593</x:v>
+      </x:c>
+      <x:c r="I513" s="10" t="s">
+        <x:v>1453</x:v>
+      </x:c>
+      <x:c r="J513" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K513" s="10" t="s">
+        <x:v>1454</x:v>
+      </x:c>
+      <x:c r="L513" s="10" t="s">
+        <x:v>1594</x:v>
+      </x:c>
+      <x:c r="M513" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" hidden="0">
+      <x:c r="A514">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="B514" s="2">
+        <x:v>46169.5020833333</x:v>
+      </x:c>
+      <x:c r="C514" s="2">
+        <x:v>46169.5029050926</x:v>
+      </x:c>
+      <x:c r="D514" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E514" s="10" t="s"/>
+      <x:c r="F514" s="2"/>
+      <x:c r="G514" s="10" t="s">
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="H514" s="10" t="s">
+        <x:v>1596</x:v>
+      </x:c>
+      <x:c r="I514" s="10" t="s">
+        <x:v>1453</x:v>
+      </x:c>
+      <x:c r="J514" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K514" s="10" t="s">
+        <x:v>1454</x:v>
+      </x:c>
+      <x:c r="L514" s="10" t="s">
+        <x:v>1594</x:v>
+      </x:c>
+      <x:c r="M514" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" hidden="0">
+      <x:c r="A515">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B515" s="2">
+        <x:v>46169.5237152778</x:v>
+      </x:c>
+      <x:c r="C515" s="2">
+        <x:v>46169.524849537</x:v>
+      </x:c>
+      <x:c r="D515" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E515" s="10" t="s"/>
+      <x:c r="F515" s="2"/>
+      <x:c r="G515" s="10" t="s">
+        <x:v>1597</x:v>
+      </x:c>
+      <x:c r="H515" s="10" t="s">
+        <x:v>1598</x:v>
+      </x:c>
+      <x:c r="I515" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J515" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K515" s="10" t="s">
+        <x:v>1568</x:v>
+      </x:c>
+      <x:c r="L515" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M515" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" hidden="0">
+      <x:c r="A516">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="B516" s="2">
+        <x:v>46169.5698263889</x:v>
+      </x:c>
+      <x:c r="C516" s="2">
+        <x:v>46169.5704976852</x:v>
+      </x:c>
+      <x:c r="D516" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E516" s="10" t="s"/>
+      <x:c r="F516" s="2"/>
+      <x:c r="G516" s="10" t="s">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="H516" s="10" t="s">
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="I516" s="10" t="s">
+        <x:v>1601</x:v>
+      </x:c>
+      <x:c r="J516" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K516" s="10" t="s">
+        <x:v>1602</x:v>
+      </x:c>
+      <x:c r="L516" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M516" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" hidden="0">
+      <x:c r="A517">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="B517" s="2">
+        <x:v>46169.6435069444</x:v>
+      </x:c>
+      <x:c r="C517" s="2">
+        <x:v>46169.6449189815</x:v>
+      </x:c>
+      <x:c r="D517" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E517" s="10" t="s"/>
+      <x:c r="F517" s="2"/>
+      <x:c r="G517" s="10" t="s">
+        <x:v>1603</x:v>
+      </x:c>
+      <x:c r="H517" s="10" t="s">
+        <x:v>1604</x:v>
+      </x:c>
+      <x:c r="I517" s="10" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="J517" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K517" s="10" t="s">
+        <x:v>1605</x:v>
+      </x:c>
+      <x:c r="L517" s="10" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M517" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" hidden="0">
+      <x:c r="A518">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B518" s="2">
+        <x:v>46169.645162037</x:v>
+      </x:c>
+      <x:c r="C518" s="2">
+        <x:v>46169.645775463</x:v>
+      </x:c>
+      <x:c r="D518" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E518" s="10" t="s"/>
+      <x:c r="F518" s="2"/>
+      <x:c r="G518" s="10" t="s">
+        <x:v>1606</x:v>
+      </x:c>
+      <x:c r="H518" s="10" t="s">
+        <x:v>1607</x:v>
+      </x:c>
+      <x:c r="I518" s="10" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="J518" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K518" s="10" t="s">
+        <x:v>1605</x:v>
+      </x:c>
+      <x:c r="L518" s="10" t="s">
+        <x:v>1608</x:v>
+      </x:c>
+      <x:c r="M518" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" hidden="0">
+      <x:c r="A519">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="B519" s="2">
+        <x:v>46169.6696527778</x:v>
+      </x:c>
+      <x:c r="C519" s="2">
+        <x:v>46169.6805092593</x:v>
+      </x:c>
+      <x:c r="D519" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E519" s="10" t="s"/>
+      <x:c r="F519" s="2"/>
+      <x:c r="G519" s="10" t="s">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="H519" s="10" t="s">
+        <x:v>1610</x:v>
+      </x:c>
+      <x:c r="I519" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J519" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K519" s="10" t="s">
+        <x:v>1482</x:v>
+      </x:c>
+      <x:c r="L519" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M519" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" hidden="0">
+      <x:c r="A520">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B520" s="2">
+        <x:v>46169.7517013889</x:v>
+      </x:c>
+      <x:c r="C520" s="2">
+        <x:v>46169.7535648148</x:v>
+      </x:c>
+      <x:c r="D520" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E520" s="10" t="s"/>
+      <x:c r="F520" s="2"/>
+      <x:c r="G520" s="10" t="s">
+        <x:v>1611</x:v>
+      </x:c>
+      <x:c r="H520" s="10" t="s">
+        <x:v>1612</x:v>
+      </x:c>
+      <x:c r="I520" s="10" t="s">
+        <x:v>1613</x:v>
+      </x:c>
+      <x:c r="J520" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K520" s="10" t="s">
+        <x:v>1571</x:v>
+      </x:c>
+      <x:c r="L520" s="10" t="s">
+        <x:v>1614</x:v>
+      </x:c>
+      <x:c r="M520" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" hidden="0">
+      <x:c r="A521">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="B521" s="2">
+        <x:v>46169.9515856481</x:v>
+      </x:c>
+      <x:c r="C521" s="2">
+        <x:v>46169.9552314815</x:v>
+      </x:c>
+      <x:c r="D521" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E521" s="10" t="s"/>
+      <x:c r="F521" s="2"/>
+      <x:c r="G521" s="10" t="s">
+        <x:v>1615</x:v>
+      </x:c>
+      <x:c r="H521" s="10" t="s">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="I521" s="10" t="s">
+        <x:v>1617</x:v>
+      </x:c>
+      <x:c r="J521" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K521" s="10" t="s">
+        <x:v>1375</x:v>
+      </x:c>
+      <x:c r="L521" s="10" t="s">
+        <x:v>1618</x:v>
+      </x:c>
+      <x:c r="M521" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" hidden="0">
+      <x:c r="A522">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="B522" s="2">
+        <x:v>46169.9570717593</x:v>
+      </x:c>
+      <x:c r="C522" s="2">
+        <x:v>46169.9598842593</x:v>
+      </x:c>
+      <x:c r="D522" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E522" s="10" t="s"/>
+      <x:c r="F522" s="2"/>
+      <x:c r="G522" s="10" t="s">
+        <x:v>1619</x:v>
+      </x:c>
+      <x:c r="H522" s="10" t="s">
+        <x:v>1620</x:v>
+      </x:c>
+      <x:c r="I522" s="10" t="s">
+        <x:v>1617</x:v>
+      </x:c>
+      <x:c r="J522" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K522" s="10" t="s">
+        <x:v>1375</x:v>
+      </x:c>
+      <x:c r="L522" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M522" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" hidden="0">
+      <x:c r="A523">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="B523" s="2">
+        <x:v>46169.9732407407</x:v>
+      </x:c>
+      <x:c r="C523" s="2">
+        <x:v>46169.9744444444</x:v>
+      </x:c>
+      <x:c r="D523" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E523" s="10" t="s"/>
+      <x:c r="F523" s="2"/>
+      <x:c r="G523" s="10" t="s">
+        <x:v>1621</x:v>
+      </x:c>
+      <x:c r="H523" s="10" t="s">
+        <x:v>1622</x:v>
+      </x:c>
+      <x:c r="I523" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J523" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K523" s="10" t="s">
+        <x:v>1623</x:v>
+      </x:c>
+      <x:c r="L523" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M523" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" hidden="0">
+      <x:c r="A524">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="B524" s="2">
+        <x:v>46170.062662037</x:v>
+      </x:c>
+      <x:c r="C524" s="2">
+        <x:v>46170.0638888889</x:v>
+      </x:c>
+      <x:c r="D524" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E524" s="10" t="s"/>
+      <x:c r="F524" s="2"/>
+      <x:c r="G524" s="10" t="s">
+        <x:v>1624</x:v>
+      </x:c>
+      <x:c r="H524" s="10" t="s">
+        <x:v>1625</x:v>
+      </x:c>
+      <x:c r="I524" s="10" t="s">
+        <x:v>1601</x:v>
+      </x:c>
+      <x:c r="J524" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K524" s="10" t="s">
+        <x:v>1602</x:v>
+      </x:c>
+      <x:c r="L524" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M524" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" hidden="0">
+      <x:c r="A525">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="B525" s="2">
+        <x:v>46170.0691898148</x:v>
+      </x:c>
+      <x:c r="C525" s="2">
+        <x:v>46170.0698148148</x:v>
+      </x:c>
+      <x:c r="D525" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E525" s="10" t="s"/>
+      <x:c r="F525" s="2"/>
+      <x:c r="G525" s="10" t="s">
+        <x:v>1626</x:v>
+      </x:c>
+      <x:c r="H525" s="10" t="s">
+        <x:v>1627</x:v>
+      </x:c>
+      <x:c r="I525" s="10" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="J525" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K525" s="10" t="s">
+        <x:v>1602</x:v>
+      </x:c>
+      <x:c r="L525" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M525" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" hidden="0">
+      <x:c r="A526">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="B526" s="2">
+        <x:v>46170.081099537</x:v>
+      </x:c>
+      <x:c r="C526" s="2">
+        <x:v>46170.0825810185</x:v>
+      </x:c>
+      <x:c r="D526" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E526" s="10" t="s"/>
+      <x:c r="F526" s="2"/>
+      <x:c r="G526" s="10" t="s">
+        <x:v>1628</x:v>
+      </x:c>
+      <x:c r="H526" s="10" t="s">
+        <x:v>1629</x:v>
+      </x:c>
+      <x:c r="I526" s="10" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J526" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K526" s="10" t="s">
+        <x:v>1602</x:v>
+      </x:c>
+      <x:c r="L526" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M526" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" hidden="0">
+      <x:c r="A527">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B527" s="2">
+        <x:v>46170.1441435185</x:v>
+      </x:c>
+      <x:c r="C527" s="2">
+        <x:v>46170.1449421296</x:v>
+      </x:c>
+      <x:c r="D527" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E527" s="10" t="s"/>
+      <x:c r="F527" s="2"/>
+      <x:c r="G527" s="10" t="s">
+        <x:v>1630</x:v>
+      </x:c>
+      <x:c r="H527" s="10" t="s">
+        <x:v>1631</x:v>
+      </x:c>
+      <x:c r="I527" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J527" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K527" s="10" t="s">
+        <x:v>1632</x:v>
+      </x:c>
+      <x:c r="L527" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M527" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528" hidden="0">
+      <x:c r="A528">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="B528" s="2">
+        <x:v>46170.1449768519</x:v>
+      </x:c>
+      <x:c r="C528" s="2">
+        <x:v>46170.1455092593</x:v>
+      </x:c>
+      <x:c r="D528" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E528" s="10" t="s"/>
+      <x:c r="F528" s="2"/>
+      <x:c r="G528" s="10" t="s">
+        <x:v>1633</x:v>
+      </x:c>
+      <x:c r="H528" s="10" t="s">
+        <x:v>1634</x:v>
+      </x:c>
+      <x:c r="I528" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J528" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K528" s="10" t="s">
+        <x:v>1635</x:v>
+      </x:c>
+      <x:c r="L528" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M528" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" hidden="0">
+      <x:c r="A529">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="B529" s="2">
+        <x:v>46170.2228819444</x:v>
+      </x:c>
+      <x:c r="C529" s="2">
+        <x:v>46170.2302083333</x:v>
+      </x:c>
+      <x:c r="D529" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E529" s="10" t="s"/>
+      <x:c r="F529" s="2"/>
+      <x:c r="G529" s="10" t="s">
+        <x:v>1636</x:v>
+      </x:c>
+      <x:c r="H529" s="10" t="s">
+        <x:v>1637</x:v>
+      </x:c>
+      <x:c r="I529" s="10" t="s">
+        <x:v>1638</x:v>
+      </x:c>
+      <x:c r="J529" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K529" s="10" t="s">
+        <x:v>1491</x:v>
+      </x:c>
+      <x:c r="L529" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M529" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" hidden="0">
+      <x:c r="A530">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B530" s="2">
+        <x:v>46170.2324305556</x:v>
+      </x:c>
+      <x:c r="C530" s="2">
+        <x:v>46170.2331712963</x:v>
+      </x:c>
+      <x:c r="D530" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E530" s="10" t="s"/>
+      <x:c r="F530" s="2"/>
+      <x:c r="G530" s="10" t="s">
+        <x:v>1639</x:v>
+      </x:c>
+      <x:c r="H530" s="10" t="s">
+        <x:v>1640</x:v>
+      </x:c>
+      <x:c r="I530" s="10" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J530" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K530" s="10" t="s">
+        <x:v>1491</x:v>
+      </x:c>
+      <x:c r="L530" s="10" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="M530" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" hidden="0">
+      <x:c r="A531">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="B531" s="2">
+        <x:v>46170.3038194444</x:v>
+      </x:c>
+      <x:c r="C531" s="2">
+        <x:v>46170.3055439815</x:v>
+      </x:c>
+      <x:c r="D531" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E531" s="10" t="s"/>
+      <x:c r="F531" s="2"/>
+      <x:c r="G531" s="10" t="s">
+        <x:v>1641</x:v>
+      </x:c>
+      <x:c r="H531" s="10" t="s">
+        <x:v>1642</x:v>
+      </x:c>
+      <x:c r="I531" s="10" t="s">
+        <x:v>1397</x:v>
+      </x:c>
+      <x:c r="J531" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K531" s="10" t="s">
+        <x:v>1580</x:v>
+      </x:c>
+      <x:c r="L531" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M531" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" hidden="0">
+      <x:c r="A532">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="B532" s="2">
+        <x:v>46170.3372106481</x:v>
+      </x:c>
+      <x:c r="C532" s="2">
+        <x:v>46170.3378587963</x:v>
+      </x:c>
+      <x:c r="D532" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E532" s="10" t="s"/>
+      <x:c r="F532" s="2"/>
+      <x:c r="G532" s="10" t="s">
+        <x:v>1643</x:v>
+      </x:c>
+      <x:c r="H532" s="10" t="s">
+        <x:v>1644</x:v>
+      </x:c>
+      <x:c r="I532" s="10" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="J532" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K532" s="10" t="s">
+        <x:v>1645</x:v>
+      </x:c>
+      <x:c r="L532" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M532" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" hidden="0">
+      <x:c r="A533">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="B533" s="2">
+        <x:v>46170.360474537</x:v>
+      </x:c>
+      <x:c r="C533" s="2">
+        <x:v>46170.361412037</x:v>
+      </x:c>
+      <x:c r="D533" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E533" s="10" t="s"/>
+      <x:c r="F533" s="2"/>
+      <x:c r="G533" s="10" t="s">
+        <x:v>1646</x:v>
+      </x:c>
+      <x:c r="H533" s="10" t="s">
+        <x:v>1647</x:v>
+      </x:c>
+      <x:c r="I533" s="10" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J533" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K533" s="10" t="s">
+        <x:v>1645</x:v>
+      </x:c>
+      <x:c r="L533" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M533" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" hidden="0">
+      <x:c r="A534">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="B534" s="2">
+        <x:v>46170.3654976852</x:v>
+      </x:c>
+      <x:c r="C534" s="2">
+        <x:v>46170.3666550926</x:v>
+      </x:c>
+      <x:c r="D534" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E534" s="10" t="s"/>
+      <x:c r="F534" s="2"/>
+      <x:c r="G534" s="10" t="s">
+        <x:v>1648</x:v>
+      </x:c>
+      <x:c r="H534" s="10" t="s">
+        <x:v>1649</x:v>
+      </x:c>
+      <x:c r="I534" s="10" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J534" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K534" s="10" t="s">
+        <x:v>1645</x:v>
+      </x:c>
+      <x:c r="L534" s="10" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="M534" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" hidden="0">
+      <x:c r="A535">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B535" s="2">
+        <x:v>46170.3720717593</x:v>
+      </x:c>
+      <x:c r="C535" s="2">
+        <x:v>46170.3725115741</x:v>
+      </x:c>
+      <x:c r="D535" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E535" s="10" t="s"/>
+      <x:c r="F535" s="2"/>
+      <x:c r="G535" s="10" t="s">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="H535" s="10" t="s">
+        <x:v>1651</x:v>
+      </x:c>
+      <x:c r="I535" s="10" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J535" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K535" s="10" t="s">
+        <x:v>1645</x:v>
+      </x:c>
+      <x:c r="L535" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M535" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536" hidden="0">
+      <x:c r="A536">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="B536" s="2">
+        <x:v>46170.3815509259</x:v>
+      </x:c>
+      <x:c r="C536" s="2">
+        <x:v>46170.3825925926</x:v>
+      </x:c>
+      <x:c r="D536" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E536" s="10" t="s"/>
+      <x:c r="F536" s="2"/>
+      <x:c r="G536" s="10" t="s">
+        <x:v>1652</x:v>
+      </x:c>
+      <x:c r="H536" s="10" t="s">
+        <x:v>1653</x:v>
+      </x:c>
+      <x:c r="I536" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J536" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K536" s="10" t="s">
+        <x:v>1654</x:v>
+      </x:c>
+      <x:c r="L536" s="10" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="M536" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" hidden="0">
+      <x:c r="A537">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B537" s="2">
+        <x:v>46170.3846180556</x:v>
+      </x:c>
+      <x:c r="C537" s="2">
+        <x:v>46170.3851041667</x:v>
+      </x:c>
+      <x:c r="D537" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E537" s="10" t="s"/>
+      <x:c r="F537" s="2"/>
+      <x:c r="G537" s="10" t="s">
+        <x:v>1655</x:v>
+      </x:c>
+      <x:c r="H537" s="10" t="s">
+        <x:v>1656</x:v>
+      </x:c>
+      <x:c r="I537" s="10" t="s">
+        <x:v>1601</x:v>
+      </x:c>
+      <x:c r="J537" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K537" s="10" t="s">
+        <x:v>1602</x:v>
+      </x:c>
+      <x:c r="L537" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M537" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538" hidden="0">
+      <x:c r="A538">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="B538" s="2">
+        <x:v>46170.4193402778</x:v>
+      </x:c>
+      <x:c r="C538" s="2">
+        <x:v>46170.4254861111</x:v>
+      </x:c>
+      <x:c r="D538" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E538" s="10" t="s"/>
+      <x:c r="F538" s="2"/>
+      <x:c r="G538" s="10" t="s">
+        <x:v>1657</x:v>
+      </x:c>
+      <x:c r="H538" s="10" t="s">
+        <x:v>1658</x:v>
+      </x:c>
+      <x:c r="I538" s="10" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J538" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K538" s="10" t="s">
+        <x:v>1659</x:v>
+      </x:c>
+      <x:c r="L538" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M538" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" hidden="0">
+      <x:c r="A539">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="B539" s="2">
+        <x:v>46170.4605787037</x:v>
+      </x:c>
+      <x:c r="C539" s="2">
+        <x:v>46170.4620601852</x:v>
+      </x:c>
+      <x:c r="D539" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E539" s="10" t="s"/>
+      <x:c r="F539" s="2"/>
+      <x:c r="G539" s="10" t="s">
+        <x:v>1660</x:v>
+      </x:c>
+      <x:c r="H539" s="10" t="s">
+        <x:v>1661</x:v>
+      </x:c>
+      <x:c r="I539" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J539" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K539" s="10" t="s">
+        <x:v>1654</x:v>
+      </x:c>
+      <x:c r="L539" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M539" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" hidden="0">
+      <x:c r="A540">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="B540" s="2">
+        <x:v>46170.4673032407</x:v>
+      </x:c>
+      <x:c r="C540" s="2">
+        <x:v>46170.4689699074</x:v>
+      </x:c>
+      <x:c r="D540" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E540" s="10" t="s"/>
+      <x:c r="F540" s="2"/>
+      <x:c r="G540" s="10" t="s">
+        <x:v>1662</x:v>
+      </x:c>
+      <x:c r="H540" s="10" t="s">
+        <x:v>1663</x:v>
+      </x:c>
+      <x:c r="I540" s="10" t="s"/>
+      <x:c r="J540" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K540" s="10" t="s">
+        <x:v>1654</x:v>
+      </x:c>
+      <x:c r="L540" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M540" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" hidden="0">
+      <x:c r="A541">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B541" s="2">
+        <x:v>46170.500150463</x:v>
+      </x:c>
+      <x:c r="C541" s="2">
+        <x:v>46170.5012962963</x:v>
+      </x:c>
+      <x:c r="D541" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E541" s="10" t="s"/>
+      <x:c r="F541" s="2"/>
+      <x:c r="G541" s="10" t="s">
+        <x:v>1664</x:v>
+      </x:c>
+      <x:c r="H541" s="10" t="s">
+        <x:v>1665</x:v>
+      </x:c>
+      <x:c r="I541" s="10" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J541" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K541" s="10" t="s">
+        <x:v>1602</x:v>
+      </x:c>
+      <x:c r="L541" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="M541" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" hidden="0">
+      <x:c r="A542">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B542" s="2">
+        <x:v>46170.5302430556</x:v>
+      </x:c>
+      <x:c r="C542" s="2">
+        <x:v>46170.5309259259</x:v>
+      </x:c>
+      <x:c r="D542" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E542" s="10" t="s"/>
+      <x:c r="F542" s="2"/>
+      <x:c r="G542" s="10" t="s">
+        <x:v>1666</x:v>
+      </x:c>
+      <x:c r="H542" s="10" t="s">
+        <x:v>849</x:v>
+      </x:c>
+      <x:c r="I542" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J542" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K542" s="10" t="s">
+        <x:v>1667</x:v>
+      </x:c>
+      <x:c r="L542" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M542" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" hidden="0">
+      <x:c r="A543">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B543" s="2">
+        <x:v>46170.5428703704</x:v>
+      </x:c>
+      <x:c r="C543" s="2">
+        <x:v>46170.5443055556</x:v>
+      </x:c>
+      <x:c r="D543" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E543" s="10" t="s"/>
+      <x:c r="F543" s="2"/>
+      <x:c r="G543" s="10" t="s">
+        <x:v>1668</x:v>
+      </x:c>
+      <x:c r="H543" s="10" t="s">
+        <x:v>1669</x:v>
+      </x:c>
+      <x:c r="I543" s="10" t="s">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="J543" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K543" s="10" t="s">
+        <x:v>1670</x:v>
+      </x:c>
+      <x:c r="L543" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M543" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" hidden="0">
+      <x:c r="A544">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="B544" s="2">
+        <x:v>46170.5857407407</x:v>
+      </x:c>
+      <x:c r="C544" s="2">
+        <x:v>46170.5861574074</x:v>
+      </x:c>
+      <x:c r="D544" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E544" s="10" t="s"/>
+      <x:c r="F544" s="2"/>
+      <x:c r="G544" s="10" t="s">
+        <x:v>1671</x:v>
+      </x:c>
+      <x:c r="H544" s="10" t="s">
+        <x:v>1672</x:v>
+      </x:c>
+      <x:c r="I544" s="10" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="J544" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K544" s="10" t="s">
+        <x:v>1673</x:v>
+      </x:c>
+      <x:c r="L544" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M544" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" hidden="0">
+      <x:c r="A545">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B545" s="2">
+        <x:v>46170.6300347222</x:v>
+      </x:c>
+      <x:c r="C545" s="2">
+        <x:v>46170.630474537</x:v>
+      </x:c>
+      <x:c r="D545" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E545" s="10" t="s"/>
+      <x:c r="F545" s="2"/>
+      <x:c r="G545" s="10" t="s">
+        <x:v>1674</x:v>
+      </x:c>
+      <x:c r="H545" s="10" t="s">
+        <x:v>1675</x:v>
+      </x:c>
+      <x:c r="I545" s="10" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="J545" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K545" s="10" t="s">
+        <x:v>1654</x:v>
+      </x:c>
+      <x:c r="L545" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M545" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546" hidden="0">
+      <x:c r="A546">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="B546" s="2">
+        <x:v>46170.6449884259</x:v>
+      </x:c>
+      <x:c r="C546" s="2">
+        <x:v>46170.6921875</x:v>
+      </x:c>
+      <x:c r="D546" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E546" s="10" t="s"/>
+      <x:c r="F546" s="2"/>
+      <x:c r="G546" s="10" t="s">
+        <x:v>1676</x:v>
+      </x:c>
+      <x:c r="H546" s="10" t="s">
+        <x:v>1677</x:v>
+      </x:c>
+      <x:c r="I546" s="10" t="s">
+        <x:v>1142</x:v>
+      </x:c>
+      <x:c r="J546" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K546" s="7" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="L546" s="10" t="s">
+        <x:v>1678</x:v>
+      </x:c>
+      <x:c r="M546" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" hidden="0">
+      <x:c r="A547">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="B547" s="2">
+        <x:v>46170.7122916667</x:v>
+      </x:c>
+      <x:c r="C547" s="2">
+        <x:v>46170.7128009259</x:v>
+      </x:c>
+      <x:c r="D547" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E547" s="10" t="s"/>
+      <x:c r="F547" s="2"/>
+      <x:c r="G547" s="10" t="s">
+        <x:v>1671</x:v>
+      </x:c>
+      <x:c r="H547" s="10" t="s">
+        <x:v>1672</x:v>
+      </x:c>
+      <x:c r="I547" s="10" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="J547" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K547" s="10" t="s">
+        <x:v>1673</x:v>
+      </x:c>
+      <x:c r="L547" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M547" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" hidden="0">
+      <x:c r="A548">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B548" s="2">
+        <x:v>46170.7157060185</x:v>
+      </x:c>
+      <x:c r="C548" s="2">
+        <x:v>46170.7300231481</x:v>
+      </x:c>
+      <x:c r="D548" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E548" s="10" t="s"/>
+      <x:c r="F548" s="2"/>
+      <x:c r="G548" s="10" t="s">
+        <x:v>1679</x:v>
+      </x:c>
+      <x:c r="H548" s="10" t="s">
+        <x:v>1680</x:v>
+      </x:c>
+      <x:c r="I548" s="10" t="s">
+        <x:v>1681</x:v>
+      </x:c>
+      <x:c r="J548" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K548" s="10" t="s">
+        <x:v>1682</x:v>
+      </x:c>
+      <x:c r="L548" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M548" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" hidden="0">
+      <x:c r="A549">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="B549" s="2">
+        <x:v>46170.7417824074</x:v>
+      </x:c>
+      <x:c r="C549" s="2">
+        <x:v>46170.7472916667</x:v>
+      </x:c>
+      <x:c r="D549" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E549" s="10" t="s"/>
+      <x:c r="F549" s="2"/>
+      <x:c r="G549" s="10" t="s">
+        <x:v>1683</x:v>
+      </x:c>
+      <x:c r="H549" s="10" t="s">
+        <x:v>1684</x:v>
+      </x:c>
+      <x:c r="I549" s="10" t="s">
+        <x:v>1685</x:v>
+      </x:c>
+      <x:c r="J549" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K549" s="10" t="s">
+        <x:v>1686</x:v>
+      </x:c>
+      <x:c r="L549" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M549" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550" hidden="0">
+      <x:c r="A550">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="B550" s="2">
+        <x:v>46170.7416666667</x:v>
+      </x:c>
+      <x:c r="C550" s="2">
+        <x:v>46170.7485416667</x:v>
+      </x:c>
+      <x:c r="D550" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E550" s="10" t="s"/>
+      <x:c r="F550" s="2"/>
+      <x:c r="G550" s="10" t="s">
+        <x:v>1687</x:v>
+      </x:c>
+      <x:c r="H550" s="10" t="s">
+        <x:v>1688</x:v>
+      </x:c>
+      <x:c r="I550" s="10" t="s">
+        <x:v>871</x:v>
+      </x:c>
+      <x:c r="J550" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K550" s="10" t="s">
+        <x:v>1689</x:v>
+      </x:c>
+      <x:c r="L550" s="10" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M550" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" hidden="0">
+      <x:c r="A551">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B551" s="2">
+        <x:v>46170.7475231481</x:v>
+      </x:c>
+      <x:c r="C551" s="2">
+        <x:v>46170.7486921296</x:v>
+      </x:c>
+      <x:c r="D551" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E551" s="10" t="s"/>
+      <x:c r="F551" s="2"/>
+      <x:c r="G551" s="10" t="s">
+        <x:v>1690</x:v>
+      </x:c>
+      <x:c r="H551" s="10" t="s">
+        <x:v>1691</x:v>
+      </x:c>
+      <x:c r="I551" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J551" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K551" s="10" t="s">
+        <x:v>1686</x:v>
+      </x:c>
+      <x:c r="L551" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M551" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552" hidden="0">
+      <x:c r="A552">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="B552" s="2">
+        <x:v>46170.7911805556</x:v>
+      </x:c>
+      <x:c r="C552" s="2">
+        <x:v>46170.8320717593</x:v>
+      </x:c>
+      <x:c r="D552" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E552" s="10" t="s"/>
+      <x:c r="F552" s="2"/>
+      <x:c r="G552" s="10" t="s">
+        <x:v>1692</x:v>
+      </x:c>
+      <x:c r="H552" s="10" t="s">
+        <x:v>1693</x:v>
+      </x:c>
+      <x:c r="I552" s="10" t="s">
+        <x:v>1694</x:v>
+      </x:c>
+      <x:c r="J552" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K552" s="10" t="s">
+        <x:v>1695</x:v>
+      </x:c>
+      <x:c r="L552" s="10" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="M552" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" hidden="0">
+      <x:c r="A553">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="B553" s="2">
+        <x:v>46171.094375</x:v>
+      </x:c>
+      <x:c r="C553" s="2">
+        <x:v>46171.096724537</x:v>
+      </x:c>
+      <x:c r="D553" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E553" s="10" t="s"/>
+      <x:c r="F553" s="2"/>
+      <x:c r="G553" s="10" t="s">
+        <x:v>1696</x:v>
+      </x:c>
+      <x:c r="H553" s="10" t="s">
+        <x:v>1697</x:v>
+      </x:c>
+      <x:c r="I553" s="10" t="s">
+        <x:v>1397</x:v>
+      </x:c>
+      <x:c r="J553" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K553" s="10" t="s">
+        <x:v>1580</x:v>
+      </x:c>
+      <x:c r="L553" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M553" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" hidden="0">
+      <x:c r="A554">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B554" s="2">
+        <x:v>46171.0802662037</x:v>
+      </x:c>
+      <x:c r="C554" s="2">
+        <x:v>46171.1006481481</x:v>
+      </x:c>
+      <x:c r="D554" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E554" s="10" t="s"/>
+      <x:c r="F554" s="2"/>
+      <x:c r="G554" s="10" t="s">
+        <x:v>1698</x:v>
+      </x:c>
+      <x:c r="H554" s="10" t="s">
+        <x:v>1699</x:v>
+      </x:c>
+      <x:c r="I554" s="10" t="s">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="J554" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K554" s="10" t="s">
+        <x:v>1701</x:v>
+      </x:c>
+      <x:c r="L554" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M554" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" hidden="0">
+      <x:c r="A555">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="B555" s="2">
+        <x:v>46171.1053125</x:v>
+      </x:c>
+      <x:c r="C555" s="2">
+        <x:v>46171.1059837963</x:v>
+      </x:c>
+      <x:c r="D555" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E555" s="10" t="s"/>
+      <x:c r="F555" s="2"/>
+      <x:c r="G555" s="10" t="s">
+        <x:v>1702</x:v>
+      </x:c>
+      <x:c r="H555" s="10" t="s">
+        <x:v>1703</x:v>
+      </x:c>
+      <x:c r="I555" s="10" t="s">
+        <x:v>1397</x:v>
+      </x:c>
+      <x:c r="J555" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K555" s="10" t="s">
+        <x:v>1580</x:v>
+      </x:c>
+      <x:c r="L555" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M555" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556" hidden="0">
+      <x:c r="A556">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="B556" s="2">
+        <x:v>46171.1062268519</x:v>
+      </x:c>
+      <x:c r="C556" s="2">
+        <x:v>46171.1069097222</x:v>
+      </x:c>
+      <x:c r="D556" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E556" s="10" t="s"/>
+      <x:c r="F556" s="2"/>
+      <x:c r="G556" s="10" t="s">
+        <x:v>1704</x:v>
+      </x:c>
+      <x:c r="H556" s="10" t="s">
+        <x:v>1705</x:v>
+      </x:c>
+      <x:c r="I556" s="10" t="s">
+        <x:v>1397</x:v>
+      </x:c>
+      <x:c r="J556" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K556" s="10" t="s">
+        <x:v>1580</x:v>
+      </x:c>
+      <x:c r="L556" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M556" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" hidden="0">
+      <x:c r="A557">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B557" s="2">
+        <x:v>46171.1287731481</x:v>
+      </x:c>
+      <x:c r="C557" s="2">
+        <x:v>46171.1296875</x:v>
+      </x:c>
+      <x:c r="D557" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E557" s="10" t="s"/>
+      <x:c r="F557" s="2"/>
+      <x:c r="G557" s="10" t="s">
+        <x:v>1706</x:v>
+      </x:c>
+      <x:c r="H557" s="10" t="s">
+        <x:v>1707</x:v>
+      </x:c>
+      <x:c r="I557" s="10" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J557" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K557" s="10" t="s">
+        <x:v>1645</x:v>
+      </x:c>
+      <x:c r="L557" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="M557" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" hidden="0">
+      <x:c r="A558">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="B558" s="2">
+        <x:v>46171.1369675926</x:v>
+      </x:c>
+      <x:c r="C558" s="2">
+        <x:v>46171.1375925926</x:v>
+      </x:c>
+      <x:c r="D558" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E558" s="10" t="s"/>
+      <x:c r="F558" s="2"/>
+      <x:c r="G558" s="10" t="s">
+        <x:v>1708</x:v>
+      </x:c>
+      <x:c r="H558" s="10" t="s">
+        <x:v>1709</x:v>
+      </x:c>
+      <x:c r="I558" s="10" t="s">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="J558" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K558" s="10" t="s">
+        <x:v>1710</x:v>
+      </x:c>
+      <x:c r="L558" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M558" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" hidden="0">
+      <x:c r="A559">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="B559" s="2">
+        <x:v>46171.1525694444</x:v>
+      </x:c>
+      <x:c r="C559" s="2">
+        <x:v>46171.1537152778</x:v>
+      </x:c>
+      <x:c r="D559" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E559" s="10" t="s"/>
+      <x:c r="F559" s="2"/>
+      <x:c r="G559" s="10" t="s">
+        <x:v>1711</x:v>
+      </x:c>
+      <x:c r="H559" s="10" t="s">
+        <x:v>1712</x:v>
+      </x:c>
+      <x:c r="I559" s="10" t="s">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="J559" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K559" s="10" t="s">
+        <x:v>1710</x:v>
+      </x:c>
+      <x:c r="L559" s="10" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="M559" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560" hidden="0">
+      <x:c r="A560">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="B560" s="2">
+        <x:v>46171.1671759259</x:v>
+      </x:c>
+      <x:c r="C560" s="2">
+        <x:v>46171.1678935185</x:v>
+      </x:c>
+      <x:c r="D560" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E560" s="10" t="s"/>
+      <x:c r="F560" s="2"/>
+      <x:c r="G560" s="10" t="s">
+        <x:v>1713</x:v>
+      </x:c>
+      <x:c r="H560" s="10" t="s">
+        <x:v>1714</x:v>
+      </x:c>
+      <x:c r="I560" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J560" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K560" s="10" t="s">
+        <x:v>1715</x:v>
+      </x:c>
+      <x:c r="L560" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M560" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" hidden="0">
+      <x:c r="A561">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B561" s="2">
+        <x:v>46171.1653125</x:v>
+      </x:c>
+      <x:c r="C561" s="2">
+        <x:v>46171.1685648148</x:v>
+      </x:c>
+      <x:c r="D561" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E561" s="10" t="s"/>
+      <x:c r="F561" s="2"/>
+      <x:c r="G561" s="10" t="s">
+        <x:v>1716</x:v>
+      </x:c>
+      <x:c r="H561" s="10" t="s">
+        <x:v>1717</x:v>
+      </x:c>
+      <x:c r="I561" s="10" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J561" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K561" s="10" t="s">
+        <x:v>1710</x:v>
+      </x:c>
+      <x:c r="L561" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M561" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562" hidden="0">
+      <x:c r="A562">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="B562" s="2">
+        <x:v>46171.1693402778</x:v>
+      </x:c>
+      <x:c r="C562" s="2">
+        <x:v>46171.1702662037</x:v>
+      </x:c>
+      <x:c r="D562" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E562" s="10" t="s"/>
+      <x:c r="F562" s="2"/>
+      <x:c r="G562" s="10" t="s">
+        <x:v>1718</x:v>
+      </x:c>
+      <x:c r="H562" s="10" t="s">
+        <x:v>1719</x:v>
+      </x:c>
+      <x:c r="I562" s="10" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J562" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K562" s="10" t="s">
+        <x:v>1710</x:v>
+      </x:c>
+      <x:c r="L562" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M562" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" hidden="0">
+      <x:c r="A563">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="B563" s="2">
+        <x:v>46171.1798611111</x:v>
+      </x:c>
+      <x:c r="C563" s="2">
+        <x:v>46171.1806481481</x:v>
+      </x:c>
+      <x:c r="D563" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E563" s="10" t="s"/>
+      <x:c r="F563" s="2"/>
+      <x:c r="G563" s="10" t="s">
+        <x:v>1720</x:v>
+      </x:c>
+      <x:c r="H563" s="10" t="s">
+        <x:v>1721</x:v>
+      </x:c>
+      <x:c r="I563" s="10" t="s">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="J563" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K563" s="10" t="s">
+        <x:v>1710</x:v>
+      </x:c>
+      <x:c r="L563" s="10" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="M563" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564" hidden="0">
+      <x:c r="A564">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="B564" s="2">
+        <x:v>46171.2891898148</x:v>
+      </x:c>
+      <x:c r="C564" s="2">
+        <x:v>46171.2901388889</x:v>
+      </x:c>
+      <x:c r="D564" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E564" s="10" t="s"/>
+      <x:c r="F564" s="2"/>
+      <x:c r="G564" s="10" t="s">
+        <x:v>1722</x:v>
+      </x:c>
+      <x:c r="H564" s="10" t="s">
+        <x:v>1723</x:v>
+      </x:c>
+      <x:c r="I564" s="10" t="s">
+        <x:v>1617</x:v>
+      </x:c>
+      <x:c r="J564" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K564" s="10" t="s">
+        <x:v>1724</x:v>
+      </x:c>
+      <x:c r="L564" s="10" t="s">
+        <x:v>1618</x:v>
+      </x:c>
+      <x:c r="M564" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" hidden="0">
+      <x:c r="A565">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="B565" s="2">
+        <x:v>46171.2932291667</x:v>
+      </x:c>
+      <x:c r="C565" s="2">
+        <x:v>46171.2946643519</x:v>
+      </x:c>
+      <x:c r="D565" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E565" s="10" t="s"/>
+      <x:c r="F565" s="2"/>
+      <x:c r="G565" s="10" t="s">
+        <x:v>1725</x:v>
+      </x:c>
+      <x:c r="H565" s="10" t="s">
+        <x:v>1726</x:v>
+      </x:c>
+      <x:c r="I565" s="10" t="s">
+        <x:v>1617</x:v>
+      </x:c>
+      <x:c r="J565" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K565" s="10" t="s">
+        <x:v>1727</x:v>
+      </x:c>
+      <x:c r="L565" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M565" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566" hidden="0">
+      <x:c r="A566">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="B566" s="2">
+        <x:v>46171.3218865741</x:v>
+      </x:c>
+      <x:c r="C566" s="2">
+        <x:v>46171.3230671296</x:v>
+      </x:c>
+      <x:c r="D566" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E566" s="10" t="s"/>
+      <x:c r="F566" s="2"/>
+      <x:c r="G566" s="10" t="s">
+        <x:v>1728</x:v>
+      </x:c>
+      <x:c r="H566" s="10" t="s">
+        <x:v>1729</x:v>
+      </x:c>
+      <x:c r="I566" s="10" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="J566" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K566" s="10" t="s">
+        <x:v>1689</x:v>
+      </x:c>
+      <x:c r="L566" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M566" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" hidden="0">
+      <x:c r="A567">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B567" s="2">
+        <x:v>46171.3384259259</x:v>
+      </x:c>
+      <x:c r="C567" s="2">
+        <x:v>46171.3476736111</x:v>
+      </x:c>
+      <x:c r="D567" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E567" s="10" t="s"/>
+      <x:c r="F567" s="2"/>
+      <x:c r="G567" s="10" t="s">
+        <x:v>1730</x:v>
+      </x:c>
+      <x:c r="H567" s="10" t="s">
+        <x:v>1731</x:v>
+      </x:c>
+      <x:c r="I567" s="10" t="s">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="J567" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K567" s="10" t="s">
+        <x:v>1732</x:v>
+      </x:c>
+      <x:c r="L567" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M567" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568" hidden="0">
+      <x:c r="A568">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B568" s="2">
+        <x:v>46171.3485416667</x:v>
+      </x:c>
+      <x:c r="C568" s="2">
+        <x:v>46171.3515856481</x:v>
+      </x:c>
+      <x:c r="D568" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E568" s="10" t="s"/>
+      <x:c r="F568" s="2"/>
+      <x:c r="G568" s="10" t="s">
+        <x:v>1733</x:v>
+      </x:c>
+      <x:c r="H568" s="10" t="s">
+        <x:v>1734</x:v>
+      </x:c>
+      <x:c r="I568" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J568" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K568" s="10" t="s">
+        <x:v>1732</x:v>
+      </x:c>
+      <x:c r="L568" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M568" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" hidden="0">
+      <x:c r="A569">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="B569" s="2">
+        <x:v>46171.3516435185</x:v>
+      </x:c>
+      <x:c r="C569" s="2">
+        <x:v>46171.3524074074</x:v>
+      </x:c>
+      <x:c r="D569" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E569" s="10" t="s"/>
+      <x:c r="F569" s="2"/>
+      <x:c r="G569" s="10" t="s">
+        <x:v>1735</x:v>
+      </x:c>
+      <x:c r="H569" s="10" t="s">
+        <x:v>1731</x:v>
+      </x:c>
+      <x:c r="I569" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J569" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K569" s="10" t="s">
+        <x:v>1732</x:v>
+      </x:c>
+      <x:c r="L569" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M569" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570" hidden="0">
+      <x:c r="A570">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B570" s="2">
+        <x:v>46171.3526851852</x:v>
+      </x:c>
+      <x:c r="C570" s="2">
+        <x:v>46171.3541782407</x:v>
+      </x:c>
+      <x:c r="D570" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E570" s="10" t="s"/>
+      <x:c r="F570" s="2"/>
+      <x:c r="G570" s="10" t="s">
+        <x:v>1736</x:v>
+      </x:c>
+      <x:c r="H570" s="10" t="s">
+        <x:v>1737</x:v>
+      </x:c>
+      <x:c r="I570" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J570" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K570" s="10" t="s">
+        <x:v>1732</x:v>
+      </x:c>
+      <x:c r="L570" s="10" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="M570" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" hidden="0">
+      <x:c r="A571">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B571" s="2">
+        <x:v>46171.3549537037</x:v>
+      </x:c>
+      <x:c r="C571" s="2">
+        <x:v>46171.3578125</x:v>
+      </x:c>
+      <x:c r="D571" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E571" s="10" t="s"/>
+      <x:c r="F571" s="2"/>
+      <x:c r="G571" s="10" t="s">
+        <x:v>1738</x:v>
+      </x:c>
+      <x:c r="H571" s="10" t="s">
+        <x:v>1739</x:v>
+      </x:c>
+      <x:c r="I571" s="10" t="s">
+        <x:v>1601</x:v>
+      </x:c>
+      <x:c r="J571" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K571" s="10" t="s">
+        <x:v>1571</x:v>
+      </x:c>
+      <x:c r="L571" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M571" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572" hidden="0">
+      <x:c r="A572">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="B572" s="2">
+        <x:v>46171.3735416667</x:v>
+      </x:c>
+      <x:c r="C572" s="2">
+        <x:v>46171.3742708333</x:v>
+      </x:c>
+      <x:c r="D572" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E572" s="10" t="s"/>
+      <x:c r="F572" s="2"/>
+      <x:c r="G572" s="10" t="s">
+        <x:v>1740</x:v>
+      </x:c>
+      <x:c r="H572" s="10" t="s">
+        <x:v>1741</x:v>
+      </x:c>
+      <x:c r="I572" s="10" t="s">
+        <x:v>1742</x:v>
+      </x:c>
+      <x:c r="J572" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K572" s="10" t="s">
+        <x:v>1743</x:v>
+      </x:c>
+      <x:c r="L572" s="10" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M572" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" hidden="0">
+      <x:c r="A573">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B573" s="2">
+        <x:v>46171.3928240741</x:v>
+      </x:c>
+      <x:c r="C573" s="2">
+        <x:v>46171.3933217593</x:v>
+      </x:c>
+      <x:c r="D573" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E573" s="10" t="s"/>
+      <x:c r="F573" s="2"/>
+      <x:c r="G573" s="10" t="s">
+        <x:v>1744</x:v>
+      </x:c>
+      <x:c r="H573" s="10" t="s">
+        <x:v>1745</x:v>
+      </x:c>
+      <x:c r="I573" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J573" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K573" s="10" t="s">
+        <x:v>1732</x:v>
+      </x:c>
+      <x:c r="L573" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M573" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574" hidden="0">
+      <x:c r="A574">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B574" s="2">
+        <x:v>46171.4134606481</x:v>
+      </x:c>
+      <x:c r="C574" s="2">
+        <x:v>46171.4143634259</x:v>
+      </x:c>
+      <x:c r="D574" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E574" s="10" t="s"/>
+      <x:c r="F574" s="2"/>
+      <x:c r="G574" s="10" t="s">
+        <x:v>1746</x:v>
+      </x:c>
+      <x:c r="H574" s="10" t="s">
+        <x:v>1747</x:v>
+      </x:c>
+      <x:c r="I574" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J574" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K574" s="10" t="s">
+        <x:v>1732</x:v>
+      </x:c>
+      <x:c r="L574" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M574" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" hidden="0">
+      <x:c r="A575">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="B575" s="2">
+        <x:v>46171.4240740741</x:v>
+      </x:c>
+      <x:c r="C575" s="2">
+        <x:v>46171.4251273148</x:v>
+      </x:c>
+      <x:c r="D575" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E575" s="10" t="s"/>
+      <x:c r="F575" s="2"/>
+      <x:c r="G575" s="10" t="s">
+        <x:v>1748</x:v>
+      </x:c>
+      <x:c r="H575" s="10" t="s">
+        <x:v>1749</x:v>
+      </x:c>
+      <x:c r="I575" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J575" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K575" s="10" t="s">
+        <x:v>1750</x:v>
+      </x:c>
+      <x:c r="L575" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M575" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576" hidden="0">
+      <x:c r="A576">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="B576" s="2">
+        <x:v>46171.4273611111</x:v>
+      </x:c>
+      <x:c r="C576" s="2">
+        <x:v>46171.4290856481</x:v>
+      </x:c>
+      <x:c r="D576" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E576" s="10" t="s"/>
+      <x:c r="F576" s="2"/>
+      <x:c r="G576" s="10" t="s">
+        <x:v>1751</x:v>
+      </x:c>
+      <x:c r="H576" s="10" t="s">
+        <x:v>1752</x:v>
+      </x:c>
+      <x:c r="I576" s="10" t="s">
+        <x:v>1753</x:v>
+      </x:c>
+      <x:c r="J576" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K576" s="10" t="s">
+        <x:v>1754</x:v>
+      </x:c>
+      <x:c r="L576" s="10" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="M576" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R974ee14605e349cd"/>
+    <x:tablePart r:id="Raa0c61b7a5e04b26"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096F5A18ADBDD9E4D8F394AC4B3466405" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e59e3e6d23932d1d7525b22f7d7f3a7d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" xmlns:ns3="76b4ec34-0f89-435f-928a-b7c414764614" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d88756df8cabe05f154bf6d416a348" ns2:_="" ns3:_="">
+    <xsd:import namespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb"/>
+    <xsd:import namespace="76b4ec34-0f89-435f-928a-b7c414764614"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ad0b2da7-f7f1-4ade-bc4d-78491eef27d0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="76b4ec34-0f89-435f-928a-b7c414764614" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c696ee1e-5302-4bbd-96b7-dbc90bffde0f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="76b4ec34-0f89-435f-928a-b7c414764614">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="76b4ec34-0f89-435f-928a-b7c414764614" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E70C458A-B127-4B5B-BCA6-208F02BC594D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2AA043A-46FE-4B9C-A7E5-8C0C6478B57E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F64B5A0E-8E01-4101-BEA0-4092991DD4AD}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1755">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="2079">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -5290,6 +5290,978 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">EySA (Epidemiology and Enviromental Health)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lars Erik Gangsei</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lars.erik.gangsei@vetinst.no</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Norway</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Norwegian Veterinary Institute</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Adley Dityo Valentinus Putra</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">adley@prevalensi.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Prevalensi Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Albertus Teguh Muljono</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">albert@prevalensi.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Professional;Animal Health Scientist;Veterinary Epidemiologist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nur Alam</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">alank@prevalensi.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Researcher;Software Engineer;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kyrre Kausrud</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">kyrre.kausrud@vetinst.no</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Professional;Biologist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mohamad Fikih Amar Dani</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">fikih@prevalensi.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Professional;Software Engineer;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Khurshid Ahmad </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">khurshidahmad1965@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Huzaifa </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Syed M. Jamal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jamal115@yahoo.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Afzal </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">drmafzal1953@yahoo.com </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Masood Akhtar </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">masood61@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Don't know exactly </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal Health Scientist;University Professor/Vice Chancellor at University of Baltistan Skardu-Pakistan ;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Trishang Udhwani</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">trishang.udhwani@vetinst.no</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Afzal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">drmafzal1953@yahoo.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Individual</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pablo Ibanez Porras</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pablo.ibanez@inia.csic.es</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graduate Student;Mathematical modeling;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Joël Durant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Joel.marcel.durant@vetinst.no</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Fiaz Qamar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">fiaz.qamar12@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CVAS Jhang</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Faria Imran</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dr.fariaimran@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graduate Student;Professional;Animal Health Scientist;Researcher;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Teresita Suarez Noguez</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tsuarez@ed.ac.uk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The colourist</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Magnus Nygård Osnes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Magnus.Nygard.Osnes@vetinst.no</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sarah Valentin</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sarah.valentin@cirad.fr</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TETIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Carolina Maciel </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">carolina.maciel@sussex.ac.uk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SafeTrade Analytics</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Haroon AKBAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">drharoonakbar@uvas.edu.pk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pakistani Disease Investigators</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Animal Health Scientist;Researcher;Veterinarian-Immunologist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vishnudas Kulangara Veettil</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vishnudasveettil@tamu.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Grazers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Trang Thi Thuy La</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lathuytrang.ftu@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ali Abouelazm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">aliazm419@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Arnav Mehta </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">arnavbps2007@tamu.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tan Li Ying</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TAN_Li_Ying@nparks.gov.sg</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Salma Ferchichi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ferchichi_salma@yahoo.fr</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tunisia </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TANIT-EI </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Scientist;Researcher;Veterinary epidemiologist ;Graduate Student;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Olivia Gibson</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ogibson@uoguelph.ca</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Quant Queens</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Moin Iqbal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">drmoiniqbal@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N/A currently no team,  At this moment I do not have a team. However, I am fully willing to be engaged in a team either within my country or internationally and I will actively contribute to the datathon. Please consider me available for team matching.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Animal Health Scientist;Veterinary Epidemiologist/ Public Health Specialist/ One Health Consultant;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">salma.ferchichi85@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Scientist;Researcher;Graduate Student;Veterinary epidemiologist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Marie Hermelienne Volasoa </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hm.volasoa@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Madagascar </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Graduate Student;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vinay Mase</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vrmase@ucdavis.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Davis Bee Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Christopher Vuong</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">chtvuong@ucdavis.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Marco Gonzalez Bernal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">marco.gonzalez.i@senasica.gob.mx</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Miguel Angel Rodriguez Ramirez</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">miguelescuelaros23@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">News Brakers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Hannah Schuster</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hannah.schuster@wu.ac.at</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pranav Shrikant Kulkarni</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pskul@ucdavis.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(1) Early Birds; (2) Davis Bee Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ayushi Gupta</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ayugupta@ucdavis.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Early Birds</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Krzysztof Tomczak</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">krzysztof.tomczak@outbreakguard.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">United Kingdom (Poland originally)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Outbreak Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;veterinary surgeon, entrepreneur ;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Juan Vicente Bogado Machuca</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">juan.vicente.bm@pol.una.py</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Paraguay</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WILDCAST</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Imelda Trejo Lorenzo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">imelda@matmor.unam.mx</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Andie Jian</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ahjian@ucdavis.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kendra Yap Kah Siew</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">kendrayks@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">María Albertina Argueta Escobar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tinargueta@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Researcher;Global Health Security professional with experience in intersectoral work under the One Health approach, including coordination across human, animal, and environmental health sectors.;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Jesper Chia-Hui Hsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hsu00124@umn.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CAHFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Hassan Mushtaq </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Hassan.mushtaq@uvas.edu.pk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">UVAS, Lahore </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lee Yen Shen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">leeyenshen@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rafaela Araújo </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">rafaela.araujo@elancoah.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Umar Farooq</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Umarfarooq.9001@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Biostatistician and Public Health expert;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ng Wan Ting Eunice</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">eunicengwt@u.nus.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Asif </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">asif1.nibge@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">One Health Pakistan </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vera Loh</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">veraxloh@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rabia Ali</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">rabipkmsn@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DataPaws</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Glory Nwakaogor </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">nwakaglory@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Savor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Professional;Graduate Student;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sree Harshini Satheeskumar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">harshisrsk@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Matilde de Carvalho Noverça Rebelo Lages </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">matilderebelolages@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sweet Rice</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Hamid Irshad </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hamidirshad@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">National Reference Lab for Poultry Diseases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Debra Okeh</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">debraokeh@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Savor </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Elohor Okpako</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">okpakoelohor53@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Braynstormers </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">João Romero</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">joao.fps.romero@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Maria Leonor Lobo da Silveira Forjaz da Costa Jorge</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">leonorcostajorge21@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Undergraduate Student;Graduate Student;Professional;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Marcelo Luís Barros</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mlb.vet@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Epitome </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Naveed ul Haque</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">muhammad.naveed@uvas.edu.pk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Umer, Uzair, and Naveed</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Anjasoa Randrianarijaona</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">anjasoarandri@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Arnab Paul Choudhury</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">arnabpchoudhury@viksitlabs.in</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DeArOH</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr. Debpriyo Kumar Dey</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dkdeyvet@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Inês dos Santos Cascais</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ines.s.cascais@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Youssef Mahdoubi</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mahdoubi.youssef@usms.ac.ma</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Morocco</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AtlasNlp</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Evgeniya Ruzmetova</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">evg.ruzmetova@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Russia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Woah! They slay</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal Health Scientist;Graduate Student;Professional;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Evgenii Kramarev</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">genijj1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Olutoberu Princewill Fiyinfoluwa </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">olutoberuprincewill@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The BioPioneers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Daniella do Nascimento Schettino </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">daniellaschettino@indea.mt.gov.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Epitome</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Animal Health Scientist;Professional;Researcher;Official Veterinarian;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lee Yuen Kei</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lkei7530@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nicolas cardenas </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ncesped@ncsu.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Anna Beatriz Oliveira Rodrigues </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">anna.driguess@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Megha Poyyara Saiju</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mpoyyarasaiju@tamu.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Barun Kumar Sharma</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">barunvet@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Xiaomei Yue</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">yxm_zoey@163.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">China</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Andrew Breed</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">andrew.breed@aff.gov.au </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Imran Rashid</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">imran.rashid@uvas.edu.pk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tick Surveillance Force</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Hafiza Joham Asghar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hafizajohamasghar@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ayka Imran</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">aykaimran28@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cocian Adrian Ionut</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">adrian.cocian@usamvcluj.ro</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Romania, Europe</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Early birds</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Jawad Hussain</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mnjawadhussain@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ANIMUSE Forecasters</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Undergraduate Student;Animal Health Scientist;Data Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Abdul Manan </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">abdulmanan5087@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rodrigo Gonçalves da Rosa Correia da Silva</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">rodrigo.silva742001@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lisbon, Portugal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Wasif Gulzar </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">gulzarmuhammadwasif@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ANIMUSE Forecasters </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Undergraduate Student;Researcher;Animal Health Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr. Muhammad Yasir</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mohmdxasir@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PakBio</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Muhammad Yar Sobhan Qadir</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sobhanqadir@yahoo.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Team GAIPAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Andrea Tonelli </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">andrea.tonelli@uniroma1.it</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BGCLab</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vladimir Morozov</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vladimv.morozov@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Spain, Barcelona</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Anamaria Páez Capador </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">anamapaezcapador@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Researcher;Undergraduate Student;Graduate Student;Data Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Naomi Daniela Mora Jaramillo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">naomi26999@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ecuador</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Eleftherios Meletis</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">emeletis@outlook.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Greece</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Carmen Ross </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Carross@ucdavis.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sarmad Nawaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sarmadnawaz08@outlook.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Vet Phone : Davetfone</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aneeqa Sardar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">aneeqasardar@gmail.om</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tick Surveillance Force </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Davetfone</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Seemab Mehmood </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">seemabmehmood26@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sara Babo Martins</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">S.babomartins@ed.ac.uk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sweet Tive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Daniel Magalhães Lima</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">daniel.magalhaes.lima@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Animal Health Scientist;Data Scientist;Epidemiologist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pranav Pandit</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pspandit@ucdavis.edu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1) Early Birds; 2) Davis Bee Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zoe Bienkiewicz</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">zoebienkiewicz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Woah! they slay</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zahratul Jannah </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">zahratulzarjan175@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Veterinary Public Health </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fresh graduate as a veterinarian ;Animal Health Scientist;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Haseeb Raza</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">haseebraza.hr13@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Felipe Álvaro de Aguiar Chaves</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">felipeaguiarchaves@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BraLBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zharko Stojmanovski</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">zarkostojmanovski@yahoo.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kumanovci</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;official veterinarian;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Adedayo Odukoya </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Odukoyaa787@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Emmanuel Adamolekun</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">adamolekunoluwaseyi@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">One Health Vanguard</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">José Daniel Hernán Conejeros Pavez</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jo.conejeros@gmail.com </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AOHL: Andes OneHealth Lab</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nicohole Atero</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">naatero@uc.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Chile </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Magdalena Gatsch Bezanilla</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mgatsch@udd.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Benjamín Diethelm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bmdiethelm@uc.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Chile - Escocia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mauricio Fuentes Allende</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mauricio.fuentes@sag.gob.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Professional;Animal Health Scientist;Official Veterinarian of the Agricultural and Livestock Service (SAG);</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">José Herrera Rodríguez</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jose.herrera@sag.gob.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Undergraduate Student;Professional;Animal Health Scientist;Official Veterinarian of the Agricultural and Livestock Service (SAG);</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The NewsBreakers</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -5386,8 +6358,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M576" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:M576"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M703" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:M703"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -27028,304 +28000,4708 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="577" hidden="0">
+      <x:c r="A577">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B577" s="2">
+        <x:v>46171.452337963</x:v>
+      </x:c>
+      <x:c r="C577" s="2">
+        <x:v>46171.4559953704</x:v>
+      </x:c>
+      <x:c r="D577" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E577" s="10" t="s"/>
+      <x:c r="F577" s="2"/>
+      <x:c r="G577" s="10" t="s">
+        <x:v>1755</x:v>
+      </x:c>
+      <x:c r="H577" s="10" t="s">
+        <x:v>1756</x:v>
+      </x:c>
+      <x:c r="I577" s="10" t="s">
+        <x:v>1757</x:v>
+      </x:c>
+      <x:c r="J577" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K577" s="10" t="s">
+        <x:v>1758</x:v>
+      </x:c>
+      <x:c r="L577" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M577" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578" hidden="0">
+      <x:c r="A578">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="B578" s="2">
+        <x:v>46171.4484606481</x:v>
+      </x:c>
+      <x:c r="C578" s="2">
+        <x:v>46171.4572337963</x:v>
+      </x:c>
+      <x:c r="D578" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E578" s="10" t="s"/>
+      <x:c r="F578" s="2"/>
+      <x:c r="G578" s="10" t="s">
+        <x:v>1759</x:v>
+      </x:c>
+      <x:c r="H578" s="10" t="s">
+        <x:v>1760</x:v>
+      </x:c>
+      <x:c r="I578" s="10" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J578" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K578" s="10" t="s">
+        <x:v>1761</x:v>
+      </x:c>
+      <x:c r="L578" s="10" t="s">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="M578" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579" hidden="0">
+      <x:c r="A579">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="B579" s="2">
+        <x:v>46171.4579050926</x:v>
+      </x:c>
+      <x:c r="C579" s="2">
+        <x:v>46171.4601967593</x:v>
+      </x:c>
+      <x:c r="D579" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E579" s="10" t="s"/>
+      <x:c r="F579" s="2"/>
+      <x:c r="G579" s="10" t="s">
+        <x:v>1762</x:v>
+      </x:c>
+      <x:c r="H579" s="10" t="s">
+        <x:v>1763</x:v>
+      </x:c>
+      <x:c r="I579" s="10" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J579" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K579" s="10" t="s">
+        <x:v>1761</x:v>
+      </x:c>
+      <x:c r="L579" s="10" t="s">
+        <x:v>1764</x:v>
+      </x:c>
+      <x:c r="M579" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580" hidden="0">
+      <x:c r="A580">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="B580" s="2">
+        <x:v>46171.4602314815</x:v>
+      </x:c>
+      <x:c r="C580" s="2">
+        <x:v>46171.4621990741</x:v>
+      </x:c>
+      <x:c r="D580" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E580" s="10" t="s"/>
+      <x:c r="F580" s="2"/>
+      <x:c r="G580" s="10" t="s">
+        <x:v>1765</x:v>
+      </x:c>
+      <x:c r="H580" s="10" t="s">
+        <x:v>1766</x:v>
+      </x:c>
+      <x:c r="I580" s="10" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J580" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K580" s="10" t="s">
+        <x:v>1761</x:v>
+      </x:c>
+      <x:c r="L580" s="10" t="s">
+        <x:v>1767</x:v>
+      </x:c>
+      <x:c r="M580" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581" hidden="0">
+      <x:c r="A581">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="B581" s="2">
+        <x:v>46171.4680671296</x:v>
+      </x:c>
+      <x:c r="C581" s="2">
+        <x:v>46171.4691319444</x:v>
+      </x:c>
+      <x:c r="D581" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E581" s="10" t="s"/>
+      <x:c r="F581" s="2"/>
+      <x:c r="G581" s="10" t="s">
+        <x:v>1768</x:v>
+      </x:c>
+      <x:c r="H581" s="10" t="s">
+        <x:v>1769</x:v>
+      </x:c>
+      <x:c r="I581" s="10" t="s">
+        <x:v>1757</x:v>
+      </x:c>
+      <x:c r="J581" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K581" s="10" t="s">
+        <x:v>1758</x:v>
+      </x:c>
+      <x:c r="L581" s="10" t="s">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="M581" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582" hidden="0">
+      <x:c r="A582">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="B582" s="2">
+        <x:v>46171.4622337963</x:v>
+      </x:c>
+      <x:c r="C582" s="2">
+        <x:v>46171.4709143518</x:v>
+      </x:c>
+      <x:c r="D582" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E582" s="10" t="s"/>
+      <x:c r="F582" s="2"/>
+      <x:c r="G582" s="10" t="s">
+        <x:v>1771</x:v>
+      </x:c>
+      <x:c r="H582" s="10" t="s">
+        <x:v>1772</x:v>
+      </x:c>
+      <x:c r="I582" s="10" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J582" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K582" s="10" t="s">
+        <x:v>1761</x:v>
+      </x:c>
+      <x:c r="L582" s="10" t="s">
+        <x:v>1773</x:v>
+      </x:c>
+      <x:c r="M582" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583" hidden="0">
+      <x:c r="A583">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="B583" s="2">
+        <x:v>46171.4813657407</x:v>
+      </x:c>
+      <x:c r="C583" s="2">
+        <x:v>46171.483287037</x:v>
+      </x:c>
+      <x:c r="D583" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E583" s="10" t="s"/>
+      <x:c r="F583" s="2"/>
+      <x:c r="G583" s="10" t="s">
+        <x:v>1774</x:v>
+      </x:c>
+      <x:c r="H583" s="10" t="s">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I583" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J583" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K583" s="10" t="s">
+        <x:v>1776</x:v>
+      </x:c>
+      <x:c r="L583" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M583" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584" hidden="0">
+      <x:c r="A584">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B584" s="2">
+        <x:v>46171.4831712963</x:v>
+      </x:c>
+      <x:c r="C584" s="2">
+        <x:v>46171.485</x:v>
+      </x:c>
+      <x:c r="D584" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E584" s="10" t="s"/>
+      <x:c r="F584" s="2"/>
+      <x:c r="G584" s="10" t="s">
+        <x:v>1777</x:v>
+      </x:c>
+      <x:c r="H584" s="10" t="s">
+        <x:v>1778</x:v>
+      </x:c>
+      <x:c r="I584" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J584" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K584" s="10" t="s">
+        <x:v>817</x:v>
+      </x:c>
+      <x:c r="L584" s="10" t="s">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c r="M584" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585" hidden="0">
+      <x:c r="A585">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="B585" s="2">
+        <x:v>46171.4943055556</x:v>
+      </x:c>
+      <x:c r="C585" s="2">
+        <x:v>46171.4960416667</x:v>
+      </x:c>
+      <x:c r="D585" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E585" s="10" t="s"/>
+      <x:c r="F585" s="2"/>
+      <x:c r="G585" s="10" t="s">
+        <x:v>1779</x:v>
+      </x:c>
+      <x:c r="H585" s="10" t="s">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="I585" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J585" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K585" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L585" s="10" t="s">
+        <x:v>725</x:v>
+      </x:c>
+      <x:c r="M585" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586" hidden="0">
+      <x:c r="A586">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B586" s="2">
+        <x:v>46171.4981018519</x:v>
+      </x:c>
+      <x:c r="C586" s="2">
+        <x:v>46171.5009143518</x:v>
+      </x:c>
+      <x:c r="D586" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E586" s="10" t="s"/>
+      <x:c r="F586" s="2"/>
+      <x:c r="G586" s="10" t="s">
+        <x:v>1781</x:v>
+      </x:c>
+      <x:c r="H586" s="10" t="s">
+        <x:v>1782</x:v>
+      </x:c>
+      <x:c r="I586" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J586" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K586" s="10" t="s">
+        <x:v>1783</x:v>
+      </x:c>
+      <x:c r="L586" s="10" t="s">
+        <x:v>1784</x:v>
+      </x:c>
+      <x:c r="M586" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587" hidden="0">
+      <x:c r="A587">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="B587" s="2">
+        <x:v>46171.5044907407</x:v>
+      </x:c>
+      <x:c r="C587" s="2">
+        <x:v>46171.5050347222</x:v>
+      </x:c>
+      <x:c r="D587" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E587" s="10" t="s"/>
+      <x:c r="F587" s="2"/>
+      <x:c r="G587" s="10" t="s">
+        <x:v>1785</x:v>
+      </x:c>
+      <x:c r="H587" s="10" t="s">
+        <x:v>1786</x:v>
+      </x:c>
+      <x:c r="I587" s="10" t="s">
+        <x:v>1757</x:v>
+      </x:c>
+      <x:c r="J587" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K587" s="10" t="s">
+        <x:v>1758</x:v>
+      </x:c>
+      <x:c r="L587" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M587" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588" hidden="0">
+      <x:c r="A588">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="B588" s="2">
+        <x:v>46171.5277199074</x:v>
+      </x:c>
+      <x:c r="C588" s="2">
+        <x:v>46171.5290972222</x:v>
+      </x:c>
+      <x:c r="D588" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E588" s="10" t="s"/>
+      <x:c r="F588" s="2"/>
+      <x:c r="G588" s="10" t="s">
+        <x:v>1787</x:v>
+      </x:c>
+      <x:c r="H588" s="10" t="s">
+        <x:v>1788</x:v>
+      </x:c>
+      <x:c r="I588" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J588" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K588" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L588" s="10" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="M588" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589" hidden="0">
+      <x:c r="A589">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B589" s="2">
+        <x:v>46171.5294791667</x:v>
+      </x:c>
+      <x:c r="C589" s="2">
+        <x:v>46171.5305671296</x:v>
+      </x:c>
+      <x:c r="D589" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E589" s="10" t="s"/>
+      <x:c r="F589" s="2"/>
+      <x:c r="G589" s="10" t="s">
+        <x:v>1777</x:v>
+      </x:c>
+      <x:c r="H589" s="10" t="s">
+        <x:v>1778</x:v>
+      </x:c>
+      <x:c r="I589" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J589" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K589" s="10" t="s">
+        <x:v>1789</x:v>
+      </x:c>
+      <x:c r="L589" s="10" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="M589" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590" hidden="0">
+      <x:c r="A590">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="B590" s="2">
+        <x:v>46171.5893402778</x:v>
+      </x:c>
+      <x:c r="C590" s="2">
+        <x:v>46171.5901851852</x:v>
+      </x:c>
+      <x:c r="D590" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E590" s="10" t="s"/>
+      <x:c r="F590" s="2"/>
+      <x:c r="G590" s="10" t="s">
+        <x:v>1790</x:v>
+      </x:c>
+      <x:c r="H590" s="10" t="s">
+        <x:v>1791</x:v>
+      </x:c>
+      <x:c r="I590" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J590" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K590" s="10" t="s">
+        <x:v>1743</x:v>
+      </x:c>
+      <x:c r="L590" s="10" t="s">
+        <x:v>1792</x:v>
+      </x:c>
+      <x:c r="M590" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591" hidden="0">
+      <x:c r="A591">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="B591" s="2">
+        <x:v>46171.5890277778</x:v>
+      </x:c>
+      <x:c r="C591" s="2">
+        <x:v>46171.5903935185</x:v>
+      </x:c>
+      <x:c r="D591" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E591" s="10" t="s"/>
+      <x:c r="F591" s="2"/>
+      <x:c r="G591" s="10" t="s">
+        <x:v>1793</x:v>
+      </x:c>
+      <x:c r="H591" s="10" t="s">
+        <x:v>1794</x:v>
+      </x:c>
+      <x:c r="I591" s="10" t="s">
+        <x:v>1757</x:v>
+      </x:c>
+      <x:c r="J591" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K591" s="10" t="s">
+        <x:v>1758</x:v>
+      </x:c>
+      <x:c r="L591" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M591" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592" hidden="0">
+      <x:c r="A592">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B592" s="2">
+        <x:v>46171.6034722222</x:v>
+      </x:c>
+      <x:c r="C592" s="2">
+        <x:v>46171.6079976852</x:v>
+      </x:c>
+      <x:c r="D592" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E592" s="10" t="s"/>
+      <x:c r="F592" s="2"/>
+      <x:c r="G592" s="10" t="s">
+        <x:v>1795</x:v>
+      </x:c>
+      <x:c r="H592" s="10" t="s">
+        <x:v>1796</x:v>
+      </x:c>
+      <x:c r="I592" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J592" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K592" s="10" t="s">
+        <x:v>1797</x:v>
+      </x:c>
+      <x:c r="L592" s="10" t="s">
+        <x:v>742</x:v>
+      </x:c>
+      <x:c r="M592" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593" hidden="0">
+      <x:c r="A593">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B593" s="2">
+        <x:v>46171.6185648148</x:v>
+      </x:c>
+      <x:c r="C593" s="2">
+        <x:v>46171.6191666667</x:v>
+      </x:c>
+      <x:c r="D593" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E593" s="10" t="s"/>
+      <x:c r="F593" s="2"/>
+      <x:c r="G593" s="10" t="s">
+        <x:v>1798</x:v>
+      </x:c>
+      <x:c r="H593" s="10" t="s">
+        <x:v>1799</x:v>
+      </x:c>
+      <x:c r="I593" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J593" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K593" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L593" s="10" t="s">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="M593" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594" hidden="0">
+      <x:c r="A594">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="B594" s="2">
+        <x:v>46171.6181365741</x:v>
+      </x:c>
+      <x:c r="C594" s="2">
+        <x:v>46171.619212963</x:v>
+      </x:c>
+      <x:c r="D594" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E594" s="10" t="s"/>
+      <x:c r="F594" s="2"/>
+      <x:c r="G594" s="10" t="s">
+        <x:v>1801</x:v>
+      </x:c>
+      <x:c r="H594" s="10" t="s">
+        <x:v>1802</x:v>
+      </x:c>
+      <x:c r="I594" s="10" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="J594" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K594" s="10" t="s">
+        <x:v>1803</x:v>
+      </x:c>
+      <x:c r="L594" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M594" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595" hidden="0">
+      <x:c r="A595">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B595" s="2">
+        <x:v>46171.6200694444</x:v>
+      </x:c>
+      <x:c r="C595" s="2">
+        <x:v>46171.6211226852</x:v>
+      </x:c>
+      <x:c r="D595" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E595" s="10" t="s"/>
+      <x:c r="F595" s="2"/>
+      <x:c r="G595" s="10" t="s">
+        <x:v>1804</x:v>
+      </x:c>
+      <x:c r="H595" s="10" t="s">
+        <x:v>1805</x:v>
+      </x:c>
+      <x:c r="I595" s="10" t="s">
+        <x:v>1757</x:v>
+      </x:c>
+      <x:c r="J595" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K595" s="10" t="s">
+        <x:v>1758</x:v>
+      </x:c>
+      <x:c r="L595" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M595" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596" hidden="0">
+      <x:c r="A596">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B596" s="2">
+        <x:v>46171.6330787037</x:v>
+      </x:c>
+      <x:c r="C596" s="2">
+        <x:v>46171.6334837963</x:v>
+      </x:c>
+      <x:c r="D596" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E596" s="10" t="s"/>
+      <x:c r="F596" s="2"/>
+      <x:c r="G596" s="10" t="s">
+        <x:v>1806</x:v>
+      </x:c>
+      <x:c r="H596" s="10" t="s">
+        <x:v>1807</x:v>
+      </x:c>
+      <x:c r="I596" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J596" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K596" s="10" t="s">
+        <x:v>1808</x:v>
+      </x:c>
+      <x:c r="L596" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M596" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597" hidden="0">
+      <x:c r="A597">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="B597" s="2">
+        <x:v>46171.6369791667</x:v>
+      </x:c>
+      <x:c r="C597" s="2">
+        <x:v>46171.6451157407</x:v>
+      </x:c>
+      <x:c r="D597" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E597" s="10" t="s"/>
+      <x:c r="F597" s="2"/>
+      <x:c r="G597" s="10" t="s">
+        <x:v>1809</x:v>
+      </x:c>
+      <x:c r="H597" s="10" t="s">
+        <x:v>1810</x:v>
+      </x:c>
+      <x:c r="I597" s="10" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="J597" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K597" s="10" t="s">
+        <x:v>1811</x:v>
+      </x:c>
+      <x:c r="L597" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M597" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598" hidden="0">
+      <x:c r="A598">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B598" s="2">
+        <x:v>46171.6435185185</x:v>
+      </x:c>
+      <x:c r="C598" s="2">
+        <x:v>46171.6459953704</x:v>
+      </x:c>
+      <x:c r="D598" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E598" s="10" t="s"/>
+      <x:c r="F598" s="2"/>
+      <x:c r="G598" s="10" t="s">
+        <x:v>1812</x:v>
+      </x:c>
+      <x:c r="H598" s="10" t="s">
+        <x:v>1813</x:v>
+      </x:c>
+      <x:c r="I598" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J598" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K598" s="10" t="s">
+        <x:v>1814</x:v>
+      </x:c>
+      <x:c r="L598" s="10" t="s">
+        <x:v>1815</x:v>
+      </x:c>
+      <x:c r="M598" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599" hidden="0">
+      <x:c r="A599">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="B599" s="2">
+        <x:v>46171.6557175926</x:v>
+      </x:c>
+      <x:c r="C599" s="2">
+        <x:v>46171.659849537</x:v>
+      </x:c>
+      <x:c r="D599" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E599" s="10" t="s"/>
+      <x:c r="F599" s="2"/>
+      <x:c r="G599" s="10" t="s">
+        <x:v>1816</x:v>
+      </x:c>
+      <x:c r="H599" s="10" t="s">
+        <x:v>1817</x:v>
+      </x:c>
+      <x:c r="I599" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J599" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K599" s="10" t="s">
+        <x:v>1818</x:v>
+      </x:c>
+      <x:c r="L599" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M599" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600" hidden="0">
+      <x:c r="A600">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="B600" s="2">
+        <x:v>46171.6613194444</x:v>
+      </x:c>
+      <x:c r="C600" s="2">
+        <x:v>46171.6616666667</x:v>
+      </x:c>
+      <x:c r="D600" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E600" s="10" t="s"/>
+      <x:c r="F600" s="2"/>
+      <x:c r="G600" s="10" t="s">
+        <x:v>1819</x:v>
+      </x:c>
+      <x:c r="H600" s="10" t="s">
+        <x:v>1820</x:v>
+      </x:c>
+      <x:c r="I600" s="10" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="J600" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K600" s="10" t="s">
+        <x:v>1818</x:v>
+      </x:c>
+      <x:c r="L600" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M600" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601" hidden="0">
+      <x:c r="A601">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B601" s="2">
+        <x:v>46171.6683796296</x:v>
+      </x:c>
+      <x:c r="C601" s="2">
+        <x:v>46171.6688541667</x:v>
+      </x:c>
+      <x:c r="D601" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E601" s="10" t="s"/>
+      <x:c r="F601" s="2"/>
+      <x:c r="G601" s="10" t="s">
+        <x:v>1821</x:v>
+      </x:c>
+      <x:c r="H601" s="10" t="s">
+        <x:v>1822</x:v>
+      </x:c>
+      <x:c r="I601" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J601" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K601" s="10" t="s">
+        <x:v>1818</x:v>
+      </x:c>
+      <x:c r="L601" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M601" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602" hidden="0">
+      <x:c r="A602">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="B602" s="2">
+        <x:v>46171.6724074074</x:v>
+      </x:c>
+      <x:c r="C602" s="2">
+        <x:v>46171.6734259259</x:v>
+      </x:c>
+      <x:c r="D602" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E602" s="10" t="s"/>
+      <x:c r="F602" s="2"/>
+      <x:c r="G602" s="10" t="s">
+        <x:v>1823</x:v>
+      </x:c>
+      <x:c r="H602" s="10" t="s">
+        <x:v>1824</x:v>
+      </x:c>
+      <x:c r="I602" s="10" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="J602" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K602" s="10" t="s">
+        <x:v>1818</x:v>
+      </x:c>
+      <x:c r="L602" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M602" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603" hidden="0">
+      <x:c r="A603">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="B603" s="2">
+        <x:v>46171.7049884259</x:v>
+      </x:c>
+      <x:c r="C603" s="2">
+        <x:v>46171.7066550926</x:v>
+      </x:c>
+      <x:c r="D603" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E603" s="10" t="s"/>
+      <x:c r="F603" s="2"/>
+      <x:c r="G603" s="10" t="s">
+        <x:v>1825</x:v>
+      </x:c>
+      <x:c r="H603" s="10" t="s">
+        <x:v>1826</x:v>
+      </x:c>
+      <x:c r="I603" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J603" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K603" s="10" t="s">
+        <x:v>1732</x:v>
+      </x:c>
+      <x:c r="L603" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M603" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604" hidden="0">
+      <x:c r="A604">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B604" s="2">
+        <x:v>46171.7161342593</x:v>
+      </x:c>
+      <x:c r="C604" s="2">
+        <x:v>46171.7177777778</x:v>
+      </x:c>
+      <x:c r="D604" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E604" s="10" t="s"/>
+      <x:c r="F604" s="2"/>
+      <x:c r="G604" s="10" t="s">
+        <x:v>1827</x:v>
+      </x:c>
+      <x:c r="H604" s="10" t="s">
+        <x:v>1828</x:v>
+      </x:c>
+      <x:c r="I604" s="10" t="s">
+        <x:v>1829</x:v>
+      </x:c>
+      <x:c r="J604" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K604" s="10" t="s">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L604" s="10" t="s">
+        <x:v>1831</x:v>
+      </x:c>
+      <x:c r="M604" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" hidden="0">
+      <x:c r="A605">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B605" s="2">
+        <x:v>46171.7159837963</x:v>
+      </x:c>
+      <x:c r="C605" s="2">
+        <x:v>46171.7196296296</x:v>
+      </x:c>
+      <x:c r="D605" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E605" s="10" t="s"/>
+      <x:c r="F605" s="2"/>
+      <x:c r="G605" s="10" t="s">
+        <x:v>1832</x:v>
+      </x:c>
+      <x:c r="H605" s="10" t="s">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="I605" s="10" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J605" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K605" s="10" t="s">
+        <x:v>1834</x:v>
+      </x:c>
+      <x:c r="L605" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M605" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606" hidden="0">
+      <x:c r="A606">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="B606" s="2">
+        <x:v>46171.7098958333</x:v>
+      </x:c>
+      <x:c r="C606" s="2">
+        <x:v>46171.7249189815</x:v>
+      </x:c>
+      <x:c r="D606" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E606" s="10" t="s"/>
+      <x:c r="F606" s="2"/>
+      <x:c r="G606" s="10" t="s">
+        <x:v>1835</x:v>
+      </x:c>
+      <x:c r="H606" s="10" t="s">
+        <x:v>1836</x:v>
+      </x:c>
+      <x:c r="I606" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J606" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K606" s="10" t="s">
+        <x:v>1837</x:v>
+      </x:c>
+      <x:c r="L606" s="10" t="s">
+        <x:v>1838</x:v>
+      </x:c>
+      <x:c r="M606" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607" hidden="0">
+      <x:c r="A607">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B607" s="2">
+        <x:v>46171.7256712963</x:v>
+      </x:c>
+      <x:c r="C607" s="2">
+        <x:v>46171.7266782407</x:v>
+      </x:c>
+      <x:c r="D607" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E607" s="10" t="s"/>
+      <x:c r="F607" s="2"/>
+      <x:c r="G607" s="10" t="s">
+        <x:v>1827</x:v>
+      </x:c>
+      <x:c r="H607" s="10" t="s">
+        <x:v>1839</x:v>
+      </x:c>
+      <x:c r="I607" s="10" t="s">
+        <x:v>1056</x:v>
+      </x:c>
+      <x:c r="J607" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K607" s="10" t="s">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L607" s="10" t="s">
+        <x:v>1840</x:v>
+      </x:c>
+      <x:c r="M607" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608" hidden="0">
+      <x:c r="A608">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="B608" s="2">
+        <x:v>46171.7680555556</x:v>
+      </x:c>
+      <x:c r="C608" s="2">
+        <x:v>46171.769375</x:v>
+      </x:c>
+      <x:c r="D608" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E608" s="10" t="s"/>
+      <x:c r="F608" s="2"/>
+      <x:c r="G608" s="10" t="s">
+        <x:v>1841</x:v>
+      </x:c>
+      <x:c r="H608" s="10" t="s">
+        <x:v>1842</x:v>
+      </x:c>
+      <x:c r="I608" s="10" t="s">
+        <x:v>1843</x:v>
+      </x:c>
+      <x:c r="J608" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K608" s="10" t="s">
+        <x:v>1689</x:v>
+      </x:c>
+      <x:c r="L608" s="10" t="s">
+        <x:v>1844</x:v>
+      </x:c>
+      <x:c r="M608" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609" hidden="0">
+      <x:c r="A609">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B609" s="2">
+        <x:v>46171.7788078704</x:v>
+      </x:c>
+      <x:c r="C609" s="2">
+        <x:v>46171.7809722222</x:v>
+      </x:c>
+      <x:c r="D609" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E609" s="10" t="s"/>
+      <x:c r="F609" s="2"/>
+      <x:c r="G609" s="10" t="s">
+        <x:v>1845</x:v>
+      </x:c>
+      <x:c r="H609" s="10" t="s">
+        <x:v>1846</x:v>
+      </x:c>
+      <x:c r="I609" s="10" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="J609" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K609" s="10" t="s">
+        <x:v>1847</x:v>
+      </x:c>
+      <x:c r="L609" s="10" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="M609" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610" hidden="0">
+      <x:c r="A610">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B610" s="2">
+        <x:v>46171.7984953704</x:v>
+      </x:c>
+      <x:c r="C610" s="2">
+        <x:v>46171.7990509259</x:v>
+      </x:c>
+      <x:c r="D610" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E610" s="10" t="s"/>
+      <x:c r="F610" s="2"/>
+      <x:c r="G610" s="10" t="s">
+        <x:v>1848</x:v>
+      </x:c>
+      <x:c r="H610" s="10" t="s">
+        <x:v>1849</x:v>
+      </x:c>
+      <x:c r="I610" s="10" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="J610" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K610" s="10" t="s">
+        <x:v>1847</x:v>
+      </x:c>
+      <x:c r="L610" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M610" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611" hidden="0">
+      <x:c r="A611">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="B611" s="2">
+        <x:v>46171.8303356481</x:v>
+      </x:c>
+      <x:c r="C611" s="2">
+        <x:v>46171.8311111111</x:v>
+      </x:c>
+      <x:c r="D611" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E611" s="10" t="s"/>
+      <x:c r="F611" s="2"/>
+      <x:c r="G611" s="10" t="s">
+        <x:v>1850</x:v>
+      </x:c>
+      <x:c r="H611" s="10" t="s">
+        <x:v>1851</x:v>
+      </x:c>
+      <x:c r="I611" s="10" t="s">
+        <x:v>976</x:v>
+      </x:c>
+      <x:c r="J611" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K611" s="10" t="s">
+        <x:v>1578</x:v>
+      </x:c>
+      <x:c r="L611" s="10" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M611" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612" hidden="0">
+      <x:c r="A612">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B612" s="2">
+        <x:v>46171.9084027778</x:v>
+      </x:c>
+      <x:c r="C612" s="2">
+        <x:v>46171.9097337963</x:v>
+      </x:c>
+      <x:c r="D612" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E612" s="10" t="s"/>
+      <x:c r="F612" s="2"/>
+      <x:c r="G612" s="10" t="s">
+        <x:v>1852</x:v>
+      </x:c>
+      <x:c r="H612" s="10" t="s">
+        <x:v>1853</x:v>
+      </x:c>
+      <x:c r="I612" s="10" t="s">
+        <x:v>1617</x:v>
+      </x:c>
+      <x:c r="J612" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K612" s="10" t="s">
+        <x:v>1854</x:v>
+      </x:c>
+      <x:c r="L612" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M612" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613" hidden="0">
+      <x:c r="A613">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B613" s="2">
+        <x:v>46171.9176157407</x:v>
+      </x:c>
+      <x:c r="C613" s="2">
+        <x:v>46171.9185069444</x:v>
+      </x:c>
+      <x:c r="D613" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E613" s="10" t="s"/>
+      <x:c r="F613" s="2"/>
+      <x:c r="G613" s="10" t="s">
+        <x:v>1855</x:v>
+      </x:c>
+      <x:c r="H613" s="10" t="s">
+        <x:v>1856</x:v>
+      </x:c>
+      <x:c r="I613" s="10" t="s">
+        <x:v>1299</x:v>
+      </x:c>
+      <x:c r="J613" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K613" s="10" t="s">
+        <x:v>1538</x:v>
+      </x:c>
+      <x:c r="L613" s="10" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="M613" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" hidden="0">
+      <x:c r="A614">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B614" s="2">
+        <x:v>46171.9224652778</x:v>
+      </x:c>
+      <x:c r="C614" s="2">
+        <x:v>46171.9232291667</x:v>
+      </x:c>
+      <x:c r="D614" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E614" s="10" t="s"/>
+      <x:c r="F614" s="2"/>
+      <x:c r="G614" s="10" t="s">
+        <x:v>1857</x:v>
+      </x:c>
+      <x:c r="H614" s="10" t="s">
+        <x:v>1858</x:v>
+      </x:c>
+      <x:c r="I614" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J614" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K614" s="10" t="s">
+        <x:v>1859</x:v>
+      </x:c>
+      <x:c r="L614" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M614" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" hidden="0">
+      <x:c r="A615">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="B615" s="2">
+        <x:v>46171.9303125</x:v>
+      </x:c>
+      <x:c r="C615" s="2">
+        <x:v>46171.9307638889</x:v>
+      </x:c>
+      <x:c r="D615" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E615" s="10" t="s"/>
+      <x:c r="F615" s="2"/>
+      <x:c r="G615" s="10" t="s">
+        <x:v>1860</x:v>
+      </x:c>
+      <x:c r="H615" s="10" t="s">
+        <x:v>1861</x:v>
+      </x:c>
+      <x:c r="I615" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J615" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K615" s="10" t="s">
+        <x:v>1862</x:v>
+      </x:c>
+      <x:c r="L615" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M615" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616" hidden="0">
+      <x:c r="A616">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B616" s="2">
+        <x:v>46171.9804050926</x:v>
+      </x:c>
+      <x:c r="C616" s="2">
+        <x:v>46171.9864814815</x:v>
+      </x:c>
+      <x:c r="D616" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E616" s="10" t="s"/>
+      <x:c r="F616" s="2"/>
+      <x:c r="G616" s="10" t="s">
+        <x:v>1863</x:v>
+      </x:c>
+      <x:c r="H616" s="10" t="s">
+        <x:v>1864</x:v>
+      </x:c>
+      <x:c r="I616" s="10" t="s">
+        <x:v>1865</x:v>
+      </x:c>
+      <x:c r="J616" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K616" s="10" t="s">
+        <x:v>1866</x:v>
+      </x:c>
+      <x:c r="L616" s="10" t="s">
+        <x:v>1867</x:v>
+      </x:c>
+      <x:c r="M616" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617" hidden="0">
+      <x:c r="A617">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="B617" s="2">
+        <x:v>46172.0317476852</x:v>
+      </x:c>
+      <x:c r="C617" s="2">
+        <x:v>46172.0630787037</x:v>
+      </x:c>
+      <x:c r="D617" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E617" s="10" t="s"/>
+      <x:c r="F617" s="2"/>
+      <x:c r="G617" s="10" t="s">
+        <x:v>1868</x:v>
+      </x:c>
+      <x:c r="H617" s="10" t="s">
+        <x:v>1869</x:v>
+      </x:c>
+      <x:c r="I617" s="10" t="s">
+        <x:v>1870</x:v>
+      </x:c>
+      <x:c r="J617" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K617" s="10" t="s">
+        <x:v>1871</x:v>
+      </x:c>
+      <x:c r="L617" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M617" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618" hidden="0">
+      <x:c r="A618">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="B618" s="2">
+        <x:v>46172.0672222222</x:v>
+      </x:c>
+      <x:c r="C618" s="2">
+        <x:v>46172.0738310185</x:v>
+      </x:c>
+      <x:c r="D618" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E618" s="10" t="s"/>
+      <x:c r="F618" s="2"/>
+      <x:c r="G618" s="10" t="s">
+        <x:v>1872</x:v>
+      </x:c>
+      <x:c r="H618" s="10" t="s">
+        <x:v>1873</x:v>
+      </x:c>
+      <x:c r="I618" s="10" t="s">
+        <x:v>976</x:v>
+      </x:c>
+      <x:c r="J618" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K618" s="10" t="s">
+        <x:v>1871</x:v>
+      </x:c>
+      <x:c r="L618" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M618" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619" hidden="0">
+      <x:c r="A619">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B619" s="2">
+        <x:v>46172.0724421296</x:v>
+      </x:c>
+      <x:c r="C619" s="2">
+        <x:v>46172.0738541667</x:v>
+      </x:c>
+      <x:c r="D619" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E619" s="10" t="s"/>
+      <x:c r="F619" s="2"/>
+      <x:c r="G619" s="10" t="s">
+        <x:v>1874</x:v>
+      </x:c>
+      <x:c r="H619" s="10" t="s">
+        <x:v>1875</x:v>
+      </x:c>
+      <x:c r="I619" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J619" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K619" s="10" t="s">
+        <x:v>1862</x:v>
+      </x:c>
+      <x:c r="L619" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M619" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620" hidden="0">
+      <x:c r="A620">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="B620" s="2">
+        <x:v>46172.0737268518</x:v>
+      </x:c>
+      <x:c r="C620" s="2">
+        <x:v>46172.0746990741</x:v>
+      </x:c>
+      <x:c r="D620" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E620" s="10" t="s"/>
+      <x:c r="F620" s="2"/>
+      <x:c r="G620" s="10" t="s">
+        <x:v>1876</x:v>
+      </x:c>
+      <x:c r="H620" s="10" t="s">
+        <x:v>1877</x:v>
+      </x:c>
+      <x:c r="I620" s="10" t="s">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="J620" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K620" s="10" t="s">
+        <x:v>1382</x:v>
+      </x:c>
+      <x:c r="L620" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M620" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621" hidden="0">
+      <x:c r="A621">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="B621" s="2">
+        <x:v>46172.0721527778</x:v>
+      </x:c>
+      <x:c r="C621" s="2">
+        <x:v>46172.0776388889</x:v>
+      </x:c>
+      <x:c r="D621" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E621" s="10" t="s"/>
+      <x:c r="F621" s="2"/>
+      <x:c r="G621" s="10" t="s">
+        <x:v>1878</x:v>
+      </x:c>
+      <x:c r="H621" s="10" t="s">
+        <x:v>1879</x:v>
+      </x:c>
+      <x:c r="I621" s="10" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="J621" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K621" s="10" t="s">
+        <x:v>1871</x:v>
+      </x:c>
+      <x:c r="L621" s="10" t="s">
+        <x:v>1880</x:v>
+      </x:c>
+      <x:c r="M621" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" hidden="0">
+      <x:c r="A622">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="B622" s="2">
+        <x:v>46172.0804398148</x:v>
+      </x:c>
+      <x:c r="C622" s="2">
+        <x:v>46172.0809606481</x:v>
+      </x:c>
+      <x:c r="D622" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E622" s="10" t="s"/>
+      <x:c r="F622" s="2"/>
+      <x:c r="G622" s="10" t="s">
+        <x:v>1881</x:v>
+      </x:c>
+      <x:c r="H622" s="10" t="s">
+        <x:v>1882</x:v>
+      </x:c>
+      <x:c r="I622" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J622" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K622" s="10" t="s">
+        <x:v>1883</x:v>
+      </x:c>
+      <x:c r="L622" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M622" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623" hidden="0">
+      <x:c r="A623">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="B623" s="2">
+        <x:v>46172.0886111111</x:v>
+      </x:c>
+      <x:c r="C623" s="2">
+        <x:v>46172.0897337963</x:v>
+      </x:c>
+      <x:c r="D623" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E623" s="10" t="s"/>
+      <x:c r="F623" s="2"/>
+      <x:c r="G623" s="10" t="s">
+        <x:v>1884</x:v>
+      </x:c>
+      <x:c r="H623" s="10" t="s">
+        <x:v>1885</x:v>
+      </x:c>
+      <x:c r="I623" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J623" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K623" s="10" t="s">
+        <x:v>1886</x:v>
+      </x:c>
+      <x:c r="L623" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M623" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" hidden="0">
+      <x:c r="A624">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="B624" s="2">
+        <x:v>46172.3429050926</x:v>
+      </x:c>
+      <x:c r="C624" s="2">
+        <x:v>46172.3436921296</x:v>
+      </x:c>
+      <x:c r="D624" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E624" s="10" t="s"/>
+      <x:c r="F624" s="2"/>
+      <x:c r="G624" s="10" t="s">
+        <x:v>1887</x:v>
+      </x:c>
+      <x:c r="H624" s="10" t="s">
+        <x:v>1888</x:v>
+      </x:c>
+      <x:c r="I624" s="10" t="s"/>
+      <x:c r="J624" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K624" s="10" t="s">
+        <x:v>1382</x:v>
+      </x:c>
+      <x:c r="L624" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M624" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625" hidden="0">
+      <x:c r="A625">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="B625" s="2">
+        <x:v>46169.7277083333</x:v>
+      </x:c>
+      <x:c r="C625" s="2">
+        <x:v>46172.4651967593</x:v>
+      </x:c>
+      <x:c r="D625" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E625" s="10" t="s"/>
+      <x:c r="F625" s="2"/>
+      <x:c r="G625" s="10" t="s">
+        <x:v>1889</x:v>
+      </x:c>
+      <x:c r="H625" s="10" t="s">
+        <x:v>1890</x:v>
+      </x:c>
+      <x:c r="I625" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J625" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K625" s="10" t="s">
+        <x:v>1568</x:v>
+      </x:c>
+      <x:c r="L625" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M625" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626" hidden="0">
+      <x:c r="A626">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="B626" s="2">
+        <x:v>46172.5086574074</x:v>
+      </x:c>
+      <x:c r="C626" s="2">
+        <x:v>46172.5102199074</x:v>
+      </x:c>
+      <x:c r="D626" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E626" s="10" t="s"/>
+      <x:c r="F626" s="2"/>
+      <x:c r="G626" s="10" t="s">
+        <x:v>1891</x:v>
+      </x:c>
+      <x:c r="H626" s="10" t="s">
+        <x:v>1892</x:v>
+      </x:c>
+      <x:c r="I626" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J626" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K626" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L626" s="10" t="s">
+        <x:v>1893</x:v>
+      </x:c>
+      <x:c r="M626" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627" hidden="0">
+      <x:c r="A627">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="B627" s="2">
+        <x:v>46172.5887037037</x:v>
+      </x:c>
+      <x:c r="C627" s="2">
+        <x:v>46172.5892361111</x:v>
+      </x:c>
+      <x:c r="D627" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E627" s="10" t="s"/>
+      <x:c r="F627" s="2"/>
+      <x:c r="G627" s="10" t="s">
+        <x:v>1894</x:v>
+      </x:c>
+      <x:c r="H627" s="10" t="s">
+        <x:v>1895</x:v>
+      </x:c>
+      <x:c r="I627" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J627" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K627" s="10" t="s">
+        <x:v>1318</x:v>
+      </x:c>
+      <x:c r="L627" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M627" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628" hidden="0">
+      <x:c r="A628">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="B628" s="2">
+        <x:v>46172.6272453704</x:v>
+      </x:c>
+      <x:c r="C628" s="2">
+        <x:v>46172.6299537037</x:v>
+      </x:c>
+      <x:c r="D628" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E628" s="10" t="s"/>
+      <x:c r="F628" s="2"/>
+      <x:c r="G628" s="10" t="s">
+        <x:v>1896</x:v>
+      </x:c>
+      <x:c r="H628" s="10" t="s">
+        <x:v>1897</x:v>
+      </x:c>
+      <x:c r="I628" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J628" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K628" s="10" t="s">
+        <x:v>1898</x:v>
+      </x:c>
+      <x:c r="L628" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M628" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629" hidden="0">
+      <x:c r="A629">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="B629" s="2">
+        <x:v>46172.6351273148</x:v>
+      </x:c>
+      <x:c r="C629" s="2">
+        <x:v>46172.6356365741</x:v>
+      </x:c>
+      <x:c r="D629" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E629" s="10" t="s"/>
+      <x:c r="F629" s="2"/>
+      <x:c r="G629" s="10" t="s">
+        <x:v>1896</x:v>
+      </x:c>
+      <x:c r="H629" s="10" t="s">
+        <x:v>1897</x:v>
+      </x:c>
+      <x:c r="I629" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J629" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K629" s="10" t="s">
+        <x:v>1898</x:v>
+      </x:c>
+      <x:c r="L629" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M629" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630" hidden="0">
+      <x:c r="A630">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="B630" s="2">
+        <x:v>46172.6779166667</x:v>
+      </x:c>
+      <x:c r="C630" s="2">
+        <x:v>46172.678599537</x:v>
+      </x:c>
+      <x:c r="D630" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E630" s="10" t="s"/>
+      <x:c r="F630" s="2"/>
+      <x:c r="G630" s="10" t="s">
+        <x:v>1899</x:v>
+      </x:c>
+      <x:c r="H630" s="10" t="s">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="I630" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J630" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K630" s="10" t="s">
+        <x:v>1382</x:v>
+      </x:c>
+      <x:c r="L630" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M630" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631" hidden="0">
+      <x:c r="A631">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="B631" s="2">
+        <x:v>46172.6876851852</x:v>
+      </x:c>
+      <x:c r="C631" s="2">
+        <x:v>46172.6896527778</x:v>
+      </x:c>
+      <x:c r="D631" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E631" s="10" t="s"/>
+      <x:c r="F631" s="2"/>
+      <x:c r="G631" s="10" t="s">
+        <x:v>1901</x:v>
+      </x:c>
+      <x:c r="H631" s="10" t="s">
+        <x:v>1902</x:v>
+      </x:c>
+      <x:c r="I631" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J631" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K631" s="10" t="s">
+        <x:v>1903</x:v>
+      </x:c>
+      <x:c r="L631" s="10" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="M631" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632" hidden="0">
+      <x:c r="A632">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="B632" s="2">
+        <x:v>46172.7106018519</x:v>
+      </x:c>
+      <x:c r="C632" s="2">
+        <x:v>46172.7123148148</x:v>
+      </x:c>
+      <x:c r="D632" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E632" s="10" t="s"/>
+      <x:c r="F632" s="2"/>
+      <x:c r="G632" s="10" t="s">
+        <x:v>1904</x:v>
+      </x:c>
+      <x:c r="H632" s="10" t="s">
+        <x:v>1905</x:v>
+      </x:c>
+      <x:c r="I632" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J632" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K632" s="10" t="s">
+        <x:v>1906</x:v>
+      </x:c>
+      <x:c r="L632" s="10" t="s">
+        <x:v>1907</x:v>
+      </x:c>
+      <x:c r="M632" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633" hidden="0">
+      <x:c r="A633">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="B633" s="2">
+        <x:v>46172.713912037</x:v>
+      </x:c>
+      <x:c r="C633" s="2">
+        <x:v>46172.7146064815</x:v>
+      </x:c>
+      <x:c r="D633" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E633" s="10" t="s"/>
+      <x:c r="F633" s="2"/>
+      <x:c r="G633" s="10" t="s">
+        <x:v>1908</x:v>
+      </x:c>
+      <x:c r="H633" s="10" t="s">
+        <x:v>1909</x:v>
+      </x:c>
+      <x:c r="I633" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J633" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K633" s="10" t="s">
+        <x:v>1818</x:v>
+      </x:c>
+      <x:c r="L633" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M633" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634" hidden="0">
+      <x:c r="A634">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="B634" s="2">
+        <x:v>46172.7149652778</x:v>
+      </x:c>
+      <x:c r="C634" s="2">
+        <x:v>46172.7161111111</x:v>
+      </x:c>
+      <x:c r="D634" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E634" s="10" t="s"/>
+      <x:c r="F634" s="2"/>
+      <x:c r="G634" s="10" t="s">
+        <x:v>1910</x:v>
+      </x:c>
+      <x:c r="H634" s="10" t="s">
+        <x:v>1911</x:v>
+      </x:c>
+      <x:c r="I634" s="10" t="s">
+        <x:v>1279</x:v>
+      </x:c>
+      <x:c r="J634" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K634" s="10" t="s">
+        <x:v>1912</x:v>
+      </x:c>
+      <x:c r="L634" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M634" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="635" hidden="0">
+      <x:c r="A635">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="B635" s="2">
+        <x:v>46172.7186111111</x:v>
+      </x:c>
+      <x:c r="C635" s="2">
+        <x:v>46172.7203356481</x:v>
+      </x:c>
+      <x:c r="D635" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E635" s="10" t="s"/>
+      <x:c r="F635" s="2"/>
+      <x:c r="G635" s="10" t="s">
+        <x:v>1913</x:v>
+      </x:c>
+      <x:c r="H635" s="10" t="s">
+        <x:v>1914</x:v>
+      </x:c>
+      <x:c r="I635" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J635" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K635" s="10" t="s">
+        <x:v>1915</x:v>
+      </x:c>
+      <x:c r="L635" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M635" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="636" hidden="0">
+      <x:c r="A636">
+        <x:v>635</x:v>
+      </x:c>
+      <x:c r="B636" s="2">
+        <x:v>46172.7033796296</x:v>
+      </x:c>
+      <x:c r="C636" s="2">
+        <x:v>46172.7240625</x:v>
+      </x:c>
+      <x:c r="D636" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E636" s="10" t="s"/>
+      <x:c r="F636" s="2"/>
+      <x:c r="G636" s="10" t="s">
+        <x:v>1916</x:v>
+      </x:c>
+      <x:c r="H636" s="10" t="s">
+        <x:v>1917</x:v>
+      </x:c>
+      <x:c r="I636" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J636" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K636" s="10" t="s">
+        <x:v>1918</x:v>
+      </x:c>
+      <x:c r="L636" s="10" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="M636" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="637" hidden="0">
+      <x:c r="A637">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="B637" s="2">
+        <x:v>46172.7251157407</x:v>
+      </x:c>
+      <x:c r="C637" s="2">
+        <x:v>46172.7256365741</x:v>
+      </x:c>
+      <x:c r="D637" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E637" s="10" t="s"/>
+      <x:c r="F637" s="2"/>
+      <x:c r="G637" s="10" t="s">
+        <x:v>1919</x:v>
+      </x:c>
+      <x:c r="H637" s="10" t="s">
+        <x:v>1920</x:v>
+      </x:c>
+      <x:c r="I637" s="10" t="s">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="J637" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K637" s="10" t="s">
+        <x:v>1921</x:v>
+      </x:c>
+      <x:c r="L637" s="10" t="s">
+        <x:v>1844</x:v>
+      </x:c>
+      <x:c r="M637" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="638" hidden="0">
+      <x:c r="A638">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="B638" s="2">
+        <x:v>46172.6213194444</x:v>
+      </x:c>
+      <x:c r="C638" s="2">
+        <x:v>46172.7402199074</x:v>
+      </x:c>
+      <x:c r="D638" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E638" s="10" t="s"/>
+      <x:c r="F638" s="2"/>
+      <x:c r="G638" s="10" t="s">
+        <x:v>1922</x:v>
+      </x:c>
+      <x:c r="H638" s="10" t="s">
+        <x:v>1923</x:v>
+      </x:c>
+      <x:c r="I638" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J638" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K638" s="10" t="s">
+        <x:v>1715</x:v>
+      </x:c>
+      <x:c r="L638" s="10" t="s">
+        <x:v>1402</x:v>
+      </x:c>
+      <x:c r="M638" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="639" hidden="0">
+      <x:c r="A639">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="B639" s="2">
+        <x:v>46172.7486805556</x:v>
+      </x:c>
+      <x:c r="C639" s="2">
+        <x:v>46172.749224537</x:v>
+      </x:c>
+      <x:c r="D639" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E639" s="10" t="s"/>
+      <x:c r="F639" s="2"/>
+      <x:c r="G639" s="10" t="s">
+        <x:v>1924</x:v>
+      </x:c>
+      <x:c r="H639" s="10" t="s">
+        <x:v>1925</x:v>
+      </x:c>
+      <x:c r="I639" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J639" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K639" s="10" t="s">
+        <x:v>1912</x:v>
+      </x:c>
+      <x:c r="L639" s="10" t="s">
+        <x:v>1926</x:v>
+      </x:c>
+      <x:c r="M639" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="640" hidden="0">
+      <x:c r="A640">
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="B640" s="2">
+        <x:v>46172.757349537</x:v>
+      </x:c>
+      <x:c r="C640" s="2">
+        <x:v>46172.7582175926</x:v>
+      </x:c>
+      <x:c r="D640" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E640" s="10" t="s"/>
+      <x:c r="F640" s="2"/>
+      <x:c r="G640" s="10" t="s">
+        <x:v>1373</x:v>
+      </x:c>
+      <x:c r="H640" s="10" t="s">
+        <x:v>1374</x:v>
+      </x:c>
+      <x:c r="I640" s="10" t="s">
+        <x:v>976</x:v>
+      </x:c>
+      <x:c r="J640" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K640" s="10" t="s">
+        <x:v>1578</x:v>
+      </x:c>
+      <x:c r="L640" s="10" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="M640" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641" hidden="0">
+      <x:c r="A641">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="B641" s="2">
+        <x:v>46172.7621412037</x:v>
+      </x:c>
+      <x:c r="C641" s="2">
+        <x:v>46172.7634490741</x:v>
+      </x:c>
+      <x:c r="D641" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E641" s="10" t="s"/>
+      <x:c r="F641" s="2"/>
+      <x:c r="G641" s="10" t="s">
+        <x:v>1927</x:v>
+      </x:c>
+      <x:c r="H641" s="10" t="s">
+        <x:v>1928</x:v>
+      </x:c>
+      <x:c r="I641" s="10" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J641" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K641" s="10" t="s">
+        <x:v>1929</x:v>
+      </x:c>
+      <x:c r="L641" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M641" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="642" hidden="0">
+      <x:c r="A642">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="B642" s="2">
+        <x:v>46172.7917013889</x:v>
+      </x:c>
+      <x:c r="C642" s="2">
+        <x:v>46172.7930787037</x:v>
+      </x:c>
+      <x:c r="D642" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E642" s="10" t="s"/>
+      <x:c r="F642" s="2"/>
+      <x:c r="G642" s="10" t="s">
+        <x:v>1930</x:v>
+      </x:c>
+      <x:c r="H642" s="10" t="s">
+        <x:v>1931</x:v>
+      </x:c>
+      <x:c r="I642" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J642" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K642" s="10" t="s">
+        <x:v>1932</x:v>
+      </x:c>
+      <x:c r="L642" s="10" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="M642" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643" hidden="0">
+      <x:c r="A643">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="B643" s="2">
+        <x:v>46172.8146296296</x:v>
+      </x:c>
+      <x:c r="C643" s="2">
+        <x:v>46172.8191550926</x:v>
+      </x:c>
+      <x:c r="D643" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E643" s="10" t="s"/>
+      <x:c r="F643" s="2"/>
+      <x:c r="G643" s="10" t="s">
+        <x:v>1933</x:v>
+      </x:c>
+      <x:c r="H643" s="10" t="s">
+        <x:v>1934</x:v>
+      </x:c>
+      <x:c r="I643" s="10" t="s">
+        <x:v>871</x:v>
+      </x:c>
+      <x:c r="J643" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K643" s="10" t="s">
+        <x:v>872</x:v>
+      </x:c>
+      <x:c r="L643" s="10" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="M643" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="644" hidden="0">
+      <x:c r="A644">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="B644" s="2">
+        <x:v>46172.8406597222</x:v>
+      </x:c>
+      <x:c r="C644" s="2">
+        <x:v>46172.8413194444</x:v>
+      </x:c>
+      <x:c r="D644" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E644" s="10" t="s"/>
+      <x:c r="F644" s="2"/>
+      <x:c r="G644" s="10" t="s">
+        <x:v>1908</x:v>
+      </x:c>
+      <x:c r="H644" s="10" t="s">
+        <x:v>1909</x:v>
+      </x:c>
+      <x:c r="I644" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J644" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K644" s="10" t="s">
+        <x:v>1818</x:v>
+      </x:c>
+      <x:c r="L644" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M644" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645" hidden="0">
+      <x:c r="A645">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="B645" s="2">
+        <x:v>46172.8320833333</x:v>
+      </x:c>
+      <x:c r="C645" s="2">
+        <x:v>46172.8498958333</x:v>
+      </x:c>
+      <x:c r="D645" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E645" s="10" t="s"/>
+      <x:c r="F645" s="2"/>
+      <x:c r="G645" s="10" t="s">
+        <x:v>1935</x:v>
+      </x:c>
+      <x:c r="H645" s="10" t="s">
+        <x:v>1936</x:v>
+      </x:c>
+      <x:c r="I645" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J645" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K645" s="10" t="s">
+        <x:v>1937</x:v>
+      </x:c>
+      <x:c r="L645" s="10" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="M645" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="646" hidden="0">
+      <x:c r="A646">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="B646" s="2">
+        <x:v>46172.8310416667</x:v>
+      </x:c>
+      <x:c r="C646" s="2">
+        <x:v>46172.8500925926</x:v>
+      </x:c>
+      <x:c r="D646" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E646" s="10" t="s"/>
+      <x:c r="F646" s="2"/>
+      <x:c r="G646" s="10" t="s">
+        <x:v>1938</x:v>
+      </x:c>
+      <x:c r="H646" s="10" t="s">
+        <x:v>1939</x:v>
+      </x:c>
+      <x:c r="I646" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J646" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K646" s="10" t="s">
+        <x:v>1937</x:v>
+      </x:c>
+      <x:c r="L646" s="10" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="M646" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647" hidden="0">
+      <x:c r="A647">
+        <x:v>646</x:v>
+      </x:c>
+      <x:c r="B647" s="2">
+        <x:v>46172.8996990741</x:v>
+      </x:c>
+      <x:c r="C647" s="2">
+        <x:v>46172.9004050926</x:v>
+      </x:c>
+      <x:c r="D647" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E647" s="10" t="s"/>
+      <x:c r="F647" s="2"/>
+      <x:c r="G647" s="10" t="s">
+        <x:v>1940</x:v>
+      </x:c>
+      <x:c r="H647" s="10" t="s">
+        <x:v>1941</x:v>
+      </x:c>
+      <x:c r="I647" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J647" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K647" s="10" t="s">
+        <x:v>1568</x:v>
+      </x:c>
+      <x:c r="L647" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M647" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="648" hidden="0">
+      <x:c r="A648">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="B648" s="2">
+        <x:v>46172.8994444444</x:v>
+      </x:c>
+      <x:c r="C648" s="2">
+        <x:v>46172.9064583333</x:v>
+      </x:c>
+      <x:c r="D648" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E648" s="10" t="s"/>
+      <x:c r="F648" s="2"/>
+      <x:c r="G648" s="10" t="s">
+        <x:v>1942</x:v>
+      </x:c>
+      <x:c r="H648" s="10" t="s">
+        <x:v>1943</x:v>
+      </x:c>
+      <x:c r="I648" s="10" t="s">
+        <x:v>1944</x:v>
+      </x:c>
+      <x:c r="J648" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K648" s="10" t="s">
+        <x:v>1945</x:v>
+      </x:c>
+      <x:c r="L648" s="10" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="M648" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="649" hidden="0">
+      <x:c r="A649">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="B649" s="2">
+        <x:v>46172.9470601852</x:v>
+      </x:c>
+      <x:c r="C649" s="2">
+        <x:v>46172.9486111111</x:v>
+      </x:c>
+      <x:c r="D649" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E649" s="10" t="s"/>
+      <x:c r="F649" s="2"/>
+      <x:c r="G649" s="10" t="s">
+        <x:v>1942</x:v>
+      </x:c>
+      <x:c r="H649" s="10" t="s">
+        <x:v>1943</x:v>
+      </x:c>
+      <x:c r="I649" s="10" t="s">
+        <x:v>1944</x:v>
+      </x:c>
+      <x:c r="J649" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K649" s="10" t="s">
+        <x:v>1945</x:v>
+      </x:c>
+      <x:c r="L649" s="10" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="M649" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="650" hidden="0">
+      <x:c r="A650">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="B650" s="2">
+        <x:v>46172.9544907407</x:v>
+      </x:c>
+      <x:c r="C650" s="2">
+        <x:v>46172.9550694444</x:v>
+      </x:c>
+      <x:c r="D650" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E650" s="10" t="s"/>
+      <x:c r="F650" s="2"/>
+      <x:c r="G650" s="10" t="s">
+        <x:v>1946</x:v>
+      </x:c>
+      <x:c r="H650" s="10" t="s">
+        <x:v>1947</x:v>
+      </x:c>
+      <x:c r="I650" s="10" t="s">
+        <x:v>1948</x:v>
+      </x:c>
+      <x:c r="J650" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K650" s="10" t="s">
+        <x:v>1949</x:v>
+      </x:c>
+      <x:c r="L650" s="10" t="s">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="M650" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="651" hidden="0">
+      <x:c r="A651">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="B651" s="2">
+        <x:v>46172.9551041667</x:v>
+      </x:c>
+      <x:c r="C651" s="2">
+        <x:v>46172.9564930556</x:v>
+      </x:c>
+      <x:c r="D651" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E651" s="10" t="s"/>
+      <x:c r="F651" s="2"/>
+      <x:c r="G651" s="10" t="s">
+        <x:v>1951</x:v>
+      </x:c>
+      <x:c r="H651" s="10" t="s">
+        <x:v>1952</x:v>
+      </x:c>
+      <x:c r="I651" s="10" t="s">
+        <x:v>1948</x:v>
+      </x:c>
+      <x:c r="J651" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K651" s="10" t="s">
+        <x:v>1949</x:v>
+      </x:c>
+      <x:c r="L651" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M651" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="652" hidden="0">
+      <x:c r="A652">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="B652" s="2">
+        <x:v>46173.0015972222</x:v>
+      </x:c>
+      <x:c r="C652" s="2">
+        <x:v>46173.0103819444</x:v>
+      </x:c>
+      <x:c r="D652" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E652" s="10" t="s"/>
+      <x:c r="F652" s="2"/>
+      <x:c r="G652" s="10" t="s">
+        <x:v>1953</x:v>
+      </x:c>
+      <x:c r="H652" s="10" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="I652" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J652" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K652" s="10" t="s">
+        <x:v>1955</x:v>
+      </x:c>
+      <x:c r="L652" s="10" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="M652" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653" hidden="0">
+      <x:c r="A653">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="B653" s="2">
+        <x:v>46173.0105092593</x:v>
+      </x:c>
+      <x:c r="C653" s="2">
+        <x:v>46173.0139930556</x:v>
+      </x:c>
+      <x:c r="D653" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E653" s="10" t="s"/>
+      <x:c r="F653" s="2"/>
+      <x:c r="G653" s="10" t="s">
+        <x:v>1956</x:v>
+      </x:c>
+      <x:c r="H653" s="10" t="s">
+        <x:v>1957</x:v>
+      </x:c>
+      <x:c r="I653" s="10" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J653" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K653" s="10" t="s">
+        <x:v>1958</x:v>
+      </x:c>
+      <x:c r="L653" s="10" t="s">
+        <x:v>1959</x:v>
+      </x:c>
+      <x:c r="M653" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="654" hidden="0">
+      <x:c r="A654">
+        <x:v>653</x:v>
+      </x:c>
+      <x:c r="B654" s="2">
+        <x:v>46173.0597685185</x:v>
+      </x:c>
+      <x:c r="C654" s="2">
+        <x:v>46173.0604861111</x:v>
+      </x:c>
+      <x:c r="D654" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E654" s="10" t="s"/>
+      <x:c r="F654" s="2"/>
+      <x:c r="G654" s="10" t="s">
+        <x:v>1960</x:v>
+      </x:c>
+      <x:c r="H654" s="10" t="s">
+        <x:v>1961</x:v>
+      </x:c>
+      <x:c r="I654" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J654" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K654" s="10" t="s">
+        <x:v>1382</x:v>
+      </x:c>
+      <x:c r="L654" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M654" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655" hidden="0">
+      <x:c r="A655">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="B655" s="2">
+        <x:v>46173.0722916667</x:v>
+      </x:c>
+      <x:c r="C655" s="2">
+        <x:v>46173.0734143518</x:v>
+      </x:c>
+      <x:c r="D655" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E655" s="10" t="s"/>
+      <x:c r="F655" s="2"/>
+      <x:c r="G655" s="10" t="s">
+        <x:v>1962</x:v>
+      </x:c>
+      <x:c r="H655" s="10" t="s">
+        <x:v>1963</x:v>
+      </x:c>
+      <x:c r="I655" s="10" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="J655" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K655" s="10" t="s">
+        <x:v>1958</x:v>
+      </x:c>
+      <x:c r="L655" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M655" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="656" hidden="0">
+      <x:c r="A656">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="B656" s="2">
+        <x:v>46173.1287152778</x:v>
+      </x:c>
+      <x:c r="C656" s="2">
+        <x:v>46173.1304166667</x:v>
+      </x:c>
+      <x:c r="D656" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E656" s="10" t="s"/>
+      <x:c r="F656" s="2"/>
+      <x:c r="G656" s="10" t="s">
+        <x:v>1964</x:v>
+      </x:c>
+      <x:c r="H656" s="10" t="s">
+        <x:v>1965</x:v>
+      </x:c>
+      <x:c r="I656" s="10" t="s">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="J656" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K656" s="10" t="s">
+        <x:v>1133</x:v>
+      </x:c>
+      <x:c r="L656" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M656" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="657" hidden="0">
+      <x:c r="A657">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="B657" s="2">
+        <x:v>46173.1845949074</x:v>
+      </x:c>
+      <x:c r="C657" s="2">
+        <x:v>46173.1856828704</x:v>
+      </x:c>
+      <x:c r="D657" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E657" s="10" t="s"/>
+      <x:c r="F657" s="2"/>
+      <x:c r="G657" s="10" t="s">
+        <x:v>1966</x:v>
+      </x:c>
+      <x:c r="H657" s="10" t="s">
+        <x:v>1967</x:v>
+      </x:c>
+      <x:c r="I657" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J657" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K657" s="10" t="s">
+        <x:v>1818</x:v>
+      </x:c>
+      <x:c r="L657" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M657" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="658" hidden="0">
+      <x:c r="A658">
+        <x:v>657</x:v>
+      </x:c>
+      <x:c r="B658" s="2">
+        <x:v>46173.2198842593</x:v>
+      </x:c>
+      <x:c r="C658" s="2">
+        <x:v>46173.220775463</x:v>
+      </x:c>
+      <x:c r="D658" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E658" s="10" t="s"/>
+      <x:c r="F658" s="2"/>
+      <x:c r="G658" s="10" t="s">
+        <x:v>1968</x:v>
+      </x:c>
+      <x:c r="H658" s="10" t="s">
+        <x:v>1969</x:v>
+      </x:c>
+      <x:c r="I658" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="J658" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K658" s="10" t="s">
+        <x:v>1212</x:v>
+      </x:c>
+      <x:c r="L658" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M658" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659" hidden="0">
+      <x:c r="A659">
+        <x:v>658</x:v>
+      </x:c>
+      <x:c r="B659" s="2">
+        <x:v>46173.2708680556</x:v>
+      </x:c>
+      <x:c r="C659" s="2">
+        <x:v>46173.2714583333</x:v>
+      </x:c>
+      <x:c r="D659" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E659" s="10" t="s"/>
+      <x:c r="F659" s="2"/>
+      <x:c r="G659" s="10" t="s">
+        <x:v>1970</x:v>
+      </x:c>
+      <x:c r="H659" s="10" t="s">
+        <x:v>1971</x:v>
+      </x:c>
+      <x:c r="I659" s="10" t="s">
+        <x:v>1972</x:v>
+      </x:c>
+      <x:c r="J659" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K659" s="10" t="s">
+        <x:v>1401</x:v>
+      </x:c>
+      <x:c r="L659" s="10" t="s">
+        <x:v>725</x:v>
+      </x:c>
+      <x:c r="M659" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="660" hidden="0">
+      <x:c r="A660">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="B660" s="2">
+        <x:v>46173.3291319444</x:v>
+      </x:c>
+      <x:c r="C660" s="2">
+        <x:v>46173.3296180556</x:v>
+      </x:c>
+      <x:c r="D660" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E660" s="10" t="s"/>
+      <x:c r="F660" s="2"/>
+      <x:c r="G660" s="10" t="s">
+        <x:v>1973</x:v>
+      </x:c>
+      <x:c r="H660" s="10" t="s">
+        <x:v>1974</x:v>
+      </x:c>
+      <x:c r="I660" s="10" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J660" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K660" s="10" t="s">
+        <x:v>1645</x:v>
+      </x:c>
+      <x:c r="L660" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M660" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="661" hidden="0">
+      <x:c r="A661">
+        <x:v>660</x:v>
+      </x:c>
+      <x:c r="B661" s="2">
+        <x:v>46173.3677430556</x:v>
+      </x:c>
+      <x:c r="C661" s="2">
+        <x:v>46173.369849537</x:v>
+      </x:c>
+      <x:c r="D661" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E661" s="10" t="s"/>
+      <x:c r="F661" s="2"/>
+      <x:c r="G661" s="10" t="s">
+        <x:v>1975</x:v>
+      </x:c>
+      <x:c r="H661" s="10" t="s">
+        <x:v>1976</x:v>
+      </x:c>
+      <x:c r="I661" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J661" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K661" s="10" t="s">
+        <x:v>1977</x:v>
+      </x:c>
+      <x:c r="L661" s="10" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="M661" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="662" hidden="0">
+      <x:c r="A662">
+        <x:v>661</x:v>
+      </x:c>
+      <x:c r="B662" s="2">
+        <x:v>46173.3798726852</x:v>
+      </x:c>
+      <x:c r="C662" s="2">
+        <x:v>46173.3816782407</x:v>
+      </x:c>
+      <x:c r="D662" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E662" s="10" t="s"/>
+      <x:c r="F662" s="2"/>
+      <x:c r="G662" s="10" t="s">
+        <x:v>1978</x:v>
+      </x:c>
+      <x:c r="H662" s="10" t="s">
+        <x:v>1979</x:v>
+      </x:c>
+      <x:c r="I662" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J662" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K662" s="10" t="s">
+        <x:v>1977</x:v>
+      </x:c>
+      <x:c r="L662" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M662" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663" hidden="0">
+      <x:c r="A663">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="B663" s="2">
+        <x:v>46173.4022453704</x:v>
+      </x:c>
+      <x:c r="C663" s="2">
+        <x:v>46173.4037384259</x:v>
+      </x:c>
+      <x:c r="D663" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E663" s="10" t="s"/>
+      <x:c r="F663" s="2"/>
+      <x:c r="G663" s="10" t="s">
+        <x:v>1980</x:v>
+      </x:c>
+      <x:c r="H663" s="10" t="s">
+        <x:v>1981</x:v>
+      </x:c>
+      <x:c r="I663" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J663" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K663" s="10" t="s">
+        <x:v>1977</x:v>
+      </x:c>
+      <x:c r="L663" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M663" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="664" hidden="0">
+      <x:c r="A664">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="B664" s="2">
+        <x:v>46173.4264930556</x:v>
+      </x:c>
+      <x:c r="C664" s="2">
+        <x:v>46173.426875</x:v>
+      </x:c>
+      <x:c r="D664" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E664" s="10" t="s"/>
+      <x:c r="F664" s="2"/>
+      <x:c r="G664" s="10" t="s">
+        <x:v>1380</x:v>
+      </x:c>
+      <x:c r="H664" s="10" t="s">
+        <x:v>1381</x:v>
+      </x:c>
+      <x:c r="I664" s="10" t="s">
+        <x:v>1317</x:v>
+      </x:c>
+      <x:c r="J664" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K664" s="10" t="s">
+        <x:v>1382</x:v>
+      </x:c>
+      <x:c r="L664" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M664" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="665" hidden="0">
+      <x:c r="A665">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="B665" s="2">
+        <x:v>46173.4547569444</x:v>
+      </x:c>
+      <x:c r="C665" s="2">
+        <x:v>46173.4575925926</x:v>
+      </x:c>
+      <x:c r="D665" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E665" s="10" t="s"/>
+      <x:c r="F665" s="2"/>
+      <x:c r="G665" s="10" t="s">
+        <x:v>1982</x:v>
+      </x:c>
+      <x:c r="H665" s="10" t="s">
+        <x:v>1983</x:v>
+      </x:c>
+      <x:c r="I665" s="10" t="s">
+        <x:v>1984</x:v>
+      </x:c>
+      <x:c r="J665" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K665" s="10" t="s">
+        <x:v>1985</x:v>
+      </x:c>
+      <x:c r="L665" s="10" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="M665" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="666" hidden="0">
+      <x:c r="A666">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="B666" s="2">
+        <x:v>46173.4673148148</x:v>
+      </x:c>
+      <x:c r="C666" s="2">
+        <x:v>46173.483599537</x:v>
+      </x:c>
+      <x:c r="D666" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E666" s="10" t="s"/>
+      <x:c r="F666" s="2"/>
+      <x:c r="G666" s="10" t="s">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="H666" s="10" t="s">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I666" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J666" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K666" s="10" t="s">
+        <x:v>1988</x:v>
+      </x:c>
+      <x:c r="L666" s="10" t="s">
+        <x:v>1989</x:v>
+      </x:c>
+      <x:c r="M666" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="667" hidden="0">
+      <x:c r="A667">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="B667" s="2">
+        <x:v>46173.4835763889</x:v>
+      </x:c>
+      <x:c r="C667" s="2">
+        <x:v>46173.4874421296</x:v>
+      </x:c>
+      <x:c r="D667" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E667" s="10" t="s"/>
+      <x:c r="F667" s="2"/>
+      <x:c r="G667" s="10" t="s">
+        <x:v>1990</x:v>
+      </x:c>
+      <x:c r="H667" s="10" t="s">
+        <x:v>1991</x:v>
+      </x:c>
+      <x:c r="I667" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J667" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K667" s="10" t="s">
+        <x:v>1988</x:v>
+      </x:c>
+      <x:c r="L667" s="10" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="M667" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="668" hidden="0">
+      <x:c r="A668">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="B668" s="2">
+        <x:v>46173.5362152778</x:v>
+      </x:c>
+      <x:c r="C668" s="2">
+        <x:v>46173.5383680556</x:v>
+      </x:c>
+      <x:c r="D668" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E668" s="10" t="s"/>
+      <x:c r="F668" s="2"/>
+      <x:c r="G668" s="10" t="s">
+        <x:v>1992</x:v>
+      </x:c>
+      <x:c r="H668" s="10" t="s">
+        <x:v>1993</x:v>
+      </x:c>
+      <x:c r="I668" s="10" t="s">
+        <x:v>1994</x:v>
+      </x:c>
+      <x:c r="J668" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K668" s="10" t="s">
+        <x:v>1912</x:v>
+      </x:c>
+      <x:c r="L668" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M668" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="669" hidden="0">
+      <x:c r="A669">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="B669" s="2">
+        <x:v>46173.5393865741</x:v>
+      </x:c>
+      <x:c r="C669" s="2">
+        <x:v>46173.5400925926</x:v>
+      </x:c>
+      <x:c r="D669" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E669" s="10" t="s"/>
+      <x:c r="F669" s="2"/>
+      <x:c r="G669" s="10" t="s">
+        <x:v>1995</x:v>
+      </x:c>
+      <x:c r="H669" s="10" t="s">
+        <x:v>1996</x:v>
+      </x:c>
+      <x:c r="I669" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J669" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K669" s="10" t="s">
+        <x:v>1997</x:v>
+      </x:c>
+      <x:c r="L669" s="10" t="s">
+        <x:v>1998</x:v>
+      </x:c>
+      <x:c r="M669" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="670" hidden="0">
+      <x:c r="A670">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="B670" s="2">
+        <x:v>46173.5722222222</x:v>
+      </x:c>
+      <x:c r="C670" s="2">
+        <x:v>46173.5729398148</x:v>
+      </x:c>
+      <x:c r="D670" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E670" s="10" t="s"/>
+      <x:c r="F670" s="2"/>
+      <x:c r="G670" s="10" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="H670" s="10" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="I670" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J670" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K670" s="10" t="s">
+        <x:v>1988</x:v>
+      </x:c>
+      <x:c r="L670" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M670" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="671" hidden="0">
+      <x:c r="A671">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="B671" s="2">
+        <x:v>46173.5721064815</x:v>
+      </x:c>
+      <x:c r="C671" s="2">
+        <x:v>46173.5729861111</x:v>
+      </x:c>
+      <x:c r="D671" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E671" s="10" t="s"/>
+      <x:c r="F671" s="2"/>
+      <x:c r="G671" s="10" t="s">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="H671" s="10" t="s">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="I671" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J671" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K671" s="10" t="s">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="L671" s="10" t="s">
+        <x:v>1241</x:v>
+      </x:c>
+      <x:c r="M671" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672" hidden="0">
+      <x:c r="A672">
+        <x:v>671</x:v>
+      </x:c>
+      <x:c r="B672" s="2">
+        <x:v>46173.573587963</x:v>
+      </x:c>
+      <x:c r="C672" s="2">
+        <x:v>46173.5741087963</x:v>
+      </x:c>
+      <x:c r="D672" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E672" s="10" t="s"/>
+      <x:c r="F672" s="2"/>
+      <x:c r="G672" s="10" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="H672" s="10" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="I672" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J672" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K672" s="10" t="s">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="L672" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M672" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673" hidden="0">
+      <x:c r="A673">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="B673" s="2">
+        <x:v>46173.5772337963</x:v>
+      </x:c>
+      <x:c r="C673" s="2">
+        <x:v>46173.5778587963</x:v>
+      </x:c>
+      <x:c r="D673" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E673" s="10" t="s"/>
+      <x:c r="F673" s="2"/>
+      <x:c r="G673" s="10" t="s">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="H673" s="10" t="s">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="I673" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J673" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K673" s="10" t="s">
+        <x:v>2004</x:v>
+      </x:c>
+      <x:c r="L673" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M673" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674" hidden="0">
+      <x:c r="A674">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="B674" s="2">
+        <x:v>46173.5840972222</x:v>
+      </x:c>
+      <x:c r="C674" s="2">
+        <x:v>46173.5846527778</x:v>
+      </x:c>
+      <x:c r="D674" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E674" s="10" t="s"/>
+      <x:c r="F674" s="2"/>
+      <x:c r="G674" s="10" t="s">
+        <x:v>2005</x:v>
+      </x:c>
+      <x:c r="H674" s="10" t="s">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="I674" s="10" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="J674" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K674" s="10" t="s">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="L674" s="10" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="M674" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="675" hidden="0">
+      <x:c r="A675">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="B675" s="2">
+        <x:v>46173.6089467593</x:v>
+      </x:c>
+      <x:c r="C675" s="2">
+        <x:v>46173.6100115741</x:v>
+      </x:c>
+      <x:c r="D675" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E675" s="10" t="s"/>
+      <x:c r="F675" s="2"/>
+      <x:c r="G675" s="10" t="s">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="H675" s="10" t="s">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="I675" s="10" t="s">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="J675" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K675" s="10" t="s">
+        <x:v>1949</x:v>
+      </x:c>
+      <x:c r="L675" s="10" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="M675" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676" hidden="0">
+      <x:c r="A676">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="B676" s="2">
+        <x:v>46173.6104398148</x:v>
+      </x:c>
+      <x:c r="C676" s="2">
+        <x:v>46173.6119444444</x:v>
+      </x:c>
+      <x:c r="D676" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E676" s="10" t="s"/>
+      <x:c r="F676" s="2"/>
+      <x:c r="G676" s="10" t="s">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="H676" s="10" t="s">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="I676" s="10" t="s">
+        <x:v>881</x:v>
+      </x:c>
+      <x:c r="J676" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K676" s="10" t="s">
+        <x:v>1871</x:v>
+      </x:c>
+      <x:c r="L676" s="10" t="s">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="M676" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="677" hidden="0">
+      <x:c r="A677">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="B677" s="2">
+        <x:v>46173.6141435185</x:v>
+      </x:c>
+      <x:c r="C677" s="2">
+        <x:v>46173.6147106481</x:v>
+      </x:c>
+      <x:c r="D677" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E677" s="10" t="s"/>
+      <x:c r="F677" s="2"/>
+      <x:c r="G677" s="10" t="s">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="H677" s="10" t="s">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="I677" s="10" t="s">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="J677" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K677" s="10" t="s">
+        <x:v>1871</x:v>
+      </x:c>
+      <x:c r="L677" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="M677" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678" hidden="0">
+      <x:c r="A678">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="B678" s="2">
+        <x:v>46173.6166319444</x:v>
+      </x:c>
+      <x:c r="C678" s="2">
+        <x:v>46173.6173958333</x:v>
+      </x:c>
+      <x:c r="D678" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E678" s="10" t="s"/>
+      <x:c r="F678" s="2"/>
+      <x:c r="G678" s="10" t="s">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="H678" s="10" t="s">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="I678" s="10" t="s">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="J678" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K678" s="7" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="L678" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="M678" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="679" hidden="0">
+      <x:c r="A679">
+        <x:v>678</x:v>
+      </x:c>
+      <x:c r="B679" s="2">
+        <x:v>46173.6438194444</x:v>
+      </x:c>
+      <x:c r="C679" s="2">
+        <x:v>46173.6443518518</x:v>
+      </x:c>
+      <x:c r="D679" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E679" s="10" t="s"/>
+      <x:c r="F679" s="2"/>
+      <x:c r="G679" s="10" t="s">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="H679" s="10" t="s">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="I679" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J679" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K679" s="10" t="s">
+        <x:v>1847</x:v>
+      </x:c>
+      <x:c r="L679" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M679" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="680" hidden="0">
+      <x:c r="A680">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="B680" s="2">
+        <x:v>46173.6494791667</x:v>
+      </x:c>
+      <x:c r="C680" s="2">
+        <x:v>46173.6500925926</x:v>
+      </x:c>
+      <x:c r="D680" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E680" s="10" t="s"/>
+      <x:c r="F680" s="2"/>
+      <x:c r="G680" s="10" t="s">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="H680" s="10" t="s">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="I680" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J680" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K680" s="10" t="s">
+        <x:v>1988</x:v>
+      </x:c>
+      <x:c r="L680" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M680" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="681" hidden="0">
+      <x:c r="A681">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="B681" s="2">
+        <x:v>46173.6811689815</x:v>
+      </x:c>
+      <x:c r="C681" s="2">
+        <x:v>46173.6817013889</x:v>
+      </x:c>
+      <x:c r="D681" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E681" s="10" t="s"/>
+      <x:c r="F681" s="2"/>
+      <x:c r="G681" s="10" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="H681" s="10" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="I681" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J681" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K681" s="10" t="s">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="L681" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M681" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="682" hidden="0">
+      <x:c r="A682">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="B682" s="2">
+        <x:v>46173.6812037037</x:v>
+      </x:c>
+      <x:c r="C682" s="2">
+        <x:v>46173.6826157407</x:v>
+      </x:c>
+      <x:c r="D682" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E682" s="10" t="s"/>
+      <x:c r="F682" s="2"/>
+      <x:c r="G682" s="10" t="s">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="H682" s="10" t="s">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="I682" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J682" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K682" s="10" t="s">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="L682" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M682" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="683" hidden="0">
+      <x:c r="A683">
+        <x:v>682</x:v>
+      </x:c>
+      <x:c r="B683" s="2">
+        <x:v>46173.688900463</x:v>
+      </x:c>
+      <x:c r="C683" s="2">
+        <x:v>46173.6905439815</x:v>
+      </x:c>
+      <x:c r="D683" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E683" s="10" t="s"/>
+      <x:c r="F683" s="2"/>
+      <x:c r="G683" s="10" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="H683" s="10" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="I683" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J683" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K683" s="10" t="s">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="L683" s="10" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M683" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="684" hidden="0">
+      <x:c r="A684">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="B684" s="2">
+        <x:v>46173.6902083333</x:v>
+      </x:c>
+      <x:c r="C684" s="2">
+        <x:v>46173.6905787037</x:v>
+      </x:c>
+      <x:c r="D684" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E684" s="10" t="s"/>
+      <x:c r="F684" s="2"/>
+      <x:c r="G684" s="10" t="s">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="H684" s="10" t="s">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="I684" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J684" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K684" s="10" t="s">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="L684" s="10" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="M684" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="685" hidden="0">
+      <x:c r="A685">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="B685" s="2">
+        <x:v>46173.6979050926</x:v>
+      </x:c>
+      <x:c r="C685" s="2">
+        <x:v>46173.6986342593</x:v>
+      </x:c>
+      <x:c r="D685" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E685" s="10" t="s"/>
+      <x:c r="F685" s="2"/>
+      <x:c r="G685" s="10" t="s">
+        <x:v>2031</x:v>
+      </x:c>
+      <x:c r="H685" s="10" t="s">
+        <x:v>2032</x:v>
+      </x:c>
+      <x:c r="I685" s="10" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="J685" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K685" s="10" t="s">
+        <x:v>2033</x:v>
+      </x:c>
+      <x:c r="L685" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M685" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="686" hidden="0">
+      <x:c r="A686">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="B686" s="2">
+        <x:v>46173.7379861111</x:v>
+      </x:c>
+      <x:c r="C686" s="2">
+        <x:v>46173.7387731481</x:v>
+      </x:c>
+      <x:c r="D686" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E686" s="10" t="s"/>
+      <x:c r="F686" s="2"/>
+      <x:c r="G686" s="10" t="s">
+        <x:v>2034</x:v>
+      </x:c>
+      <x:c r="H686" s="10" t="s">
+        <x:v>2035</x:v>
+      </x:c>
+      <x:c r="I686" s="10" t="s">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="J686" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K686" s="10" t="s">
+        <x:v>1958</x:v>
+      </x:c>
+      <x:c r="L686" s="10" t="s">
+        <x:v>2036</x:v>
+      </x:c>
+      <x:c r="M686" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="687" hidden="0">
+      <x:c r="A687">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="B687" s="2">
+        <x:v>46173.7544097222</x:v>
+      </x:c>
+      <x:c r="C687" s="2">
+        <x:v>46173.7550462963</x:v>
+      </x:c>
+      <x:c r="D687" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E687" s="10" t="s"/>
+      <x:c r="F687" s="2"/>
+      <x:c r="G687" s="10" t="s">
+        <x:v>2037</x:v>
+      </x:c>
+      <x:c r="H687" s="10" t="s">
+        <x:v>2038</x:v>
+      </x:c>
+      <x:c r="I687" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J687" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K687" s="10" t="s">
+        <x:v>2039</x:v>
+      </x:c>
+      <x:c r="L687" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M687" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="688" hidden="0">
+      <x:c r="A688">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="B688" s="2">
+        <x:v>46173.778599537</x:v>
+      </x:c>
+      <x:c r="C688" s="2">
+        <x:v>46173.7789236111</x:v>
+      </x:c>
+      <x:c r="D688" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E688" s="10" t="s"/>
+      <x:c r="F688" s="2"/>
+      <x:c r="G688" s="10" t="s">
+        <x:v>2040</x:v>
+      </x:c>
+      <x:c r="H688" s="10" t="s">
+        <x:v>2041</x:v>
+      </x:c>
+      <x:c r="I688" s="10" t="s">
+        <x:v>2041</x:v>
+      </x:c>
+      <x:c r="J688" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K688" s="10" t="s">
+        <x:v>2042</x:v>
+      </x:c>
+      <x:c r="L688" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M688" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="689" hidden="0">
+      <x:c r="A689">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="B689" s="2">
+        <x:v>46173.7971875</x:v>
+      </x:c>
+      <x:c r="C689" s="2">
+        <x:v>46173.8015277778</x:v>
+      </x:c>
+      <x:c r="D689" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E689" s="10" t="s"/>
+      <x:c r="F689" s="2"/>
+      <x:c r="G689" s="10" t="s">
+        <x:v>2043</x:v>
+      </x:c>
+      <x:c r="H689" s="10" t="s">
+        <x:v>2044</x:v>
+      </x:c>
+      <x:c r="I689" s="10" t="s">
+        <x:v>1411</x:v>
+      </x:c>
+      <x:c r="J689" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K689" s="10" t="s">
+        <x:v>2045</x:v>
+      </x:c>
+      <x:c r="L689" s="10" t="s">
+        <x:v>2046</x:v>
+      </x:c>
+      <x:c r="M689" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="690" hidden="0">
+      <x:c r="A690">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="B690" s="2">
+        <x:v>46173.8006828704</x:v>
+      </x:c>
+      <x:c r="C690" s="2">
+        <x:v>46173.8037731481</x:v>
+      </x:c>
+      <x:c r="D690" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E690" s="10" t="s"/>
+      <x:c r="F690" s="2"/>
+      <x:c r="G690" s="10" t="s">
+        <x:v>1978</x:v>
+      </x:c>
+      <x:c r="H690" s="10" t="s">
+        <x:v>1979</x:v>
+      </x:c>
+      <x:c r="I690" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J690" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K690" s="10" t="s">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="L690" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M690" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="691" hidden="0">
+      <x:c r="A691">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="B691" s="2">
+        <x:v>46173.8740856481</x:v>
+      </x:c>
+      <x:c r="C691" s="2">
+        <x:v>46173.8744907407</x:v>
+      </x:c>
+      <x:c r="D691" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E691" s="10" t="s"/>
+      <x:c r="F691" s="2"/>
+      <x:c r="G691" s="10" t="s">
+        <x:v>2047</x:v>
+      </x:c>
+      <x:c r="H691" s="10" t="s">
+        <x:v>2048</x:v>
+      </x:c>
+      <x:c r="I691" s="10" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J691" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K691" s="10" t="s">
+        <x:v>1988</x:v>
+      </x:c>
+      <x:c r="L691" s="10" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="M691" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="692" hidden="0">
+      <x:c r="A692">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="B692" s="2">
+        <x:v>46173.9225810185</x:v>
+      </x:c>
+      <x:c r="C692" s="2">
+        <x:v>46173.9249074074</x:v>
+      </x:c>
+      <x:c r="D692" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E692" s="10" t="s"/>
+      <x:c r="F692" s="2"/>
+      <x:c r="G692" s="10" t="s">
+        <x:v>2049</x:v>
+      </x:c>
+      <x:c r="H692" s="10" t="s">
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="I692" s="10" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J692" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K692" s="10" t="s">
+        <x:v>2051</x:v>
+      </x:c>
+      <x:c r="L692" s="10" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="M692" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="693" hidden="0">
+      <x:c r="A693">
+        <x:v>692</x:v>
+      </x:c>
+      <x:c r="B693" s="2">
+        <x:v>46173.9256944444</x:v>
+      </x:c>
+      <x:c r="C693" s="2">
+        <x:v>46173.9268981481</x:v>
+      </x:c>
+      <x:c r="D693" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E693" s="10" t="s"/>
+      <x:c r="F693" s="2"/>
+      <x:c r="G693" s="10" t="s">
+        <x:v>2052</x:v>
+      </x:c>
+      <x:c r="H693" s="10" t="s">
+        <x:v>2053</x:v>
+      </x:c>
+      <x:c r="I693" s="10" t="s">
+        <x:v>1270</x:v>
+      </x:c>
+      <x:c r="J693" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K693" s="10" t="s">
+        <x:v>2054</x:v>
+      </x:c>
+      <x:c r="L693" s="10" t="s">
+        <x:v>2055</x:v>
+      </x:c>
+      <x:c r="M693" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="694" hidden="0">
+      <x:c r="A694">
+        <x:v>693</x:v>
+      </x:c>
+      <x:c r="B694" s="2">
+        <x:v>46173.932037037</x:v>
+      </x:c>
+      <x:c r="C694" s="2">
+        <x:v>46173.9344444444</x:v>
+      </x:c>
+      <x:c r="D694" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E694" s="10" t="s"/>
+      <x:c r="F694" s="2"/>
+      <x:c r="G694" s="10" t="s">
+        <x:v>2049</x:v>
+      </x:c>
+      <x:c r="H694" s="10" t="s">
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="I694" s="10" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J694" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K694" s="10" t="s">
+        <x:v>2051</x:v>
+      </x:c>
+      <x:c r="L694" s="10" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="M694" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="695" hidden="0">
+      <x:c r="A695">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c r="B695" s="2">
+        <x:v>46173.9178125</x:v>
+      </x:c>
+      <x:c r="C695" s="2">
+        <x:v>46173.9409027778</x:v>
+      </x:c>
+      <x:c r="D695" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E695" s="10" t="s"/>
+      <x:c r="F695" s="2"/>
+      <x:c r="G695" s="10" t="s">
+        <x:v>2056</x:v>
+      </x:c>
+      <x:c r="H695" s="10" t="s">
+        <x:v>2057</x:v>
+      </x:c>
+      <x:c r="I695" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J695" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K695" s="10" t="s">
+        <x:v>1906</x:v>
+      </x:c>
+      <x:c r="L695" s="10" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="M695" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="696" hidden="0">
+      <x:c r="A696">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="B696" s="2">
+        <x:v>46173.9478935185</x:v>
+      </x:c>
+      <x:c r="C696" s="2">
+        <x:v>46173.9485648148</x:v>
+      </x:c>
+      <x:c r="D696" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E696" s="10" t="s"/>
+      <x:c r="F696" s="2"/>
+      <x:c r="G696" s="10" t="s">
+        <x:v>2058</x:v>
+      </x:c>
+      <x:c r="H696" s="10" t="s">
+        <x:v>2059</x:v>
+      </x:c>
+      <x:c r="I696" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J696" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K696" s="10" t="s">
+        <x:v>2060</x:v>
+      </x:c>
+      <x:c r="L696" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M696" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="697" hidden="0">
+      <x:c r="A697">
+        <x:v>696</x:v>
+      </x:c>
+      <x:c r="B697" s="2">
+        <x:v>46173.951724537</x:v>
+      </x:c>
+      <x:c r="C697" s="2">
+        <x:v>46173.9531481481</x:v>
+      </x:c>
+      <x:c r="D697" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E697" s="10" t="s"/>
+      <x:c r="F697" s="2"/>
+      <x:c r="G697" s="10" t="s">
+        <x:v>2061</x:v>
+      </x:c>
+      <x:c r="H697" s="10" t="s">
+        <x:v>2062</x:v>
+      </x:c>
+      <x:c r="I697" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="J697" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K697" s="10" t="s">
+        <x:v>2063</x:v>
+      </x:c>
+      <x:c r="L697" s="10" t="s">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="M697" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="698" hidden="0">
+      <x:c r="A698">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="B698" s="2">
+        <x:v>46173.953275463</x:v>
+      </x:c>
+      <x:c r="C698" s="2">
+        <x:v>46173.9540972222</x:v>
+      </x:c>
+      <x:c r="D698" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E698" s="10" t="s"/>
+      <x:c r="F698" s="2"/>
+      <x:c r="G698" s="10" t="s">
+        <x:v>2064</x:v>
+      </x:c>
+      <x:c r="H698" s="10" t="s">
+        <x:v>2065</x:v>
+      </x:c>
+      <x:c r="I698" s="10" t="s">
+        <x:v>2066</x:v>
+      </x:c>
+      <x:c r="J698" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K698" s="10" t="s">
+        <x:v>2063</x:v>
+      </x:c>
+      <x:c r="L698" s="10" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="M698" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="699" hidden="0">
+      <x:c r="A699">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="B699" s="2">
+        <x:v>46173.9541203704</x:v>
+      </x:c>
+      <x:c r="C699" s="2">
+        <x:v>46173.954537037</x:v>
+      </x:c>
+      <x:c r="D699" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E699" s="10" t="s"/>
+      <x:c r="F699" s="2"/>
+      <x:c r="G699" s="10" t="s">
+        <x:v>2067</x:v>
+      </x:c>
+      <x:c r="H699" s="10" t="s">
+        <x:v>2068</x:v>
+      </x:c>
+      <x:c r="I699" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="J699" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K699" s="10" t="s">
+        <x:v>2063</x:v>
+      </x:c>
+      <x:c r="L699" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M699" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="700" hidden="0">
+      <x:c r="A700">
+        <x:v>699</x:v>
+      </x:c>
+      <x:c r="B700" s="2">
+        <x:v>46173.9545717593</x:v>
+      </x:c>
+      <x:c r="C700" s="2">
+        <x:v>46173.955150463</x:v>
+      </x:c>
+      <x:c r="D700" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E700" s="10" t="s"/>
+      <x:c r="F700" s="2"/>
+      <x:c r="G700" s="10" t="s">
+        <x:v>2069</x:v>
+      </x:c>
+      <x:c r="H700" s="10" t="s">
+        <x:v>2070</x:v>
+      </x:c>
+      <x:c r="I700" s="10" t="s">
+        <x:v>2071</x:v>
+      </x:c>
+      <x:c r="J700" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K700" s="10" t="s">
+        <x:v>2063</x:v>
+      </x:c>
+      <x:c r="L700" s="10" t="s">
+        <x:v>915</x:v>
+      </x:c>
+      <x:c r="M700" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="701" hidden="0">
+      <x:c r="A701">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="B701" s="2">
+        <x:v>46173.9552314815</x:v>
+      </x:c>
+      <x:c r="C701" s="2">
+        <x:v>46173.9561342593</x:v>
+      </x:c>
+      <x:c r="D701" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E701" s="10" t="s"/>
+      <x:c r="F701" s="2"/>
+      <x:c r="G701" s="10" t="s">
+        <x:v>2072</x:v>
+      </x:c>
+      <x:c r="H701" s="10" t="s">
+        <x:v>2073</x:v>
+      </x:c>
+      <x:c r="I701" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="J701" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K701" s="10" t="s">
+        <x:v>2063</x:v>
+      </x:c>
+      <x:c r="L701" s="10" t="s">
+        <x:v>2074</x:v>
+      </x:c>
+      <x:c r="M701" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="702" hidden="0">
+      <x:c r="A702">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="B702" s="2">
+        <x:v>46173.9561574074</x:v>
+      </x:c>
+      <x:c r="C702" s="2">
+        <x:v>46173.9566550926</x:v>
+      </x:c>
+      <x:c r="D702" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E702" s="10" t="s"/>
+      <x:c r="F702" s="2"/>
+      <x:c r="G702" s="10" t="s">
+        <x:v>2075</x:v>
+      </x:c>
+      <x:c r="H702" s="10" t="s">
+        <x:v>2076</x:v>
+      </x:c>
+      <x:c r="I702" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="J702" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K702" s="10" t="s">
+        <x:v>2063</x:v>
+      </x:c>
+      <x:c r="L702" s="10" t="s">
+        <x:v>2077</x:v>
+      </x:c>
+      <x:c r="M702" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="703" hidden="0">
+      <x:c r="A703">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="B703" s="2">
+        <x:v>46173.9770833333</x:v>
+      </x:c>
+      <x:c r="C703" s="2">
+        <x:v>46173.9784143518</x:v>
+      </x:c>
+      <x:c r="D703" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E703" s="10" t="s"/>
+      <x:c r="F703" s="2"/>
+      <x:c r="G703" s="10" t="s">
+        <x:v>1373</x:v>
+      </x:c>
+      <x:c r="H703" s="10" t="s">
+        <x:v>1374</x:v>
+      </x:c>
+      <x:c r="I703" s="10" t="s">
+        <x:v>1617</x:v>
+      </x:c>
+      <x:c r="J703" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K703" s="10" t="s">
+        <x:v>2078</x:v>
+      </x:c>
+      <x:c r="L703" s="10" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="M703" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Raa0c61b7a5e04b26"/>
+    <x:tablePart r:id="Rb47b7b15653e4a5b"/>
   </x:tableParts>
 </x:worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096F5A18ADBDD9E4D8F394AC4B3466405" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e59e3e6d23932d1d7525b22f7d7f3a7d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" xmlns:ns3="76b4ec34-0f89-435f-928a-b7c414764614" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d88756df8cabe05f154bf6d416a348" ns2:_="" ns3:_="">
-    <xsd:import namespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb"/>
-    <xsd:import namespace="76b4ec34-0f89-435f-928a-b7c414764614"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ad0b2da7-f7f1-4ade-bc4d-78491eef27d0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="76b4ec34-0f89-435f-928a-b7c414764614" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c696ee1e-5302-4bbd-96b7-dbc90bffde0f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="76b4ec34-0f89-435f-928a-b7c414764614">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="76b4ec34-0f89-435f-928a-b7c414764614" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E70C458A-B127-4B5B-BCA6-208F02BC594D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2AA043A-46FE-4B9C-A7E5-8C0C6478B57E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F64B5A0E-8E01-4101-BEA0-4092991DD4AD}"/>
 </file>
--- a/WOAH Datathon registration form.xlsx
+++ b/WOAH Datathon registration form.xlsx
@@ -32704,4 +32704,297 @@
     <x:tablePart r:id="Rb47b7b15653e4a5b"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096F5A18ADBDD9E4D8F394AC4B3466405" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e59e3e6d23932d1d7525b22f7d7f3a7d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" xmlns:ns3="76b4ec34-0f89-435f-928a-b7c414764614" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d88756df8cabe05f154bf6d416a348" ns2:_="" ns3:_="">
+    <xsd:import namespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb"/>
+    <xsd:import namespace="76b4ec34-0f89-435f-928a-b7c414764614"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ad0b2da7-f7f1-4ade-bc4d-78491eef27d0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="76b4ec34-0f89-435f-928a-b7c414764614" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c696ee1e-5302-4bbd-96b7-dbc90bffde0f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="76b4ec34-0f89-435f-928a-b7c414764614">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="76b4ec34-0f89-435f-928a-b7c414764614" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a018c8fa-b569-4a3a-a61d-777c9f4cbcbb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEB2A0AE-24E8-426B-B491-FC7D19746714}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{632B6555-FAF5-4714-A462-E30C6E8F5748}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A77026D4-071F-47D3-976E-2AF47112C9B9}"/>
 </file>